--- a/immobilien/Hauskauf_Rechner_Damme.xlsx
+++ b/immobilien/Hauskauf_Rechner_Damme.xlsx
@@ -62,6 +62,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
@@ -74,11 +79,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00008000"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -135,13 +135,13 @@
     <xf numFmtId="1" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -153,27 +153,34 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -194,6 +201,13 @@
         <b val="1"/>
         <color rgb="00B3362F"/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F8EDD8"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -274,19 +288,29 @@
     <author>Rechner</author>
   </authors>
   <commentList>
-    <comment ref="H29" authorId="0" shapeId="0">
+    <comment ref="H26" authorId="0" shapeId="0">
       <text>
-        <t>Vereinfacht: (Miete − Ausfall − Instandhaltung − sonstige Kosten) − Zinsen − AfA, × Steuersatz. Negativ = Steuererstattung.</t>
+        <t>Aus dem Blatt Prognose: Zinsen der ersten 12 Monatsraten. Etwas weniger als Darlehen × Zins, weil die Tilgung die Schuld schon im ersten Jahr senkt.</t>
+      </text>
+    </comment>
+    <comment ref="H30" authorId="0" shapeId="0">
+      <text>
+        <t>Vereinfacht: (Miete − Ausfall − Instandhaltung − sonstige Kosten) − Zinsen − AfA, × Steuersatz. Negativ = Steuererstattung. Achtung: Eine Instandhaltungs-RÜCKLAGE ist steuerlich nicht absetzbar, nur tatsächliche Reparaturen. Hier wird angenommen, dass im Schnitt so viel repariert wird.</t>
       </text>
     </comment>
     <comment ref="H32" authorId="0" shapeId="0">
       <text>
-        <t>Der Cashflow hängt linear vom Kaufpreis ab. Dieser Wert ist der Preis, bei dem der Cashflow nach Steuern genau 0 € wäre (gleiches Eigenkapital, Darlehen &gt; 0).</t>
+        <t>Der Cashflow nach Steuern hängt linear vom Kaufpreis ab (Nebenkosten, Darlehen, Zinsen und AfA wachsen proportional mit). Dieser Wert ist der Preis, bei dem der Cashflow genau 0 € wäre – bei gleichem Eigenkapital. Gilt nur, solange ein Darlehen nötig ist.</t>
       </text>
     </comment>
     <comment ref="H38" authorId="0" shapeId="0">
       <text>
         <t>Fernere Lebenserwartung Frauen (vorsichtiger, längerer Wert), gerundet nach Sterbetafel Destatis 2021/23, linear interpoliert. Siehe Blatt Lebenserwartung.</t>
+      </text>
+    </comment>
+    <comment ref="H39" authorId="0" shapeId="0">
+      <text>
+        <t>Wie viele Jahre der Verkaufserlös (verzinst mit dem Kapitalzins) für die Jahresmiete reicht. "unbegrenzt" = die Zinsen allein decken die Miete.</t>
       </text>
     </comment>
   </commentList>
@@ -582,18 +606,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I48"/>
+  <dimension ref="B1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
     <col width="3" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -652,7 +676,7 @@
         </is>
       </c>
       <c r="H6" s="7">
-        <f>C7*C8</f>
+        <f>$C$7*$C$8</f>
         <v/>
       </c>
     </row>
@@ -681,7 +705,7 @@
         </is>
       </c>
       <c r="H7" s="7">
-        <f>H6+C11</f>
+        <f>$H$6+$C$11</f>
         <v/>
       </c>
     </row>
@@ -710,7 +734,7 @@
         </is>
       </c>
       <c r="H8" s="7">
-        <f>C6*(C13+C14+C15)</f>
+        <f>$C$6*($C$13+$C$14+$C$15)</f>
         <v/>
       </c>
     </row>
@@ -739,7 +763,7 @@
         </is>
       </c>
       <c r="H9" s="7">
-        <f>C6+H8+C9</f>
+        <f>$C$6+$H$8+$C$9</f>
         <v/>
       </c>
     </row>
@@ -768,7 +792,7 @@
         </is>
       </c>
       <c r="H10" s="7">
-        <f>MAX(0,H9-C17)</f>
+        <f>MAX(0,$H$9-$C$17)</f>
         <v/>
       </c>
     </row>
@@ -793,7 +817,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Monatliche Rechnung (1. Jahr)</t>
+          <t>Monatliche Rechnung (Durchschnitt 1. Jahr)</t>
         </is>
       </c>
       <c r="H11" s="4" t="n"/>
@@ -814,7 +838,7 @@
         </is>
       </c>
       <c r="H12" s="7">
-        <f>H7</f>
+        <f>$H$7</f>
         <v/>
       </c>
     </row>
@@ -843,7 +867,7 @@
         </is>
       </c>
       <c r="H13" s="7">
-        <f>-H7*C23</f>
+        <f>-$H$7*$C$25</f>
         <v/>
       </c>
     </row>
@@ -872,7 +896,7 @@
         </is>
       </c>
       <c r="H14" s="7">
-        <f>-H10*(C18+C19)/12</f>
+        <f>-$H$10*($C$18+$C$19)/12</f>
         <v/>
       </c>
     </row>
@@ -901,7 +925,7 @@
         </is>
       </c>
       <c r="H15" s="7">
-        <f>-(C7+C10)*C21/12</f>
+        <f>-($C$7+$C$10)*$C$23/12</f>
         <v/>
       </c>
     </row>
@@ -920,7 +944,7 @@
         </is>
       </c>
       <c r="H16" s="7">
-        <f>-C22</f>
+        <f>-$C$24</f>
         <v/>
       </c>
     </row>
@@ -949,7 +973,7 @@
         </is>
       </c>
       <c r="H17" s="12">
-        <f>SUM(H12:H16)</f>
+        <f>SUM($H$12:$H$16)</f>
         <v/>
       </c>
     </row>
@@ -969,7 +993,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Annahme; aktuelles Bankangebot eintragen</t>
+          <t>Annahme – aktuelles Bankangebot eintragen</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -978,7 +1002,7 @@
         </is>
       </c>
       <c r="H18" s="7">
-        <f>-H29/12</f>
+        <f>-$H$30/12</f>
         <v/>
       </c>
     </row>
@@ -996,30 +1020,44 @@
           <t>% p. a.</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Rate = Darlehen × (Zins + Tilgung) ÷ 12</t>
+        </is>
+      </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
           <t>CASHFLOW NACH STEUERN / MONAT</t>
         </is>
       </c>
       <c r="H19" s="15">
-        <f>H17+H18</f>
+        <f>$H$17+$H$18</f>
         <v/>
       </c>
       <c r="I19" s="14">
-        <f>IF(H19&gt;=0,"Trägt sich selbst",IF(H19&gt;=-150,"Leichter Zuschuss nötig","Deutlicher Zuschuss nötig"))</f>
+        <f>IF($H$19&gt;=0,"Trägt sich selbst",IF($H$19&gt;=-150,"Leichter Zuschuss nötig","Deutlicher Zuschuss nötig"))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Laufende Kosten &amp; Steuer</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Zinsbindung</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Jahre</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>danach gilt der Anschlusszins (Rate bleibt gleich)</t>
+        </is>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Kennzahlen</t>
@@ -1031,20 +1069,20 @@
     <row r="21">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Instandhaltung</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>14</v>
+          <t>Anschlusszins</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>0.045</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>€/m² · Jahr</t>
+          <t>% p. a.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Altbau: ca. 12–18 €</t>
+          <t>Annahme für die Zeit nach der Zinsbindung</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -1053,85 +1091,79 @@
         </is>
       </c>
       <c r="H21" s="16">
-        <f>IFERROR(C6/(H7*12),0)</f>
+        <f>IFERROR($C$6/($H$7*12),0)</f>
         <v/>
       </c>
       <c r="I21" s="11">
-        <f>IF(H21&lt;=18,"günstig",IF(H21&lt;=22,"mittel","teuer"))</f>
+        <f>IF($H$21&lt;=18,"günstig",IF($H$21&lt;=22,"mittel","teuer"))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Nicht umlagefähige Kosten</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>€/Monat</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Verwaltung, Bankgebühren</t>
-        </is>
-      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Laufende Kosten &amp; Steuer</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Bruttomietrendite</t>
         </is>
       </c>
       <c r="H22" s="17">
-        <f>IFERROR(H7*12/C6,0)</f>
+        <f>IFERROR($H$7*12/$C$6,0)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Mietausfall-Reserve</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>0.02</v>
+          <t>Instandhaltung</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>14</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>% der Miete</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
+          <t>€/m² · Jahr</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Altbau: ca. 12–18 €</t>
+        </is>
+      </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Nettomietrendite</t>
         </is>
       </c>
       <c r="H23" s="17">
-        <f>IFERROR((H12+H13+H15+H16)*12/H9,0)</f>
+        <f>IFERROR(($H$12+$H$13+$H$15+$H$16)*12/$H$9,0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Gebäudeanteil</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="n">
-        <v>0.7</v>
+          <t>Nicht umlagefähige Kosten</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>20</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>% vom Kaufpreis</t>
+          <t>€/Monat</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Rest = Grundstück (nicht abschreibbar)</t>
+          <t>Verwaltung, Bankgebühren</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1140,14 +1172,14 @@
         </is>
       </c>
       <c r="H24" s="18">
-        <f>IFERROR((H19*12+H30)/C17,0)</f>
+        <f>IFERROR(($H$19*12+$H$27)/$C$17,0)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>AfA-Satz</t>
+          <t>Mietausfall-Reserve</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
@@ -1155,14 +1187,10 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>% p. a.</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Baujahr 1925–2022: 2 %</t>
-        </is>
-      </c>
+          <t>% der Miete</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Steuer 1. Jahr (vereinfacht)</t>
@@ -1174,143 +1202,157 @@
     <row r="26">
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Persönlicher Steuersatz</t>
+          <t>Gebäudeanteil</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% vom Kaufpreis</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Grenzsteuersatz</t>
+          <t>Rest = Grundstück (nicht abschreibbar)</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Zinsen Jahr 1</t>
-        </is>
-      </c>
-      <c r="H26" s="7">
-        <f>H10*C18</f>
+          <t>Zinsen Jahr 1 (monatsgenau)</t>
+        </is>
+      </c>
+      <c r="H26" s="19">
+        <f>-Prognose!$G$5</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Entwicklung (für Blatt Prognose)</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>AfA-Satz</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>% p. a.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Baujahr 1925–2022: 2 %, vor 1925: 2,5 %</t>
+        </is>
+      </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>AfA pro Jahr</t>
-        </is>
-      </c>
-      <c r="H27" s="7">
-        <f>((C6+H8)*C24+C9)*C25</f>
+          <t>Tilgung Jahr 1 (Vermögensaufbau)</t>
+        </is>
+      </c>
+      <c r="H27" s="19">
+        <f>-Prognose!$H$5</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="5" t="inlineStr">
         <is>
+          <t>Persönlicher Steuersatz</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Grenzsteuersatz</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>AfA pro Jahr</t>
+        </is>
+      </c>
+      <c r="H28" s="7">
+        <f>(($C$6+$H$8)*$C$26+$C$9)*$C$27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Entwicklung (für Blatt Prognose)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Steuerliches Ergebnis</t>
+        </is>
+      </c>
+      <c r="H29" s="7">
+        <f>($H$12+$H$13+$H$15+$H$16)*12-$H$26-$H$28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
           <t>Mietsteigerung</t>
         </is>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C30" s="10" t="n">
         <v>0.015</v>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>% p. a.</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Annahme</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Steuerliches Ergebnis</t>
-        </is>
-      </c>
-      <c r="H28" s="7">
-        <f>(H12+H13+H15+H16)*12-H26-H27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Wertsteigerung</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>% p. a.</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Annahme</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Annahme; gesetzlich begrenzt (Mietspiegel, Kappungsgrenze)</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Steuer (+ zahlen / − Erstattung)</t>
         </is>
       </c>
-      <c r="H29" s="7">
-        <f>H28*C26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Verkäufer</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Tilgung Jahr 1 (Vermögensaufbau)</t>
-        </is>
-      </c>
       <c r="H30" s="7">
-        <f>H10*C19</f>
+        <f>$H$29*$C$28</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Alter (jüngste Person)</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>75</v>
+          <t>Kostensteigerung</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>0.02</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Jahre</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
+          <t>% p. a.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Annahme für Instandhaltung und sonstige Kosten</t>
+        </is>
+      </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Maximaler Kaufpreis</t>
@@ -1322,60 +1364,104 @@
     <row r="32">
       <c r="B32" s="5" t="inlineStr">
         <is>
+          <t>Wertsteigerung</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>% p. a.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Annahme</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>Max. Kaufpreis für Cashflow ≥ 0</t>
+        </is>
+      </c>
+      <c r="H32" s="20">
+        <f>IF($H$10&lt;=0,"–",MAX(0,$C$6+$H$19/((1+$C$13+$C$14+$C$15)/12*(($C$18+$C$19)-$C$28*($H$26/$H$10+$C$26*$C$27)))))</f>
+        <v/>
+      </c>
+      <c r="I32" s="21" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Verkäufer</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Nötiger Abschlag</t>
+        </is>
+      </c>
+      <c r="H33" s="7">
+        <f>IF(ISNUMBER($H$32),MAX(0,$C$6-$H$32),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Alter (jüngste Person)</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Jahre</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Tabelle reicht von 60 bis 95 Jahre</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Nötiger Abschlag in %</t>
+        </is>
+      </c>
+      <c r="H34" s="18">
+        <f>IFERROR($H$33/$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="I34" s="11">
+        <f>IF($H$10&lt;=0,"kein Darlehen – Formel nicht nötig",IF($H$33=0,"Preis passt","so viel Abschlag bräuchtest du"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
           <t>Zins auf sein Kapital</t>
         </is>
       </c>
-      <c r="C32" s="10" t="n">
+      <c r="C35" s="10" t="n">
         <v>0.025</v>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>% p. a.</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Tagesgeld/Anleihen, Annahme</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>Max. Kaufpreis für Cashflow ≥ 0</t>
-        </is>
-      </c>
-      <c r="H32" s="19">
-        <f>IFERROR(MAX(0,C6+H19/((1+C13+C14+C15)/12*((C18+C19)-C26*(C18+C24*C25)))),0)</f>
-        <v/>
-      </c>
-      <c r="I32" s="20" t="n"/>
-    </row>
-    <row r="33">
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>Nötiger Abschlag</t>
-        </is>
-      </c>
-      <c r="H33" s="7">
-        <f>MAX(0,C6-H32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Nötiger Abschlag in %</t>
-        </is>
-      </c>
-      <c r="H34" s="18">
-        <f>IFERROR(H33/C6,0)</f>
-        <v/>
-      </c>
-      <c r="I34" s="11">
-        <f>IF(H33=0,"Preis passt","so viel Abschlag bräuchtest du")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
       <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Sicht des Verkäufers</t>
@@ -1391,7 +1477,7 @@
         </is>
       </c>
       <c r="H36" s="7">
-        <f>C6</f>
+        <f>$C$6</f>
         <v/>
       </c>
     </row>
@@ -1402,7 +1488,7 @@
         </is>
       </c>
       <c r="H37" s="7">
-        <f>H6*12</f>
+        <f>$H$6*12</f>
         <v/>
       </c>
     </row>
@@ -1413,7 +1499,7 @@
         </is>
       </c>
       <c r="H38" s="16">
-        <f>INDEX(Lebenserwartung!$B$4:$B$11,MATCH(MIN(MAX(C31,60),94.99),Lebenserwartung!$A$4:$A$11,1))+(INDEX(Lebenserwartung!$B$4:$B$11,MATCH(MIN(MAX(C31,60),94.99),Lebenserwartung!$A$4:$A$11,1)+1)-INDEX(Lebenserwartung!$B$4:$B$11,MATCH(MIN(MAX(C31,60),94.99),Lebenserwartung!$A$4:$A$11,1)))*(MIN(MAX(C31,60),95)-INDEX(Lebenserwartung!$A$4:$A$11,MATCH(MIN(MAX(C31,60),94.99),Lebenserwartung!$A$4:$A$11,1)))/5</f>
+        <f>INDEX(Lebenserwartung!$B$4:$B$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1))+(INDEX(Lebenserwartung!$B$4:$B$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)+1)-INDEX(Lebenserwartung!$B$4:$B$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)))*(MIN(MAX($C$34,60),95)-INDEX(Lebenserwartung!$A$4:$A$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)))/(INDEX(Lebenserwartung!$A$4:$A$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)+1)-INDEX(Lebenserwartung!$A$4:$A$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)))</f>
         <v/>
       </c>
     </row>
@@ -1424,7 +1510,7 @@
         </is>
       </c>
       <c r="H39" s="16">
-        <f>IF(H37&lt;=C6*C32,"unbegrenzt",IF(C32=0,C6/H37,NPER(C32,-H37,C6)))</f>
+        <f>IF($H$37&lt;=0,"unbegrenzt",IF($C$35=0,$C$6/$H$37,IF($H$37&lt;=$C$6*$C$35,"unbegrenzt",NPER($C$35,-$H$37,$C$6))))</f>
         <v/>
       </c>
     </row>
@@ -1435,7 +1521,7 @@
         </is>
       </c>
       <c r="H40" s="7">
-        <f>MAX(0,IF(C32=0,C6-H37*H38,FV(C32,H38,H37,-C6)))</f>
+        <f>MAX(0,IF($C$35=0,$C$6-$H$37*$H$38,FV($C$35,$H$38,$H$37,-$C$6)))</f>
         <v/>
       </c>
     </row>
@@ -1445,41 +1531,90 @@
           <t>Bewertung</t>
         </is>
       </c>
-      <c r="H41" s="21">
-        <f>IF(H39="unbegrenzt","Geld reicht sicher",IF(H39&gt;H38,"Geld reicht sicher","Achtung: Geld reicht voraussichtlich nicht"))</f>
-        <v/>
-      </c>
+      <c r="H41" s="22">
+        <f>IF($H$39="unbegrenzt","Geld reicht sicher",IF($H$39&gt;$H$38,"Geld reicht sicher","Achtung: Geld reicht voraussichtlich nicht"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Kontrolle</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="11" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Prognose Jahr 1 = Monatswert × 12</t>
+        </is>
+      </c>
+      <c r="H44" s="23">
+        <f>IF(ABS(Prognose!$M$5-$H$19*12)&lt;1,"OK","Abweichung prüfen")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Restschuld nie negativ</t>
+        </is>
+      </c>
+      <c r="H45" s="23">
+        <f>IF(MIN(Prognose!$I$5:$I$34)&gt;=-0.01,"OK","Abweichung prüfen")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Tilgung Jahr 1 + Zinsen = 12 Raten</t>
+        </is>
+      </c>
+      <c r="H46" s="23">
+        <f>IF($H$10=0,"OK",IF(ABS($H$26+$H$27+$H$14*12)&lt;1,"OK","Abweichung prüfen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>Hinweise:</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>• Kreditrate = Annuität aus Sollzins + anfänglicher Tilgung. Zinsen Jahr 1 vereinfacht = Darlehen × Zins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>• AfA = Gebäudeanteil von Kaufpreis + Nebenkosten × AfA-Satz; Sofort-Investitionen vereinfacht mit abgeschrieben.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="2" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>• Kreditrate = Annuität: Darlehen × (Sollzins + anfängliche Tilgung) ÷ 12, monatlich gezahlt. Nach der Zinsbindung bleibt die Rate gleich, es gilt der Anschlusszins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>• Zinsen und Tilgung werden im Blatt Prognose monatsgenau je Jahr berechnet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>• AfA = Gebäudeanteil von Kaufpreis + Nebenkosten × AfA-Satz; Sofort-Investitionen vereinfacht mit abgeschrieben (anschaffungsnahe Herstellungskosten).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>• Kaufpreisfaktor: bis 18 günstig, 18–22 mittel, über 22 teuer (Faustregel ländliche Lage).</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="2" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>• Keine Steuer- oder Rechtsberatung. Vor dem Kauf Bank, Steuerberater und Notar einbeziehen.</t>
         </is>
@@ -1516,6 +1651,132 @@
       <formula>LEFT($H$41,7)&lt;&gt;"Achtung"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H44">
+    <cfRule type="expression" priority="9" dxfId="0">
+      <formula>$H$44="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="2">
+      <formula>$H$44&lt;&gt;"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H45">
+    <cfRule type="expression" priority="11" dxfId="0">
+      <formula>$H$45="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="2">
+      <formula>$H$45&lt;&gt;"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H46">
+    <cfRule type="expression" priority="13" dxfId="0">
+      <formula>$H$46="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="2">
+      <formula>$H$46&lt;&gt;"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="25">
+    <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Wert zwischen 0 und 1e+09 eingeben." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Wert zwischen 0 und 1e+09 eingeben." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Wert zwischen 0 und 1e+09 eingeben." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Wert zwischen 0 und 1e+09 eingeben." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Wert zwischen 0 und 1e+09 eingeben." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Wert zwischen 0 und 1e+09 eingeben." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Prozentwert zwischen 0 % und 100 % eingeben, z. B. 5 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Prozentwert zwischen 0 % und 100 % eingeben, z. B. 5 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Prozentwert zwischen 0 % und 100 % eingeben, z. B. 5 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Wert zwischen 0 und 1e+09 eingeben." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Prozentwert zwischen 0 % und 100 % eingeben, z. B. 5 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Prozentwert zwischen 0 % und 100 % eingeben, z. B. 5 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Wert zwischen 1 und 40 eingeben." type="whole" operator="between">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Prozentwert zwischen 0 % und 100 % eingeben, z. B. 5 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Wert zwischen 0 und 1e+09 eingeben." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Wert zwischen 0 und 1e+09 eingeben." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Prozentwert zwischen 0 % und 100 % eingeben, z. B. 5 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Prozentwert zwischen 0 % und 100 % eingeben, z. B. 5 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Prozentwert zwischen 0 % und 100 % eingeben, z. B. 5 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Prozentwert zwischen 0 % und 100 % eingeben, z. B. 5 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Prozentwert zwischen 0 % und 100 % eingeben, z. B. 5 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Prozentwert zwischen 0 % und 100 % eingeben, z. B. 5 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Prozentwert zwischen 0 % und 100 % eingeben, z. B. 5 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Wert zwischen 18 und 110 eingeben." type="whole" operator="between">
+      <formula1>18</formula1>
+      <formula2>110</formula2>
+    </dataValidation>
+    <dataValidation sqref="C35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Ungültiger Wert" error="Bitte einen Prozentwert zwischen 0 % und 100 % eingeben, z. B. 5 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -1527,11 +1788,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1545,94 +1806,100 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
-        <is>
-          <t>Prognose über 20 Jahre (Werte pro Jahr)</t>
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Prognose über 30 Jahre (Werte pro Jahr)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Basiert auf den Eingaben im Blatt Rechner. Miete steigt mit der Mietsteigerung, Kosten bleiben konstant (vereinfacht).</t>
+          <t>Basiert auf dem Blatt Rechner. Zinsen/Tilgung monatsgenau; Miete und Kosten steigen mit den eingegebenen Raten. Grüne Schrift = Bezug auf das Blatt Rechner.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Jahr</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Zinssatz</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Restschuld Anfang</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>Kaltmiete</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>Mietausfall</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>Instandh. + Kosten</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>Zinsen</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="H4" s="25" t="inlineStr">
         <is>
           <t>Tilgung</t>
         </is>
       </c>
-      <c r="H4" s="23" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t>Restschuld Ende</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="J4" s="25" t="inlineStr">
         <is>
           <t>Cashflow vor Steuern</t>
         </is>
       </c>
-      <c r="J4" s="23" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>AfA</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr">
+      <c r="L4" s="25" t="inlineStr">
         <is>
           <t>Steuereffekt</t>
         </is>
       </c>
-      <c r="L4" s="23" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>Cashflow nach Steuern</t>
         </is>
       </c>
-      <c r="M4" s="23" t="inlineStr">
+      <c r="N4" s="25" t="inlineStr">
         <is>
           <t>Kumulierter Cashflow</t>
         </is>
       </c>
-      <c r="N4" s="23" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t>Immobilienwert</t>
         </is>
       </c>
-      <c r="O4" s="23" t="inlineStr">
+      <c r="P4" s="25" t="inlineStr">
         <is>
           <t>Eigenkapital im Objekt</t>
         </is>
@@ -1642,60 +1909,64 @@
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="26">
+        <f>IF(A5&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C5" s="27">
         <f>Rechner!$H$10</f>
         <v/>
       </c>
-      <c r="C5" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A5-1)</f>
-        <v/>
-      </c>
-      <c r="D5" s="24">
-        <f>-C5*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E5" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F5" s="24">
-        <f>-B5*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G5" s="25">
-        <f>-MIN(B5,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F5)</f>
-        <v/>
-      </c>
-      <c r="H5" s="25">
-        <f>B5+G5</f>
-        <v/>
-      </c>
-      <c r="I5" s="25">
-        <f>C5+D5+E5+F5+G5</f>
-        <v/>
-      </c>
-      <c r="J5" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K5" s="25">
-        <f>-(C5+D5+E5+F5+J5)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L5" s="26">
-        <f>I5+K5</f>
-        <v/>
-      </c>
-      <c r="M5" s="25">
-        <f>L5</f>
-        <v/>
-      </c>
-      <c r="N5" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A5</f>
-        <v/>
-      </c>
-      <c r="O5" s="26">
-        <f>N5-H5</f>
+      <c r="D5" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A5-1)</f>
+        <v/>
+      </c>
+      <c r="E5" s="27">
+        <f>-D5*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F5" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A5-1)</f>
+        <v/>
+      </c>
+      <c r="G5" s="28">
+        <f>IF(C5&lt;=0,0,IF(I5&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C5-I5)),IF(B5=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B5/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C5)-C5))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="28">
+        <f>-(C5-I5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="28">
+        <f>IF(C5&lt;=0,0,IF(B5=0,MAX(0,C5-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C5*(1+B5/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B5/12)^12-1)/(B5/12)))))</f>
+        <v/>
+      </c>
+      <c r="J5" s="28">
+        <f>D5+E5+F5+G5+H5</f>
+        <v/>
+      </c>
+      <c r="K5" s="27">
+        <f>-Rechner!$H$28*(A5&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L5" s="28">
+        <f>-(D5+E5+F5+G5+K5)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M5" s="29">
+        <f>J5+L5</f>
+        <v/>
+      </c>
+      <c r="N5" s="28">
+        <f>M5</f>
+        <v/>
+      </c>
+      <c r="O5" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A5</f>
+        <v/>
+      </c>
+      <c r="P5" s="29">
+        <f>O5-I5</f>
         <v/>
       </c>
     </row>
@@ -1703,60 +1974,64 @@
       <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="25">
-        <f>H5</f>
-        <v/>
-      </c>
-      <c r="C6" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A6-1)</f>
-        <v/>
-      </c>
-      <c r="D6" s="24">
-        <f>-C6*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E6" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F6" s="24">
-        <f>-B6*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G6" s="25">
-        <f>-MIN(B6,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F6)</f>
-        <v/>
-      </c>
-      <c r="H6" s="25">
-        <f>B6+G6</f>
-        <v/>
-      </c>
-      <c r="I6" s="25">
-        <f>C6+D6+E6+F6+G6</f>
-        <v/>
-      </c>
-      <c r="J6" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K6" s="25">
-        <f>-(C6+D6+E6+F6+J6)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L6" s="26">
-        <f>I6+K6</f>
-        <v/>
-      </c>
-      <c r="M6" s="25">
-        <f>M5+L6</f>
-        <v/>
-      </c>
-      <c r="N6" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A6</f>
-        <v/>
-      </c>
-      <c r="O6" s="26">
-        <f>N6-H6</f>
+      <c r="B6" s="26">
+        <f>IF(A6&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C6" s="28">
+        <f>I5</f>
+        <v/>
+      </c>
+      <c r="D6" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A6-1)</f>
+        <v/>
+      </c>
+      <c r="E6" s="27">
+        <f>-D6*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F6" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A6-1)</f>
+        <v/>
+      </c>
+      <c r="G6" s="28">
+        <f>IF(C6&lt;=0,0,IF(I6&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C6-I6)),IF(B6=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B6/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C6)-C6))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="28">
+        <f>-(C6-I6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="28">
+        <f>IF(C6&lt;=0,0,IF(B6=0,MAX(0,C6-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C6*(1+B6/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B6/12)^12-1)/(B6/12)))))</f>
+        <v/>
+      </c>
+      <c r="J6" s="28">
+        <f>D6+E6+F6+G6+H6</f>
+        <v/>
+      </c>
+      <c r="K6" s="27">
+        <f>-Rechner!$H$28*(A6&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L6" s="28">
+        <f>-(D6+E6+F6+G6+K6)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M6" s="29">
+        <f>J6+L6</f>
+        <v/>
+      </c>
+      <c r="N6" s="28">
+        <f>N5+M6</f>
+        <v/>
+      </c>
+      <c r="O6" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A6</f>
+        <v/>
+      </c>
+      <c r="P6" s="29">
+        <f>O6-I6</f>
         <v/>
       </c>
     </row>
@@ -1764,60 +2039,64 @@
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="25">
-        <f>H6</f>
-        <v/>
-      </c>
-      <c r="C7" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A7-1)</f>
-        <v/>
-      </c>
-      <c r="D7" s="24">
-        <f>-C7*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E7" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F7" s="24">
-        <f>-B7*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G7" s="25">
-        <f>-MIN(B7,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="25">
-        <f>B7+G7</f>
-        <v/>
-      </c>
-      <c r="I7" s="25">
-        <f>C7+D7+E7+F7+G7</f>
-        <v/>
-      </c>
-      <c r="J7" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K7" s="25">
-        <f>-(C7+D7+E7+F7+J7)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L7" s="26">
-        <f>I7+K7</f>
-        <v/>
-      </c>
-      <c r="M7" s="25">
-        <f>M6+L7</f>
-        <v/>
-      </c>
-      <c r="N7" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A7</f>
-        <v/>
-      </c>
-      <c r="O7" s="26">
-        <f>N7-H7</f>
+      <c r="B7" s="26">
+        <f>IF(A7&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C7" s="28">
+        <f>I6</f>
+        <v/>
+      </c>
+      <c r="D7" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A7-1)</f>
+        <v/>
+      </c>
+      <c r="E7" s="27">
+        <f>-D7*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F7" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A7-1)</f>
+        <v/>
+      </c>
+      <c r="G7" s="28">
+        <f>IF(C7&lt;=0,0,IF(I7&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C7-I7)),IF(B7=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B7/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C7)-C7))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="28">
+        <f>-(C7-I7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="28">
+        <f>IF(C7&lt;=0,0,IF(B7=0,MAX(0,C7-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C7*(1+B7/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B7/12)^12-1)/(B7/12)))))</f>
+        <v/>
+      </c>
+      <c r="J7" s="28">
+        <f>D7+E7+F7+G7+H7</f>
+        <v/>
+      </c>
+      <c r="K7" s="27">
+        <f>-Rechner!$H$28*(A7&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L7" s="28">
+        <f>-(D7+E7+F7+G7+K7)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M7" s="29">
+        <f>J7+L7</f>
+        <v/>
+      </c>
+      <c r="N7" s="28">
+        <f>N6+M7</f>
+        <v/>
+      </c>
+      <c r="O7" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A7</f>
+        <v/>
+      </c>
+      <c r="P7" s="29">
+        <f>O7-I7</f>
         <v/>
       </c>
     </row>
@@ -1825,60 +2104,64 @@
       <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="25">
-        <f>H7</f>
-        <v/>
-      </c>
-      <c r="C8" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A8-1)</f>
-        <v/>
-      </c>
-      <c r="D8" s="24">
-        <f>-C8*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E8" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F8" s="24">
-        <f>-B8*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G8" s="25">
-        <f>-MIN(B8,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="25">
-        <f>B8+G8</f>
-        <v/>
-      </c>
-      <c r="I8" s="25">
-        <f>C8+D8+E8+F8+G8</f>
-        <v/>
-      </c>
-      <c r="J8" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K8" s="25">
-        <f>-(C8+D8+E8+F8+J8)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L8" s="26">
-        <f>I8+K8</f>
-        <v/>
-      </c>
-      <c r="M8" s="25">
-        <f>M7+L8</f>
-        <v/>
-      </c>
-      <c r="N8" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A8</f>
-        <v/>
-      </c>
-      <c r="O8" s="26">
-        <f>N8-H8</f>
+      <c r="B8" s="26">
+        <f>IF(A8&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C8" s="28">
+        <f>I7</f>
+        <v/>
+      </c>
+      <c r="D8" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A8-1)</f>
+        <v/>
+      </c>
+      <c r="E8" s="27">
+        <f>-D8*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F8" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A8-1)</f>
+        <v/>
+      </c>
+      <c r="G8" s="28">
+        <f>IF(C8&lt;=0,0,IF(I8&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C8-I8)),IF(B8=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B8/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C8)-C8))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="28">
+        <f>-(C8-I8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="28">
+        <f>IF(C8&lt;=0,0,IF(B8=0,MAX(0,C8-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C8*(1+B8/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B8/12)^12-1)/(B8/12)))))</f>
+        <v/>
+      </c>
+      <c r="J8" s="28">
+        <f>D8+E8+F8+G8+H8</f>
+        <v/>
+      </c>
+      <c r="K8" s="27">
+        <f>-Rechner!$H$28*(A8&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L8" s="28">
+        <f>-(D8+E8+F8+G8+K8)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M8" s="29">
+        <f>J8+L8</f>
+        <v/>
+      </c>
+      <c r="N8" s="28">
+        <f>N7+M8</f>
+        <v/>
+      </c>
+      <c r="O8" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A8</f>
+        <v/>
+      </c>
+      <c r="P8" s="29">
+        <f>O8-I8</f>
         <v/>
       </c>
     </row>
@@ -1886,60 +2169,64 @@
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="25">
-        <f>H8</f>
-        <v/>
-      </c>
-      <c r="C9" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A9-1)</f>
-        <v/>
-      </c>
-      <c r="D9" s="24">
-        <f>-C9*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E9" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F9" s="24">
-        <f>-B9*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G9" s="25">
-        <f>-MIN(B9,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="25">
-        <f>B9+G9</f>
-        <v/>
-      </c>
-      <c r="I9" s="25">
-        <f>C9+D9+E9+F9+G9</f>
-        <v/>
-      </c>
-      <c r="J9" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K9" s="25">
-        <f>-(C9+D9+E9+F9+J9)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L9" s="26">
-        <f>I9+K9</f>
-        <v/>
-      </c>
-      <c r="M9" s="25">
-        <f>M8+L9</f>
-        <v/>
-      </c>
-      <c r="N9" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A9</f>
-        <v/>
-      </c>
-      <c r="O9" s="26">
-        <f>N9-H9</f>
+      <c r="B9" s="26">
+        <f>IF(A9&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C9" s="28">
+        <f>I8</f>
+        <v/>
+      </c>
+      <c r="D9" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A9-1)</f>
+        <v/>
+      </c>
+      <c r="E9" s="27">
+        <f>-D9*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F9" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A9-1)</f>
+        <v/>
+      </c>
+      <c r="G9" s="28">
+        <f>IF(C9&lt;=0,0,IF(I9&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C9-I9)),IF(B9=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B9/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C9)-C9))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="28">
+        <f>-(C9-I9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="28">
+        <f>IF(C9&lt;=0,0,IF(B9=0,MAX(0,C9-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C9*(1+B9/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B9/12)^12-1)/(B9/12)))))</f>
+        <v/>
+      </c>
+      <c r="J9" s="28">
+        <f>D9+E9+F9+G9+H9</f>
+        <v/>
+      </c>
+      <c r="K9" s="27">
+        <f>-Rechner!$H$28*(A9&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L9" s="28">
+        <f>-(D9+E9+F9+G9+K9)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M9" s="29">
+        <f>J9+L9</f>
+        <v/>
+      </c>
+      <c r="N9" s="28">
+        <f>N8+M9</f>
+        <v/>
+      </c>
+      <c r="O9" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A9</f>
+        <v/>
+      </c>
+      <c r="P9" s="29">
+        <f>O9-I9</f>
         <v/>
       </c>
     </row>
@@ -1947,60 +2234,64 @@
       <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="25">
-        <f>H9</f>
-        <v/>
-      </c>
-      <c r="C10" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A10-1)</f>
-        <v/>
-      </c>
-      <c r="D10" s="24">
-        <f>-C10*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E10" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F10" s="24">
-        <f>-B10*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G10" s="25">
-        <f>-MIN(B10,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="25">
-        <f>B10+G10</f>
-        <v/>
-      </c>
-      <c r="I10" s="25">
-        <f>C10+D10+E10+F10+G10</f>
-        <v/>
-      </c>
-      <c r="J10" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K10" s="25">
-        <f>-(C10+D10+E10+F10+J10)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L10" s="26">
-        <f>I10+K10</f>
-        <v/>
-      </c>
-      <c r="M10" s="25">
-        <f>M9+L10</f>
-        <v/>
-      </c>
-      <c r="N10" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A10</f>
-        <v/>
-      </c>
-      <c r="O10" s="26">
-        <f>N10-H10</f>
+      <c r="B10" s="26">
+        <f>IF(A10&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C10" s="28">
+        <f>I9</f>
+        <v/>
+      </c>
+      <c r="D10" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A10-1)</f>
+        <v/>
+      </c>
+      <c r="E10" s="27">
+        <f>-D10*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F10" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A10-1)</f>
+        <v/>
+      </c>
+      <c r="G10" s="28">
+        <f>IF(C10&lt;=0,0,IF(I10&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C10-I10)),IF(B10=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B10/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C10)-C10))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="28">
+        <f>-(C10-I10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="28">
+        <f>IF(C10&lt;=0,0,IF(B10=0,MAX(0,C10-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C10*(1+B10/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B10/12)^12-1)/(B10/12)))))</f>
+        <v/>
+      </c>
+      <c r="J10" s="28">
+        <f>D10+E10+F10+G10+H10</f>
+        <v/>
+      </c>
+      <c r="K10" s="27">
+        <f>-Rechner!$H$28*(A10&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L10" s="28">
+        <f>-(D10+E10+F10+G10+K10)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M10" s="29">
+        <f>J10+L10</f>
+        <v/>
+      </c>
+      <c r="N10" s="28">
+        <f>N9+M10</f>
+        <v/>
+      </c>
+      <c r="O10" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A10</f>
+        <v/>
+      </c>
+      <c r="P10" s="29">
+        <f>O10-I10</f>
         <v/>
       </c>
     </row>
@@ -2008,60 +2299,64 @@
       <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="25">
-        <f>H10</f>
-        <v/>
-      </c>
-      <c r="C11" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A11-1)</f>
-        <v/>
-      </c>
-      <c r="D11" s="24">
-        <f>-C11*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E11" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F11" s="24">
-        <f>-B11*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G11" s="25">
-        <f>-MIN(B11,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="25">
-        <f>B11+G11</f>
-        <v/>
-      </c>
-      <c r="I11" s="25">
-        <f>C11+D11+E11+F11+G11</f>
-        <v/>
-      </c>
-      <c r="J11" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K11" s="25">
-        <f>-(C11+D11+E11+F11+J11)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L11" s="26">
-        <f>I11+K11</f>
-        <v/>
-      </c>
-      <c r="M11" s="25">
-        <f>M10+L11</f>
-        <v/>
-      </c>
-      <c r="N11" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A11</f>
-        <v/>
-      </c>
-      <c r="O11" s="26">
-        <f>N11-H11</f>
+      <c r="B11" s="26">
+        <f>IF(A11&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C11" s="28">
+        <f>I10</f>
+        <v/>
+      </c>
+      <c r="D11" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A11-1)</f>
+        <v/>
+      </c>
+      <c r="E11" s="27">
+        <f>-D11*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F11" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A11-1)</f>
+        <v/>
+      </c>
+      <c r="G11" s="28">
+        <f>IF(C11&lt;=0,0,IF(I11&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C11-I11)),IF(B11=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B11/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C11)-C11))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="28">
+        <f>-(C11-I11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="28">
+        <f>IF(C11&lt;=0,0,IF(B11=0,MAX(0,C11-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C11*(1+B11/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B11/12)^12-1)/(B11/12)))))</f>
+        <v/>
+      </c>
+      <c r="J11" s="28">
+        <f>D11+E11+F11+G11+H11</f>
+        <v/>
+      </c>
+      <c r="K11" s="27">
+        <f>-Rechner!$H$28*(A11&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L11" s="28">
+        <f>-(D11+E11+F11+G11+K11)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M11" s="29">
+        <f>J11+L11</f>
+        <v/>
+      </c>
+      <c r="N11" s="28">
+        <f>N10+M11</f>
+        <v/>
+      </c>
+      <c r="O11" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A11</f>
+        <v/>
+      </c>
+      <c r="P11" s="29">
+        <f>O11-I11</f>
         <v/>
       </c>
     </row>
@@ -2069,60 +2364,64 @@
       <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="25">
-        <f>H11</f>
-        <v/>
-      </c>
-      <c r="C12" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A12-1)</f>
-        <v/>
-      </c>
-      <c r="D12" s="24">
-        <f>-C12*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E12" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F12" s="24">
-        <f>-B12*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G12" s="25">
-        <f>-MIN(B12,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="25">
-        <f>B12+G12</f>
-        <v/>
-      </c>
-      <c r="I12" s="25">
-        <f>C12+D12+E12+F12+G12</f>
-        <v/>
-      </c>
-      <c r="J12" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K12" s="25">
-        <f>-(C12+D12+E12+F12+J12)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L12" s="26">
-        <f>I12+K12</f>
-        <v/>
-      </c>
-      <c r="M12" s="25">
-        <f>M11+L12</f>
-        <v/>
-      </c>
-      <c r="N12" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A12</f>
-        <v/>
-      </c>
-      <c r="O12" s="26">
-        <f>N12-H12</f>
+      <c r="B12" s="26">
+        <f>IF(A12&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C12" s="28">
+        <f>I11</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A12-1)</f>
+        <v/>
+      </c>
+      <c r="E12" s="27">
+        <f>-D12*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F12" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A12-1)</f>
+        <v/>
+      </c>
+      <c r="G12" s="28">
+        <f>IF(C12&lt;=0,0,IF(I12&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C12-I12)),IF(B12=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B12/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C12)-C12))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="28">
+        <f>-(C12-I12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="28">
+        <f>IF(C12&lt;=0,0,IF(B12=0,MAX(0,C12-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C12*(1+B12/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B12/12)^12-1)/(B12/12)))))</f>
+        <v/>
+      </c>
+      <c r="J12" s="28">
+        <f>D12+E12+F12+G12+H12</f>
+        <v/>
+      </c>
+      <c r="K12" s="27">
+        <f>-Rechner!$H$28*(A12&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L12" s="28">
+        <f>-(D12+E12+F12+G12+K12)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M12" s="29">
+        <f>J12+L12</f>
+        <v/>
+      </c>
+      <c r="N12" s="28">
+        <f>N11+M12</f>
+        <v/>
+      </c>
+      <c r="O12" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A12</f>
+        <v/>
+      </c>
+      <c r="P12" s="29">
+        <f>O12-I12</f>
         <v/>
       </c>
     </row>
@@ -2130,60 +2429,64 @@
       <c r="A13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="25">
-        <f>H12</f>
-        <v/>
-      </c>
-      <c r="C13" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A13-1)</f>
-        <v/>
-      </c>
-      <c r="D13" s="24">
-        <f>-C13*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E13" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F13" s="24">
-        <f>-B13*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G13" s="25">
-        <f>-MIN(B13,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="25">
-        <f>B13+G13</f>
-        <v/>
-      </c>
-      <c r="I13" s="25">
-        <f>C13+D13+E13+F13+G13</f>
-        <v/>
-      </c>
-      <c r="J13" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K13" s="25">
-        <f>-(C13+D13+E13+F13+J13)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L13" s="26">
-        <f>I13+K13</f>
-        <v/>
-      </c>
-      <c r="M13" s="25">
-        <f>M12+L13</f>
-        <v/>
-      </c>
-      <c r="N13" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A13</f>
-        <v/>
-      </c>
-      <c r="O13" s="26">
-        <f>N13-H13</f>
+      <c r="B13" s="26">
+        <f>IF(A13&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>I12</f>
+        <v/>
+      </c>
+      <c r="D13" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A13-1)</f>
+        <v/>
+      </c>
+      <c r="E13" s="27">
+        <f>-D13*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F13" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A13-1)</f>
+        <v/>
+      </c>
+      <c r="G13" s="28">
+        <f>IF(C13&lt;=0,0,IF(I13&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C13-I13)),IF(B13=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B13/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C13)-C13))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="28">
+        <f>-(C13-I13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="28">
+        <f>IF(C13&lt;=0,0,IF(B13=0,MAX(0,C13-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C13*(1+B13/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B13/12)^12-1)/(B13/12)))))</f>
+        <v/>
+      </c>
+      <c r="J13" s="28">
+        <f>D13+E13+F13+G13+H13</f>
+        <v/>
+      </c>
+      <c r="K13" s="27">
+        <f>-Rechner!$H$28*(A13&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L13" s="28">
+        <f>-(D13+E13+F13+G13+K13)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M13" s="29">
+        <f>J13+L13</f>
+        <v/>
+      </c>
+      <c r="N13" s="28">
+        <f>N12+M13</f>
+        <v/>
+      </c>
+      <c r="O13" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A13</f>
+        <v/>
+      </c>
+      <c r="P13" s="29">
+        <f>O13-I13</f>
         <v/>
       </c>
     </row>
@@ -2191,60 +2494,64 @@
       <c r="A14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="25">
-        <f>H13</f>
-        <v/>
-      </c>
-      <c r="C14" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A14-1)</f>
-        <v/>
-      </c>
-      <c r="D14" s="24">
-        <f>-C14*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E14" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F14" s="24">
-        <f>-B14*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G14" s="25">
-        <f>-MIN(B14,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="25">
-        <f>B14+G14</f>
-        <v/>
-      </c>
-      <c r="I14" s="25">
-        <f>C14+D14+E14+F14+G14</f>
-        <v/>
-      </c>
-      <c r="J14" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K14" s="25">
-        <f>-(C14+D14+E14+F14+J14)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L14" s="26">
-        <f>I14+K14</f>
-        <v/>
-      </c>
-      <c r="M14" s="25">
-        <f>M13+L14</f>
-        <v/>
-      </c>
-      <c r="N14" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A14</f>
-        <v/>
-      </c>
-      <c r="O14" s="26">
-        <f>N14-H14</f>
+      <c r="B14" s="26">
+        <f>IF(A14&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C14" s="28">
+        <f>I13</f>
+        <v/>
+      </c>
+      <c r="D14" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A14-1)</f>
+        <v/>
+      </c>
+      <c r="E14" s="27">
+        <f>-D14*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F14" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A14-1)</f>
+        <v/>
+      </c>
+      <c r="G14" s="28">
+        <f>IF(C14&lt;=0,0,IF(I14&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C14-I14)),IF(B14=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B14/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C14)-C14))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="28">
+        <f>-(C14-I14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="28">
+        <f>IF(C14&lt;=0,0,IF(B14=0,MAX(0,C14-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C14*(1+B14/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B14/12)^12-1)/(B14/12)))))</f>
+        <v/>
+      </c>
+      <c r="J14" s="28">
+        <f>D14+E14+F14+G14+H14</f>
+        <v/>
+      </c>
+      <c r="K14" s="27">
+        <f>-Rechner!$H$28*(A14&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L14" s="28">
+        <f>-(D14+E14+F14+G14+K14)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M14" s="29">
+        <f>J14+L14</f>
+        <v/>
+      </c>
+      <c r="N14" s="28">
+        <f>N13+M14</f>
+        <v/>
+      </c>
+      <c r="O14" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A14</f>
+        <v/>
+      </c>
+      <c r="P14" s="29">
+        <f>O14-I14</f>
         <v/>
       </c>
     </row>
@@ -2252,60 +2559,64 @@
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="25">
-        <f>H14</f>
-        <v/>
-      </c>
-      <c r="C15" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A15-1)</f>
-        <v/>
-      </c>
-      <c r="D15" s="24">
-        <f>-C15*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E15" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F15" s="24">
-        <f>-B15*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G15" s="25">
-        <f>-MIN(B15,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F15)</f>
-        <v/>
-      </c>
-      <c r="H15" s="25">
-        <f>B15+G15</f>
-        <v/>
-      </c>
-      <c r="I15" s="25">
-        <f>C15+D15+E15+F15+G15</f>
-        <v/>
-      </c>
-      <c r="J15" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K15" s="25">
-        <f>-(C15+D15+E15+F15+J15)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L15" s="26">
-        <f>I15+K15</f>
-        <v/>
-      </c>
-      <c r="M15" s="25">
-        <f>M14+L15</f>
-        <v/>
-      </c>
-      <c r="N15" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A15</f>
-        <v/>
-      </c>
-      <c r="O15" s="26">
-        <f>N15-H15</f>
+      <c r="B15" s="26">
+        <f>IF(A15&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C15" s="28">
+        <f>I14</f>
+        <v/>
+      </c>
+      <c r="D15" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A15-1)</f>
+        <v/>
+      </c>
+      <c r="E15" s="27">
+        <f>-D15*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F15" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A15-1)</f>
+        <v/>
+      </c>
+      <c r="G15" s="28">
+        <f>IF(C15&lt;=0,0,IF(I15&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C15-I15)),IF(B15=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B15/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C15)-C15))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="28">
+        <f>-(C15-I15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="28">
+        <f>IF(C15&lt;=0,0,IF(B15=0,MAX(0,C15-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C15*(1+B15/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B15/12)^12-1)/(B15/12)))))</f>
+        <v/>
+      </c>
+      <c r="J15" s="28">
+        <f>D15+E15+F15+G15+H15</f>
+        <v/>
+      </c>
+      <c r="K15" s="27">
+        <f>-Rechner!$H$28*(A15&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L15" s="28">
+        <f>-(D15+E15+F15+G15+K15)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M15" s="29">
+        <f>J15+L15</f>
+        <v/>
+      </c>
+      <c r="N15" s="28">
+        <f>N14+M15</f>
+        <v/>
+      </c>
+      <c r="O15" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A15</f>
+        <v/>
+      </c>
+      <c r="P15" s="29">
+        <f>O15-I15</f>
         <v/>
       </c>
     </row>
@@ -2313,60 +2624,64 @@
       <c r="A16" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="25">
-        <f>H15</f>
-        <v/>
-      </c>
-      <c r="C16" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A16-1)</f>
-        <v/>
-      </c>
-      <c r="D16" s="24">
-        <f>-C16*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E16" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F16" s="24">
-        <f>-B16*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G16" s="25">
-        <f>-MIN(B16,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F16)</f>
-        <v/>
-      </c>
-      <c r="H16" s="25">
-        <f>B16+G16</f>
-        <v/>
-      </c>
-      <c r="I16" s="25">
-        <f>C16+D16+E16+F16+G16</f>
-        <v/>
-      </c>
-      <c r="J16" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K16" s="25">
-        <f>-(C16+D16+E16+F16+J16)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L16" s="26">
-        <f>I16+K16</f>
-        <v/>
-      </c>
-      <c r="M16" s="25">
-        <f>M15+L16</f>
-        <v/>
-      </c>
-      <c r="N16" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A16</f>
-        <v/>
-      </c>
-      <c r="O16" s="26">
-        <f>N16-H16</f>
+      <c r="B16" s="26">
+        <f>IF(A16&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C16" s="28">
+        <f>I15</f>
+        <v/>
+      </c>
+      <c r="D16" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A16-1)</f>
+        <v/>
+      </c>
+      <c r="E16" s="27">
+        <f>-D16*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F16" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A16-1)</f>
+        <v/>
+      </c>
+      <c r="G16" s="28">
+        <f>IF(C16&lt;=0,0,IF(I16&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C16-I16)),IF(B16=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B16/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C16)-C16))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="28">
+        <f>-(C16-I16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="28">
+        <f>IF(C16&lt;=0,0,IF(B16=0,MAX(0,C16-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C16*(1+B16/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B16/12)^12-1)/(B16/12)))))</f>
+        <v/>
+      </c>
+      <c r="J16" s="28">
+        <f>D16+E16+F16+G16+H16</f>
+        <v/>
+      </c>
+      <c r="K16" s="27">
+        <f>-Rechner!$H$28*(A16&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L16" s="28">
+        <f>-(D16+E16+F16+G16+K16)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M16" s="29">
+        <f>J16+L16</f>
+        <v/>
+      </c>
+      <c r="N16" s="28">
+        <f>N15+M16</f>
+        <v/>
+      </c>
+      <c r="O16" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A16</f>
+        <v/>
+      </c>
+      <c r="P16" s="29">
+        <f>O16-I16</f>
         <v/>
       </c>
     </row>
@@ -2374,60 +2689,64 @@
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="25">
-        <f>H16</f>
-        <v/>
-      </c>
-      <c r="C17" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A17-1)</f>
-        <v/>
-      </c>
-      <c r="D17" s="24">
-        <f>-C17*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E17" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F17" s="24">
-        <f>-B17*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G17" s="25">
-        <f>-MIN(B17,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F17)</f>
-        <v/>
-      </c>
-      <c r="H17" s="25">
-        <f>B17+G17</f>
-        <v/>
-      </c>
-      <c r="I17" s="25">
-        <f>C17+D17+E17+F17+G17</f>
-        <v/>
-      </c>
-      <c r="J17" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K17" s="25">
-        <f>-(C17+D17+E17+F17+J17)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L17" s="26">
-        <f>I17+K17</f>
-        <v/>
-      </c>
-      <c r="M17" s="25">
-        <f>M16+L17</f>
-        <v/>
-      </c>
-      <c r="N17" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A17</f>
-        <v/>
-      </c>
-      <c r="O17" s="26">
-        <f>N17-H17</f>
+      <c r="B17" s="26">
+        <f>IF(A17&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C17" s="28">
+        <f>I16</f>
+        <v/>
+      </c>
+      <c r="D17" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A17-1)</f>
+        <v/>
+      </c>
+      <c r="E17" s="27">
+        <f>-D17*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F17" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A17-1)</f>
+        <v/>
+      </c>
+      <c r="G17" s="28">
+        <f>IF(C17&lt;=0,0,IF(I17&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C17-I17)),IF(B17=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B17/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C17)-C17))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="28">
+        <f>-(C17-I17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="28">
+        <f>IF(C17&lt;=0,0,IF(B17=0,MAX(0,C17-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C17*(1+B17/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B17/12)^12-1)/(B17/12)))))</f>
+        <v/>
+      </c>
+      <c r="J17" s="28">
+        <f>D17+E17+F17+G17+H17</f>
+        <v/>
+      </c>
+      <c r="K17" s="27">
+        <f>-Rechner!$H$28*(A17&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L17" s="28">
+        <f>-(D17+E17+F17+G17+K17)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M17" s="29">
+        <f>J17+L17</f>
+        <v/>
+      </c>
+      <c r="N17" s="28">
+        <f>N16+M17</f>
+        <v/>
+      </c>
+      <c r="O17" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A17</f>
+        <v/>
+      </c>
+      <c r="P17" s="29">
+        <f>O17-I17</f>
         <v/>
       </c>
     </row>
@@ -2435,60 +2754,64 @@
       <c r="A18" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="25">
-        <f>H17</f>
-        <v/>
-      </c>
-      <c r="C18" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A18-1)</f>
-        <v/>
-      </c>
-      <c r="D18" s="24">
-        <f>-C18*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E18" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F18" s="24">
-        <f>-B18*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G18" s="25">
-        <f>-MIN(B18,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F18)</f>
-        <v/>
-      </c>
-      <c r="H18" s="25">
-        <f>B18+G18</f>
-        <v/>
-      </c>
-      <c r="I18" s="25">
-        <f>C18+D18+E18+F18+G18</f>
-        <v/>
-      </c>
-      <c r="J18" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K18" s="25">
-        <f>-(C18+D18+E18+F18+J18)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L18" s="26">
-        <f>I18+K18</f>
-        <v/>
-      </c>
-      <c r="M18" s="25">
-        <f>M17+L18</f>
-        <v/>
-      </c>
-      <c r="N18" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A18</f>
-        <v/>
-      </c>
-      <c r="O18" s="26">
-        <f>N18-H18</f>
+      <c r="B18" s="26">
+        <f>IF(A18&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C18" s="28">
+        <f>I17</f>
+        <v/>
+      </c>
+      <c r="D18" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A18-1)</f>
+        <v/>
+      </c>
+      <c r="E18" s="27">
+        <f>-D18*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F18" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A18-1)</f>
+        <v/>
+      </c>
+      <c r="G18" s="28">
+        <f>IF(C18&lt;=0,0,IF(I18&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C18-I18)),IF(B18=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B18/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C18)-C18))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="28">
+        <f>-(C18-I18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="28">
+        <f>IF(C18&lt;=0,0,IF(B18=0,MAX(0,C18-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C18*(1+B18/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B18/12)^12-1)/(B18/12)))))</f>
+        <v/>
+      </c>
+      <c r="J18" s="28">
+        <f>D18+E18+F18+G18+H18</f>
+        <v/>
+      </c>
+      <c r="K18" s="27">
+        <f>-Rechner!$H$28*(A18&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L18" s="28">
+        <f>-(D18+E18+F18+G18+K18)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M18" s="29">
+        <f>J18+L18</f>
+        <v/>
+      </c>
+      <c r="N18" s="28">
+        <f>N17+M18</f>
+        <v/>
+      </c>
+      <c r="O18" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A18</f>
+        <v/>
+      </c>
+      <c r="P18" s="29">
+        <f>O18-I18</f>
         <v/>
       </c>
     </row>
@@ -2496,60 +2819,64 @@
       <c r="A19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="25">
-        <f>H18</f>
-        <v/>
-      </c>
-      <c r="C19" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A19-1)</f>
-        <v/>
-      </c>
-      <c r="D19" s="24">
-        <f>-C19*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E19" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F19" s="24">
-        <f>-B19*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G19" s="25">
-        <f>-MIN(B19,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F19)</f>
-        <v/>
-      </c>
-      <c r="H19" s="25">
-        <f>B19+G19</f>
-        <v/>
-      </c>
-      <c r="I19" s="25">
-        <f>C19+D19+E19+F19+G19</f>
-        <v/>
-      </c>
-      <c r="J19" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K19" s="25">
-        <f>-(C19+D19+E19+F19+J19)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L19" s="26">
-        <f>I19+K19</f>
-        <v/>
-      </c>
-      <c r="M19" s="25">
-        <f>M18+L19</f>
-        <v/>
-      </c>
-      <c r="N19" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A19</f>
-        <v/>
-      </c>
-      <c r="O19" s="26">
-        <f>N19-H19</f>
+      <c r="B19" s="26">
+        <f>IF(A19&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C19" s="28">
+        <f>I18</f>
+        <v/>
+      </c>
+      <c r="D19" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A19-1)</f>
+        <v/>
+      </c>
+      <c r="E19" s="27">
+        <f>-D19*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F19" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A19-1)</f>
+        <v/>
+      </c>
+      <c r="G19" s="28">
+        <f>IF(C19&lt;=0,0,IF(I19&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C19-I19)),IF(B19=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B19/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C19)-C19))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="28">
+        <f>-(C19-I19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="28">
+        <f>IF(C19&lt;=0,0,IF(B19=0,MAX(0,C19-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C19*(1+B19/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B19/12)^12-1)/(B19/12)))))</f>
+        <v/>
+      </c>
+      <c r="J19" s="28">
+        <f>D19+E19+F19+G19+H19</f>
+        <v/>
+      </c>
+      <c r="K19" s="27">
+        <f>-Rechner!$H$28*(A19&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L19" s="28">
+        <f>-(D19+E19+F19+G19+K19)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M19" s="29">
+        <f>J19+L19</f>
+        <v/>
+      </c>
+      <c r="N19" s="28">
+        <f>N18+M19</f>
+        <v/>
+      </c>
+      <c r="O19" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A19</f>
+        <v/>
+      </c>
+      <c r="P19" s="29">
+        <f>O19-I19</f>
         <v/>
       </c>
     </row>
@@ -2557,60 +2884,64 @@
       <c r="A20" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="25">
-        <f>H19</f>
-        <v/>
-      </c>
-      <c r="C20" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A20-1)</f>
-        <v/>
-      </c>
-      <c r="D20" s="24">
-        <f>-C20*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E20" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F20" s="24">
-        <f>-B20*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G20" s="25">
-        <f>-MIN(B20,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F20)</f>
-        <v/>
-      </c>
-      <c r="H20" s="25">
-        <f>B20+G20</f>
-        <v/>
-      </c>
-      <c r="I20" s="25">
-        <f>C20+D20+E20+F20+G20</f>
-        <v/>
-      </c>
-      <c r="J20" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K20" s="25">
-        <f>-(C20+D20+E20+F20+J20)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L20" s="26">
-        <f>I20+K20</f>
-        <v/>
-      </c>
-      <c r="M20" s="25">
-        <f>M19+L20</f>
-        <v/>
-      </c>
-      <c r="N20" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A20</f>
-        <v/>
-      </c>
-      <c r="O20" s="26">
-        <f>N20-H20</f>
+      <c r="B20" s="26">
+        <f>IF(A20&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C20" s="28">
+        <f>I19</f>
+        <v/>
+      </c>
+      <c r="D20" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A20-1)</f>
+        <v/>
+      </c>
+      <c r="E20" s="27">
+        <f>-D20*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F20" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A20-1)</f>
+        <v/>
+      </c>
+      <c r="G20" s="28">
+        <f>IF(C20&lt;=0,0,IF(I20&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C20-I20)),IF(B20=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B20/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C20)-C20))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="28">
+        <f>-(C20-I20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="28">
+        <f>IF(C20&lt;=0,0,IF(B20=0,MAX(0,C20-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C20*(1+B20/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B20/12)^12-1)/(B20/12)))))</f>
+        <v/>
+      </c>
+      <c r="J20" s="28">
+        <f>D20+E20+F20+G20+H20</f>
+        <v/>
+      </c>
+      <c r="K20" s="27">
+        <f>-Rechner!$H$28*(A20&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L20" s="28">
+        <f>-(D20+E20+F20+G20+K20)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M20" s="29">
+        <f>J20+L20</f>
+        <v/>
+      </c>
+      <c r="N20" s="28">
+        <f>N19+M20</f>
+        <v/>
+      </c>
+      <c r="O20" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A20</f>
+        <v/>
+      </c>
+      <c r="P20" s="29">
+        <f>O20-I20</f>
         <v/>
       </c>
     </row>
@@ -2618,60 +2949,64 @@
       <c r="A21" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="25">
-        <f>H20</f>
-        <v/>
-      </c>
-      <c r="C21" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A21-1)</f>
-        <v/>
-      </c>
-      <c r="D21" s="24">
-        <f>-C21*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E21" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F21" s="24">
-        <f>-B21*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G21" s="25">
-        <f>-MIN(B21,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F21)</f>
-        <v/>
-      </c>
-      <c r="H21" s="25">
-        <f>B21+G21</f>
-        <v/>
-      </c>
-      <c r="I21" s="25">
-        <f>C21+D21+E21+F21+G21</f>
-        <v/>
-      </c>
-      <c r="J21" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K21" s="25">
-        <f>-(C21+D21+E21+F21+J21)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L21" s="26">
-        <f>I21+K21</f>
-        <v/>
-      </c>
-      <c r="M21" s="25">
-        <f>M20+L21</f>
-        <v/>
-      </c>
-      <c r="N21" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A21</f>
-        <v/>
-      </c>
-      <c r="O21" s="26">
-        <f>N21-H21</f>
+      <c r="B21" s="26">
+        <f>IF(A21&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C21" s="28">
+        <f>I20</f>
+        <v/>
+      </c>
+      <c r="D21" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A21-1)</f>
+        <v/>
+      </c>
+      <c r="E21" s="27">
+        <f>-D21*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F21" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A21-1)</f>
+        <v/>
+      </c>
+      <c r="G21" s="28">
+        <f>IF(C21&lt;=0,0,IF(I21&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C21-I21)),IF(B21=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B21/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C21)-C21))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="28">
+        <f>-(C21-I21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="28">
+        <f>IF(C21&lt;=0,0,IF(B21=0,MAX(0,C21-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C21*(1+B21/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B21/12)^12-1)/(B21/12)))))</f>
+        <v/>
+      </c>
+      <c r="J21" s="28">
+        <f>D21+E21+F21+G21+H21</f>
+        <v/>
+      </c>
+      <c r="K21" s="27">
+        <f>-Rechner!$H$28*(A21&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L21" s="28">
+        <f>-(D21+E21+F21+G21+K21)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M21" s="29">
+        <f>J21+L21</f>
+        <v/>
+      </c>
+      <c r="N21" s="28">
+        <f>N20+M21</f>
+        <v/>
+      </c>
+      <c r="O21" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A21</f>
+        <v/>
+      </c>
+      <c r="P21" s="29">
+        <f>O21-I21</f>
         <v/>
       </c>
     </row>
@@ -2679,60 +3014,64 @@
       <c r="A22" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="25">
-        <f>H21</f>
-        <v/>
-      </c>
-      <c r="C22" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A22-1)</f>
-        <v/>
-      </c>
-      <c r="D22" s="24">
-        <f>-C22*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E22" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F22" s="24">
-        <f>-B22*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G22" s="25">
-        <f>-MIN(B22,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F22)</f>
-        <v/>
-      </c>
-      <c r="H22" s="25">
-        <f>B22+G22</f>
-        <v/>
-      </c>
-      <c r="I22" s="25">
-        <f>C22+D22+E22+F22+G22</f>
-        <v/>
-      </c>
-      <c r="J22" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K22" s="25">
-        <f>-(C22+D22+E22+F22+J22)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L22" s="26">
-        <f>I22+K22</f>
-        <v/>
-      </c>
-      <c r="M22" s="25">
-        <f>M21+L22</f>
-        <v/>
-      </c>
-      <c r="N22" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A22</f>
-        <v/>
-      </c>
-      <c r="O22" s="26">
-        <f>N22-H22</f>
+      <c r="B22" s="26">
+        <f>IF(A22&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="28">
+        <f>I21</f>
+        <v/>
+      </c>
+      <c r="D22" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A22-1)</f>
+        <v/>
+      </c>
+      <c r="E22" s="27">
+        <f>-D22*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F22" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A22-1)</f>
+        <v/>
+      </c>
+      <c r="G22" s="28">
+        <f>IF(C22&lt;=0,0,IF(I22&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C22-I22)),IF(B22=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B22/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C22)-C22))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="28">
+        <f>-(C22-I22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="28">
+        <f>IF(C22&lt;=0,0,IF(B22=0,MAX(0,C22-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C22*(1+B22/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B22/12)^12-1)/(B22/12)))))</f>
+        <v/>
+      </c>
+      <c r="J22" s="28">
+        <f>D22+E22+F22+G22+H22</f>
+        <v/>
+      </c>
+      <c r="K22" s="27">
+        <f>-Rechner!$H$28*(A22&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L22" s="28">
+        <f>-(D22+E22+F22+G22+K22)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M22" s="29">
+        <f>J22+L22</f>
+        <v/>
+      </c>
+      <c r="N22" s="28">
+        <f>N21+M22</f>
+        <v/>
+      </c>
+      <c r="O22" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A22</f>
+        <v/>
+      </c>
+      <c r="P22" s="29">
+        <f>O22-I22</f>
         <v/>
       </c>
     </row>
@@ -2740,60 +3079,64 @@
       <c r="A23" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="25">
-        <f>H22</f>
-        <v/>
-      </c>
-      <c r="C23" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A23-1)</f>
-        <v/>
-      </c>
-      <c r="D23" s="24">
-        <f>-C23*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E23" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F23" s="24">
-        <f>-B23*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G23" s="25">
-        <f>-MIN(B23,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F23)</f>
-        <v/>
-      </c>
-      <c r="H23" s="25">
-        <f>B23+G23</f>
-        <v/>
-      </c>
-      <c r="I23" s="25">
-        <f>C23+D23+E23+F23+G23</f>
-        <v/>
-      </c>
-      <c r="J23" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K23" s="25">
-        <f>-(C23+D23+E23+F23+J23)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L23" s="26">
-        <f>I23+K23</f>
-        <v/>
-      </c>
-      <c r="M23" s="25">
-        <f>M22+L23</f>
-        <v/>
-      </c>
-      <c r="N23" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A23</f>
-        <v/>
-      </c>
-      <c r="O23" s="26">
-        <f>N23-H23</f>
+      <c r="B23" s="26">
+        <f>IF(A23&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C23" s="28">
+        <f>I22</f>
+        <v/>
+      </c>
+      <c r="D23" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A23-1)</f>
+        <v/>
+      </c>
+      <c r="E23" s="27">
+        <f>-D23*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F23" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A23-1)</f>
+        <v/>
+      </c>
+      <c r="G23" s="28">
+        <f>IF(C23&lt;=0,0,IF(I23&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C23-I23)),IF(B23=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B23/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C23)-C23))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="28">
+        <f>-(C23-I23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="28">
+        <f>IF(C23&lt;=0,0,IF(B23=0,MAX(0,C23-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C23*(1+B23/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B23/12)^12-1)/(B23/12)))))</f>
+        <v/>
+      </c>
+      <c r="J23" s="28">
+        <f>D23+E23+F23+G23+H23</f>
+        <v/>
+      </c>
+      <c r="K23" s="27">
+        <f>-Rechner!$H$28*(A23&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L23" s="28">
+        <f>-(D23+E23+F23+G23+K23)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M23" s="29">
+        <f>J23+L23</f>
+        <v/>
+      </c>
+      <c r="N23" s="28">
+        <f>N22+M23</f>
+        <v/>
+      </c>
+      <c r="O23" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A23</f>
+        <v/>
+      </c>
+      <c r="P23" s="29">
+        <f>O23-I23</f>
         <v/>
       </c>
     </row>
@@ -2801,74 +3144,733 @@
       <c r="A24" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="25">
-        <f>H23</f>
-        <v/>
-      </c>
-      <c r="C24" s="24">
-        <f>Rechner!$H$7*12*(1+Rechner!$C$28)^(A24-1)</f>
-        <v/>
-      </c>
-      <c r="D24" s="24">
-        <f>-C24*Rechner!$C$23</f>
-        <v/>
-      </c>
-      <c r="E24" s="24">
-        <f>(Rechner!$H$15+Rechner!$H$16)*12</f>
-        <v/>
-      </c>
-      <c r="F24" s="24">
-        <f>-B24*Rechner!$C$18</f>
-        <v/>
-      </c>
-      <c r="G24" s="25">
-        <f>-MIN(B24,Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)+F24)</f>
-        <v/>
-      </c>
-      <c r="H24" s="25">
-        <f>B24+G24</f>
-        <v/>
-      </c>
-      <c r="I24" s="25">
-        <f>C24+D24+E24+F24+G24</f>
-        <v/>
-      </c>
-      <c r="J24" s="24">
-        <f>-Rechner!$H$27</f>
-        <v/>
-      </c>
-      <c r="K24" s="25">
-        <f>-(C24+D24+E24+F24+J24)*Rechner!$C$26</f>
-        <v/>
-      </c>
-      <c r="L24" s="26">
-        <f>I24+K24</f>
-        <v/>
-      </c>
-      <c r="M24" s="25">
-        <f>M23+L24</f>
-        <v/>
-      </c>
-      <c r="N24" s="24">
-        <f>Rechner!$C$6*(1+Rechner!$C$29)^A24</f>
-        <v/>
-      </c>
-      <c r="O24" s="26">
-        <f>N24-H24</f>
+      <c r="B24" s="26">
+        <f>IF(A24&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C24" s="28">
+        <f>I23</f>
+        <v/>
+      </c>
+      <c r="D24" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A24-1)</f>
+        <v/>
+      </c>
+      <c r="E24" s="27">
+        <f>-D24*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F24" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A24-1)</f>
+        <v/>
+      </c>
+      <c r="G24" s="28">
+        <f>IF(C24&lt;=0,0,IF(I24&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C24-I24)),IF(B24=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B24/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C24)-C24))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="28">
+        <f>-(C24-I24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="28">
+        <f>IF(C24&lt;=0,0,IF(B24=0,MAX(0,C24-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C24*(1+B24/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B24/12)^12-1)/(B24/12)))))</f>
+        <v/>
+      </c>
+      <c r="J24" s="28">
+        <f>D24+E24+F24+G24+H24</f>
+        <v/>
+      </c>
+      <c r="K24" s="27">
+        <f>-Rechner!$H$28*(A24&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L24" s="28">
+        <f>-(D24+E24+F24+G24+K24)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M24" s="29">
+        <f>J24+L24</f>
+        <v/>
+      </c>
+      <c r="N24" s="28">
+        <f>N23+M24</f>
+        <v/>
+      </c>
+      <c r="O24" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A24</f>
+        <v/>
+      </c>
+      <c r="P24" s="29">
+        <f>O24-I24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="26">
+        <f>IF(A25&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C25" s="28">
+        <f>I24</f>
+        <v/>
+      </c>
+      <c r="D25" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A25-1)</f>
+        <v/>
+      </c>
+      <c r="E25" s="27">
+        <f>-D25*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F25" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A25-1)</f>
+        <v/>
+      </c>
+      <c r="G25" s="28">
+        <f>IF(C25&lt;=0,0,IF(I25&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C25-I25)),IF(B25=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B25/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C25)-C25))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="28">
+        <f>-(C25-I25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="28">
+        <f>IF(C25&lt;=0,0,IF(B25=0,MAX(0,C25-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C25*(1+B25/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B25/12)^12-1)/(B25/12)))))</f>
+        <v/>
+      </c>
+      <c r="J25" s="28">
+        <f>D25+E25+F25+G25+H25</f>
+        <v/>
+      </c>
+      <c r="K25" s="27">
+        <f>-Rechner!$H$28*(A25&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L25" s="28">
+        <f>-(D25+E25+F25+G25+K25)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M25" s="29">
+        <f>J25+L25</f>
+        <v/>
+      </c>
+      <c r="N25" s="28">
+        <f>N24+M25</f>
+        <v/>
+      </c>
+      <c r="O25" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A25</f>
+        <v/>
+      </c>
+      <c r="P25" s="29">
+        <f>O25-I25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Grüne Schrift = Bezug auf das Blatt Rechner. Jahr 1 entspricht dem Monatswert im Rechner × 12.</t>
+      <c r="A26" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="26">
+        <f>IF(A26&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C26" s="28">
+        <f>I25</f>
+        <v/>
+      </c>
+      <c r="D26" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A26-1)</f>
+        <v/>
+      </c>
+      <c r="E26" s="27">
+        <f>-D26*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F26" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A26-1)</f>
+        <v/>
+      </c>
+      <c r="G26" s="28">
+        <f>IF(C26&lt;=0,0,IF(I26&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C26-I26)),IF(B26=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B26/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C26)-C26))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="28">
+        <f>-(C26-I26)</f>
+        <v/>
+      </c>
+      <c r="I26" s="28">
+        <f>IF(C26&lt;=0,0,IF(B26=0,MAX(0,C26-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C26*(1+B26/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B26/12)^12-1)/(B26/12)))))</f>
+        <v/>
+      </c>
+      <c r="J26" s="28">
+        <f>D26+E26+F26+G26+H26</f>
+        <v/>
+      </c>
+      <c r="K26" s="27">
+        <f>-Rechner!$H$28*(A26&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L26" s="28">
+        <f>-(D26+E26+F26+G26+K26)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M26" s="29">
+        <f>J26+L26</f>
+        <v/>
+      </c>
+      <c r="N26" s="28">
+        <f>N25+M26</f>
+        <v/>
+      </c>
+      <c r="O26" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A26</f>
+        <v/>
+      </c>
+      <c r="P26" s="29">
+        <f>O26-I26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="26">
+        <f>IF(A27&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C27" s="28">
+        <f>I26</f>
+        <v/>
+      </c>
+      <c r="D27" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A27-1)</f>
+        <v/>
+      </c>
+      <c r="E27" s="27">
+        <f>-D27*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F27" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A27-1)</f>
+        <v/>
+      </c>
+      <c r="G27" s="28">
+        <f>IF(C27&lt;=0,0,IF(I27&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C27-I27)),IF(B27=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B27/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C27)-C27))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="28">
+        <f>-(C27-I27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="28">
+        <f>IF(C27&lt;=0,0,IF(B27=0,MAX(0,C27-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C27*(1+B27/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B27/12)^12-1)/(B27/12)))))</f>
+        <v/>
+      </c>
+      <c r="J27" s="28">
+        <f>D27+E27+F27+G27+H27</f>
+        <v/>
+      </c>
+      <c r="K27" s="27">
+        <f>-Rechner!$H$28*(A27&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L27" s="28">
+        <f>-(D27+E27+F27+G27+K27)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M27" s="29">
+        <f>J27+L27</f>
+        <v/>
+      </c>
+      <c r="N27" s="28">
+        <f>N26+M27</f>
+        <v/>
+      </c>
+      <c r="O27" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A27</f>
+        <v/>
+      </c>
+      <c r="P27" s="29">
+        <f>O27-I27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="26">
+        <f>IF(A28&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C28" s="28">
+        <f>I27</f>
+        <v/>
+      </c>
+      <c r="D28" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A28-1)</f>
+        <v/>
+      </c>
+      <c r="E28" s="27">
+        <f>-D28*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F28" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A28-1)</f>
+        <v/>
+      </c>
+      <c r="G28" s="28">
+        <f>IF(C28&lt;=0,0,IF(I28&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C28-I28)),IF(B28=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B28/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C28)-C28))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="28">
+        <f>-(C28-I28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="28">
+        <f>IF(C28&lt;=0,0,IF(B28=0,MAX(0,C28-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C28*(1+B28/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B28/12)^12-1)/(B28/12)))))</f>
+        <v/>
+      </c>
+      <c r="J28" s="28">
+        <f>D28+E28+F28+G28+H28</f>
+        <v/>
+      </c>
+      <c r="K28" s="27">
+        <f>-Rechner!$H$28*(A28&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L28" s="28">
+        <f>-(D28+E28+F28+G28+K28)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M28" s="29">
+        <f>J28+L28</f>
+        <v/>
+      </c>
+      <c r="N28" s="28">
+        <f>N27+M28</f>
+        <v/>
+      </c>
+      <c r="O28" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A28</f>
+        <v/>
+      </c>
+      <c r="P28" s="29">
+        <f>O28-I28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="26">
+        <f>IF(A29&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C29" s="28">
+        <f>I28</f>
+        <v/>
+      </c>
+      <c r="D29" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A29-1)</f>
+        <v/>
+      </c>
+      <c r="E29" s="27">
+        <f>-D29*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F29" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A29-1)</f>
+        <v/>
+      </c>
+      <c r="G29" s="28">
+        <f>IF(C29&lt;=0,0,IF(I29&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C29-I29)),IF(B29=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B29/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C29)-C29))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="28">
+        <f>-(C29-I29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="28">
+        <f>IF(C29&lt;=0,0,IF(B29=0,MAX(0,C29-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C29*(1+B29/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B29/12)^12-1)/(B29/12)))))</f>
+        <v/>
+      </c>
+      <c r="J29" s="28">
+        <f>D29+E29+F29+G29+H29</f>
+        <v/>
+      </c>
+      <c r="K29" s="27">
+        <f>-Rechner!$H$28*(A29&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L29" s="28">
+        <f>-(D29+E29+F29+G29+K29)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M29" s="29">
+        <f>J29+L29</f>
+        <v/>
+      </c>
+      <c r="N29" s="28">
+        <f>N28+M29</f>
+        <v/>
+      </c>
+      <c r="O29" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A29</f>
+        <v/>
+      </c>
+      <c r="P29" s="29">
+        <f>O29-I29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="26">
+        <f>IF(A30&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C30" s="28">
+        <f>I29</f>
+        <v/>
+      </c>
+      <c r="D30" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A30-1)</f>
+        <v/>
+      </c>
+      <c r="E30" s="27">
+        <f>-D30*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F30" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A30-1)</f>
+        <v/>
+      </c>
+      <c r="G30" s="28">
+        <f>IF(C30&lt;=0,0,IF(I30&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C30-I30)),IF(B30=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B30/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C30)-C30))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="28">
+        <f>-(C30-I30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="28">
+        <f>IF(C30&lt;=0,0,IF(B30=0,MAX(0,C30-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C30*(1+B30/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B30/12)^12-1)/(B30/12)))))</f>
+        <v/>
+      </c>
+      <c r="J30" s="28">
+        <f>D30+E30+F30+G30+H30</f>
+        <v/>
+      </c>
+      <c r="K30" s="27">
+        <f>-Rechner!$H$28*(A30&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L30" s="28">
+        <f>-(D30+E30+F30+G30+K30)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M30" s="29">
+        <f>J30+L30</f>
+        <v/>
+      </c>
+      <c r="N30" s="28">
+        <f>N29+M30</f>
+        <v/>
+      </c>
+      <c r="O30" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A30</f>
+        <v/>
+      </c>
+      <c r="P30" s="29">
+        <f>O30-I30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="26">
+        <f>IF(A31&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C31" s="28">
+        <f>I30</f>
+        <v/>
+      </c>
+      <c r="D31" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A31-1)</f>
+        <v/>
+      </c>
+      <c r="E31" s="27">
+        <f>-D31*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F31" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A31-1)</f>
+        <v/>
+      </c>
+      <c r="G31" s="28">
+        <f>IF(C31&lt;=0,0,IF(I31&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C31-I31)),IF(B31=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B31/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C31)-C31))))</f>
+        <v/>
+      </c>
+      <c r="H31" s="28">
+        <f>-(C31-I31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="28">
+        <f>IF(C31&lt;=0,0,IF(B31=0,MAX(0,C31-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C31*(1+B31/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B31/12)^12-1)/(B31/12)))))</f>
+        <v/>
+      </c>
+      <c r="J31" s="28">
+        <f>D31+E31+F31+G31+H31</f>
+        <v/>
+      </c>
+      <c r="K31" s="27">
+        <f>-Rechner!$H$28*(A31&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L31" s="28">
+        <f>-(D31+E31+F31+G31+K31)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M31" s="29">
+        <f>J31+L31</f>
+        <v/>
+      </c>
+      <c r="N31" s="28">
+        <f>N30+M31</f>
+        <v/>
+      </c>
+      <c r="O31" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A31</f>
+        <v/>
+      </c>
+      <c r="P31" s="29">
+        <f>O31-I31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="26">
+        <f>IF(A32&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C32" s="28">
+        <f>I31</f>
+        <v/>
+      </c>
+      <c r="D32" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A32-1)</f>
+        <v/>
+      </c>
+      <c r="E32" s="27">
+        <f>-D32*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F32" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A32-1)</f>
+        <v/>
+      </c>
+      <c r="G32" s="28">
+        <f>IF(C32&lt;=0,0,IF(I32&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C32-I32)),IF(B32=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B32/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C32)-C32))))</f>
+        <v/>
+      </c>
+      <c r="H32" s="28">
+        <f>-(C32-I32)</f>
+        <v/>
+      </c>
+      <c r="I32" s="28">
+        <f>IF(C32&lt;=0,0,IF(B32=0,MAX(0,C32-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C32*(1+B32/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B32/12)^12-1)/(B32/12)))))</f>
+        <v/>
+      </c>
+      <c r="J32" s="28">
+        <f>D32+E32+F32+G32+H32</f>
+        <v/>
+      </c>
+      <c r="K32" s="27">
+        <f>-Rechner!$H$28*(A32&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L32" s="28">
+        <f>-(D32+E32+F32+G32+K32)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M32" s="29">
+        <f>J32+L32</f>
+        <v/>
+      </c>
+      <c r="N32" s="28">
+        <f>N31+M32</f>
+        <v/>
+      </c>
+      <c r="O32" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A32</f>
+        <v/>
+      </c>
+      <c r="P32" s="29">
+        <f>O32-I32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="26">
+        <f>IF(A33&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C33" s="28">
+        <f>I32</f>
+        <v/>
+      </c>
+      <c r="D33" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A33-1)</f>
+        <v/>
+      </c>
+      <c r="E33" s="27">
+        <f>-D33*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F33" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A33-1)</f>
+        <v/>
+      </c>
+      <c r="G33" s="28">
+        <f>IF(C33&lt;=0,0,IF(I33&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C33-I33)),IF(B33=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B33/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C33)-C33))))</f>
+        <v/>
+      </c>
+      <c r="H33" s="28">
+        <f>-(C33-I33)</f>
+        <v/>
+      </c>
+      <c r="I33" s="28">
+        <f>IF(C33&lt;=0,0,IF(B33=0,MAX(0,C33-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C33*(1+B33/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B33/12)^12-1)/(B33/12)))))</f>
+        <v/>
+      </c>
+      <c r="J33" s="28">
+        <f>D33+E33+F33+G33+H33</f>
+        <v/>
+      </c>
+      <c r="K33" s="27">
+        <f>-Rechner!$H$28*(A33&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L33" s="28">
+        <f>-(D33+E33+F33+G33+K33)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M33" s="29">
+        <f>J33+L33</f>
+        <v/>
+      </c>
+      <c r="N33" s="28">
+        <f>N32+M33</f>
+        <v/>
+      </c>
+      <c r="O33" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A33</f>
+        <v/>
+      </c>
+      <c r="P33" s="29">
+        <f>O33-I33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="26">
+        <f>IF(A34&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C34" s="28">
+        <f>I33</f>
+        <v/>
+      </c>
+      <c r="D34" s="27">
+        <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A34-1)</f>
+        <v/>
+      </c>
+      <c r="E34" s="27">
+        <f>-D34*Rechner!$C$25</f>
+        <v/>
+      </c>
+      <c r="F34" s="27">
+        <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A34-1)</f>
+        <v/>
+      </c>
+      <c r="G34" s="28">
+        <f>IF(C34&lt;=0,0,IF(I34&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C34-I34)),IF(B34=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B34/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C34)-C34))))</f>
+        <v/>
+      </c>
+      <c r="H34" s="28">
+        <f>-(C34-I34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="28">
+        <f>IF(C34&lt;=0,0,IF(B34=0,MAX(0,C34-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C34*(1+B34/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B34/12)^12-1)/(B34/12)))))</f>
+        <v/>
+      </c>
+      <c r="J34" s="28">
+        <f>D34+E34+F34+G34+H34</f>
+        <v/>
+      </c>
+      <c r="K34" s="27">
+        <f>-Rechner!$H$28*(A34&lt;=1/Rechner!$C$27)</f>
+        <v/>
+      </c>
+      <c r="L34" s="28">
+        <f>-(D34+E34+F34+G34+K34)*Rechner!$C$28</f>
+        <v/>
+      </c>
+      <c r="M34" s="29">
+        <f>J34+L34</f>
+        <v/>
+      </c>
+      <c r="N34" s="28">
+        <f>N33+M34</f>
+        <v/>
+      </c>
+      <c r="O34" s="27">
+        <f>Rechner!$C$6*(1+Rechner!$C$32)^A34</f>
+        <v/>
+      </c>
+      <c r="P34" s="29">
+        <f>O34-I34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Beige hinterlegter Zinssatz = nach Ende der Zinsbindung (Anschlusszins). Jahr 1 entspricht dem Monatswert im Rechner × 12.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="L5:M24">
+  <conditionalFormatting sqref="M5:N34">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="2">
       <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B34">
+    <cfRule type="expression" priority="2" dxfId="3">
+      <formula>A5&gt;Rechner!$C$20</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2889,7 +3891,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Fernere Lebenserwartung (Frauen, gerundet)</t>
         </is>
@@ -2915,66 +3917,66 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="n">
+      <c r="A4" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="B4" s="28" t="n">
+      <c r="B4" s="31" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n">
+      <c r="A5" s="30" t="n">
         <v>65</v>
       </c>
-      <c r="B5" s="28" t="n">
+      <c r="B5" s="31" t="n">
         <v>20.9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="31" t="n">
         <v>16.9</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="30" t="n">
         <v>75</v>
       </c>
-      <c r="B7" s="28" t="n">
+      <c r="B7" s="31" t="n">
         <v>13.2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="B8" s="28" t="n">
+      <c r="B8" s="31" t="n">
         <v>9.800000000000001</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="30" t="n">
         <v>85</v>
       </c>
-      <c r="B9" s="28" t="n">
+      <c r="B9" s="31" t="n">
         <v>6.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="30" t="n">
         <v>90</v>
       </c>
-      <c r="B10" s="28" t="n">
+      <c r="B10" s="31" t="n">
         <v>4.6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="n">
+      <c r="A11" s="30" t="n">
         <v>95</v>
       </c>
-      <c r="B11" s="28" t="n">
+      <c r="B11" s="31" t="n">
         <v>3</v>
       </c>
     </row>

--- a/immobilien/Hauskauf_Rechner_Damme.xlsx
+++ b/immobilien/Hauskauf_Rechner_Damme.xlsx
@@ -7,25 +7,32 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rechner" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prognose" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lebenserwartung" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rechner" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prognose" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lebenserwartung" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagrammdaten" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard'!$A$1:$S$72</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="#,##0 €;-#,##0 €;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00 €;-#,##0.00 €;&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%;-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00%;-0.00%;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.000000"/>
+    <numFmt numFmtId="170" formatCode="+0%;-0%;&quot;aktuell&quot;"/>
+    <numFmt numFmtId="171" formatCode="0&quot; Jahre&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,8 +87,32 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001C2430"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005B6470"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001C2430"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="005B6470"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -103,6 +134,11 @@
         <fgColor rgb="00F5E6E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F4F1"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -121,10 +157,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="171" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -135,7 +190,6 @@
     <xf numFmtId="1" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -176,11 +230,31 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="002E7A4B"/>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="00B3362F"/>
+        <sz val="18"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -282,6 +356,1296 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1150" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1150" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Cashflow nach Steuern pro Jahr</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Prognose'!M4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="3B5B7A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="3B5B7A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Prognose'!$A$5:$A$34</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Prognose'!$M$5:$M$34</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="50"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Jahr</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="5B6470"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="5B6470"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E6E6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0 €" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="5B6470"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="5B6470"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1150" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1150" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Vermögensaufbau: Immobilienwert und Restschuld</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Prognose'!O4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
+              <a:solidFill>
+                <a:srgbClr val="1F8A6A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Prognose'!$A$5:$A$34</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Prognose'!$O$5:$O$34</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Prognose'!I4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
+              <a:solidFill>
+                <a:srgbClr val="A4452C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Prognose'!$A$5:$A$34</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Prognose'!$I$5:$I$34</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Jahr</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="5B6470"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="5B6470"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E6E6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0 €" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="5B6470"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="5B6470"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1C2430"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900">
+            <a:solidFill>
+              <a:srgbClr val="1C2430"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1150" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1150" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Kreditrate pro Jahr: Zinsen und Tilgung</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Diagrammdaten'!I3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="A4452C"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="A4452C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Diagrammdaten'!$H$4:$H$33</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagrammdaten'!$I$4:$I$33</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Diagrammdaten'!J3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1F8A6A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F8A6A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Diagrammdaten'!$H$4:$H$33</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagrammdaten'!$J$4:$J$33</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="50"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Jahr</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="5B6470"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="5B6470"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E6E6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0 €" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="5B6470"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="5B6470"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1C2430"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900">
+            <a:solidFill>
+              <a:srgbClr val="1C2430"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1150" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1150" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Kumulierter Cashflow nach Steuern</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Prognose'!N4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
+              <a:solidFill>
+                <a:srgbClr val="3B5B7A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Prognose'!$A$5:$A$34</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Prognose'!$N$5:$N$34</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Jahr</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="5B6470"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="5B6470"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E6E6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0 €" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="5B6470"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="5B6470"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1150" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1150" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Monatliche Rechnung (1. Jahr)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Diagrammdaten'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="3B5B7A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="3B5B7A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Diagrammdaten'!$A$4:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagrammdaten'!$B$4:$B$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <numFmt formatCode="#,##0 €"/>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="800">
+                  <a:solidFill>
+                    <a:srgbClr val="1C2430"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+              <a:endParaRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
+        <gapWidth val="40"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="5B6470"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="5B6470"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E6E6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0 €" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="5B6470"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="5B6470"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1150" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1150" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Cashflow / Monat je nach Kaufpreis</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Diagrammdaten'!E3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="A4452C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="A4452C"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Diagrammdaten'!$D$4:$D$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagrammdaten'!$E$4:$E$12</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Kaufpreis</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0 €" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="5B6470"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="5B6470"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E6E6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0 €" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="5B6470"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="5B6470"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1150" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1150" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1C2430"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Verkäufer: Guthaben nach Mietzahlungen</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Diagrammdaten'!K3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
+              <a:solidFill>
+                <a:srgbClr val="1F8A6A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Diagrammdaten'!$H$4:$H$33</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagrammdaten'!$K$4:$K$33</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Jahre nach dem Verkauf</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="5B6470"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="5B6470"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E6E6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0 €" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="5B6470"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="5B6470"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -315,6 +1679,165 @@
     </comment>
   </commentList>
 </comments>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="2736000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="2736000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="2736000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="2736000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="2736000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="2736000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="6" name="Chart 6"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>55</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="2736000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="7" name="Chart 7"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -604,6 +2127,273 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:S64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="11.5" customWidth="1" min="2" max="2"/>
+    <col width="11.5" customWidth="1" min="3" max="3"/>
+    <col width="11.5" customWidth="1" min="4" max="4"/>
+    <col width="11.5" customWidth="1" min="5" max="5"/>
+    <col width="11.5" customWidth="1" min="6" max="6"/>
+    <col width="11.5" customWidth="1" min="7" max="7"/>
+    <col width="11.5" customWidth="1" min="8" max="8"/>
+    <col width="11.5" customWidth="1" min="9" max="9"/>
+    <col width="11.5" customWidth="1" min="10" max="10"/>
+    <col width="11.5" customWidth="1" min="11" max="11"/>
+    <col width="11.5" customWidth="1" min="12" max="12"/>
+    <col width="11.5" customWidth="1" min="13" max="13"/>
+    <col width="11.5" customWidth="1" min="14" max="14"/>
+    <col width="11.5" customWidth="1" min="15" max="15"/>
+    <col width="11.5" customWidth="1" min="16" max="16"/>
+    <col width="11.5" customWidth="1" min="17" max="17"/>
+    <col width="11.5" customWidth="1" min="18" max="18"/>
+    <col width="11.5" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dashboard – Hauskauf mit Rückmietung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alle Werte kommen aus dem Blatt Rechner. Dort die gelben Felder ändern – Kennzahlen und Diagramme passen sich an.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Cashflow / Monat</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Kaufpreisfaktor</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Bruttomietrendite</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Max. Kaufpreis</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Vermögenszuwachs 10 J.</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Geld Verkäufer reicht</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="n"/>
+      <c r="S4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="5">
+        <f>Rechner!$H$19</f>
+        <v/>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="6">
+        <f>Rechner!$H$21</f>
+        <v/>
+      </c>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="7">
+        <f>Rechner!$H$22</f>
+        <v/>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="5">
+        <f>Rechner!$H$32</f>
+        <v/>
+      </c>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="5">
+        <f>Prognose!P14+Prognose!N14-Rechner!$C$17</f>
+        <v/>
+      </c>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="8">
+        <f>Rechner!$H$39</f>
+        <v/>
+      </c>
+      <c r="R5" s="4" t="n"/>
+      <c r="S5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>nach Steuern, 1. Jahr</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="9">
+        <f>Rechner!I21</f>
+        <v/>
+      </c>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Jahreskaltmiete ÷ Kaufpreis</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>für Cashflow ≥ 0 €</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>Eigenkapital im Objekt + Cashflow − Einsatz</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="9">
+        <f>"Lebenserwartung ca. "&amp;TEXT(Rechner!$H$38,"0")&amp;" J."</f>
+        <v/>
+      </c>
+      <c r="R6" s="4" t="n"/>
+      <c r="S6" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="K57" s="10" t="inlineStr">
+        <is>
+          <t>So liest du die Diagramme</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>• Cashflow pro Jahr: Balken unter 0 = du legst monatlich Geld dazu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>• Vermögensaufbau: Der Abstand zwischen grüner und roter Linie ist dein Eigenkapital im Haus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>• Zinsen und Tilgung: Der rote Zinsanteil sinkt, der grüne Tilgungsanteil wächst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>• Kumulierter Cashflow: Summe aller Zuschüsse/Überschüsse seit dem Kauf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>• Kaufpreis: Wo die Linie 0 € kreuzt, trägt sich das Haus selbst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>• Verkäufer: So entwickelt sich sein Geld, wenn er davon die Miete zahlt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>• Beispielzahlen – keine echten Objektdaten.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H6:J6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$B$5&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$B$5&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N5">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>$N$5&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>$N$5&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B1:I54"/>
@@ -621,7 +2411,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Hauskauf-Rechner Damme – Verkauf mit Rückmietung</t>
         </is>
@@ -635,29 +2425,29 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Objekt</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>Ergebnis</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Kaufpreis</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="15" t="n">
         <v>260000</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -670,23 +2460,23 @@
           <t>Verhandelter Kaufpreis</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>Kaltmiete Verkäufer / Monat</t>
         </is>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="16">
         <f>$C$7*$C$8</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Wohnfläche Verkäufer</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="17" t="n">
         <v>125</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -699,23 +2489,23 @@
           <t>Fläche der Wohnung, in der der Verkäufer bleibt</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>Kaltmiete gesamt / Monat</t>
         </is>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="16">
         <f>$H$6+$C$11</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Kaltmiete Verkäufer</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="18" t="n">
         <v>7.5</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -728,23 +2518,23 @@
           <t>Damme 2026: ca. 7,15–9,90 €/m² (Mietspiegel-Portale)</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>Kaufnebenkosten</t>
         </is>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="16">
         <f>$C$6*($C$13+$C$14+$C$15)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Sofort-Investitionen</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="15" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -757,23 +2547,23 @@
           <t>z. B. Heizung, GEG-Pflichten nach Eigentümerwechsel</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>Gesamtinvestition</t>
         </is>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="16">
         <f>$C$6+$H$8+$C$9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Einliegerwohnung Fläche</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="17" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -786,23 +2576,23 @@
           <t>0, wenn keine vorhanden</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>Darlehen</t>
         </is>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="16">
         <f>MAX(0,$H$9-$C$17)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Einliegerwohnung Miete</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="15" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -815,40 +2605,40 @@
           <t>Kaltmiete der zweiten Einheit</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>Monatliche Rechnung (Durchschnitt 1. Jahr)</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="13" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Kaufnebenkosten</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>Kaltmiete</t>
         </is>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="16">
         <f>$H$7</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Grunderwerbsteuer</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="19" t="n">
         <v>0.05</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -861,23 +2651,23 @@
           <t>Niedersachsen: 5 %</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>Mietausfall-Reserve</t>
         </is>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="16">
         <f>-$H$7*$C$25</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Notar &amp; Grundbuch</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="19" t="n">
         <v>0.02</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -890,23 +2680,23 @@
           <t>üblich ca. 1,5–2 %</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>Kreditrate (Zins + Tilgung)</t>
         </is>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="16">
         <f>-$H$10*($C$18+$C$19)/12</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Makler</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="19" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -919,42 +2709,42 @@
           <t>bei Direktkauf 0 %</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>Instandhaltungsrücklage</t>
         </is>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="16">
         <f>-($C$7+$C$10)*$C$23/12</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Finanzierung</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>Nicht umlagefähige Kosten</t>
         </is>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="16">
         <f>-$C$24</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>Eigenkapital</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="15" t="n">
         <v>55000</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -967,23 +2757,23 @@
           <t>eingesetztes Eigenkapital</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Cashflow vor Steuern</t>
         </is>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="20">
         <f>SUM($H$12:$H$16)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Sollzins</t>
         </is>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="21" t="n">
         <v>0.038</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -996,23 +2786,23 @@
           <t>Annahme – aktuelles Bankangebot eintragen</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>Steuereffekt (+ = Ersparnis)</t>
         </is>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="16">
         <f>-$H$30/12</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Anfängliche Tilgung</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="21" t="n">
         <v>0.02</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1025,27 +2815,27 @@
           <t>Rate = Darlehen × (Zins + Tilgung) ÷ 12</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>CASHFLOW NACH STEUERN / MONAT</t>
         </is>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="23">
         <f>$H$17+$H$18</f>
         <v/>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="22">
         <f>IF($H$19&gt;=0,"Trägt sich selbst",IF($H$19&gt;=-150,"Leichter Zuschuss nötig","Deutlicher Zuschuss nötig"))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Zinsbindung</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="17" t="n">
         <v>10</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1058,21 +2848,21 @@
           <t>danach gilt der Anschlusszins (Rate bleibt gleich)</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>Kennzahlen</t>
         </is>
       </c>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
+      <c r="H20" s="13" t="n"/>
+      <c r="I20" s="13" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Anschlusszins</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="21" t="n">
         <v>0.045</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1085,46 +2875,46 @@
           <t>Annahme für die Zeit nach der Zinsbindung</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>Kaufpreisfaktor</t>
         </is>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="24">
         <f>IFERROR($C$6/($H$7*12),0)</f>
         <v/>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="10">
         <f>IF($H$21&lt;=18,"günstig",IF($H$21&lt;=22,"mittel","teuer"))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Laufende Kosten &amp; Steuer</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>Bruttomietrendite</t>
         </is>
       </c>
-      <c r="H22" s="17">
+      <c r="H22" s="25">
         <f>IFERROR($H$7*12/$C$6,0)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Instandhaltung</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="18" t="n">
         <v>14</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1137,23 +2927,23 @@
           <t>Altbau: ca. 12–18 €</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>Nettomietrendite</t>
         </is>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="25">
         <f>IFERROR(($H$12+$H$13+$H$15+$H$16)*12/$H$9,0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>Nicht umlagefähige Kosten</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C24" s="15" t="n">
         <v>20</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1166,23 +2956,23 @@
           <t>Verwaltung, Bankgebühren</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>Eigenkapitalrendite (CF + Tilgung)</t>
         </is>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="26">
         <f>IFERROR(($H$19*12+$H$27)/$C$17,0)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Mietausfall-Reserve</t>
         </is>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="19" t="n">
         <v>0.02</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1191,21 +2981,21 @@
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>Steuer 1. Jahr (vereinfacht)</t>
         </is>
       </c>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Gebäudeanteil</t>
         </is>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C26" s="19" t="n">
         <v>0.7</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1218,23 +3008,23 @@
           <t>Rest = Grundstück (nicht abschreibbar)</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>Zinsen Jahr 1 (monatsgenau)</t>
         </is>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="27">
         <f>-Prognose!$G$5</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>AfA-Satz</t>
         </is>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="19" t="n">
         <v>0.02</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1247,23 +3037,23 @@
           <t>Baujahr 1925–2022: 2 %, vor 1925: 2,5 %</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>Tilgung Jahr 1 (Vermögensaufbau)</t>
         </is>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="27">
         <f>-Prognose!$H$5</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Persönlicher Steuersatz</t>
         </is>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C28" s="19" t="n">
         <v>0.3</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1276,42 +3066,42 @@
           <t>Grenzsteuersatz</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>AfA pro Jahr</t>
         </is>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="16">
         <f>(($C$6+$H$8)*$C$26+$C$9)*$C$27</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Entwicklung (für Blatt Prognose)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>Steuerliches Ergebnis</t>
         </is>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="16">
         <f>($H$12+$H$13+$H$15+$H$16)*12-$H$26-$H$28</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>Mietsteigerung</t>
         </is>
       </c>
-      <c r="C30" s="10" t="n">
+      <c r="C30" s="19" t="n">
         <v>0.015</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1324,23 +3114,23 @@
           <t>Annahme; gesetzlich begrenzt (Mietspiegel, Kappungsgrenze)</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>Steuer (+ zahlen / − Erstattung)</t>
         </is>
       </c>
-      <c r="H30" s="7">
+      <c r="H30" s="16">
         <f>$H$29*$C$28</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>Kostensteigerung</t>
         </is>
       </c>
-      <c r="C31" s="10" t="n">
+      <c r="C31" s="19" t="n">
         <v>0.02</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1353,21 +3143,21 @@
           <t>Annahme für Instandhaltung und sonstige Kosten</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>Maximaler Kaufpreis</t>
         </is>
       </c>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
+      <c r="H31" s="13" t="n"/>
+      <c r="I31" s="13" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>Wertsteigerung</t>
         </is>
       </c>
-      <c r="C32" s="10" t="n">
+      <c r="C32" s="19" t="n">
         <v>0.015</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1380,43 +3170,43 @@
           <t>Annahme</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>Max. Kaufpreis für Cashflow ≥ 0</t>
         </is>
       </c>
-      <c r="H32" s="20">
+      <c r="H32" s="28">
         <f>IF($H$10&lt;=0,"–",MAX(0,$C$6+$H$19/((1+$C$13+$C$14+$C$15)/12*(($C$18+$C$19)-$C$28*($H$26/$H$10+$C$26*$C$27)))))</f>
         <v/>
       </c>
-      <c r="I32" s="21" t="n"/>
+      <c r="I32" s="29" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Verkäufer</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="13" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>Nötiger Abschlag</t>
         </is>
       </c>
-      <c r="H33" s="7">
+      <c r="H33" s="16">
         <f>IF(ISNUMBER($H$32),MAX(0,$C$6-$H$32),0)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>Alter (jüngste Person)</t>
         </is>
       </c>
-      <c r="C34" s="8" t="n">
+      <c r="C34" s="17" t="n">
         <v>75</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1429,27 +3219,27 @@
           <t>Tabelle reicht von 60 bis 95 Jahre</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>Nötiger Abschlag in %</t>
         </is>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="26">
         <f>IFERROR($H$33/$C$6,0)</f>
         <v/>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="10">
         <f>IF($H$10&lt;=0,"kein Darlehen – Formel nicht nötig",IF($H$33=0,"Preis passt","so viel Abschlag bräuchtest du"))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>Zins auf sein Kapital</t>
         </is>
       </c>
-      <c r="C35" s="10" t="n">
+      <c r="C35" s="19" t="n">
         <v>0.025</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1462,124 +3252,124 @@
           <t>Tagesgeld/Anleihen, Annahme</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>Sicht des Verkäufers</t>
         </is>
       </c>
-      <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="n"/>
+      <c r="H35" s="13" t="n"/>
+      <c r="I35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>Erlös für den Verkäufer</t>
         </is>
       </c>
-      <c r="H36" s="7">
+      <c r="H36" s="16">
         <f>$C$6</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>Seine Miete pro Jahr</t>
         </is>
       </c>
-      <c r="H37" s="7">
+      <c r="H37" s="16">
         <f>$H$6*12</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>Lebenserwartung (Jahre, ca.)</t>
         </is>
       </c>
-      <c r="H38" s="16">
+      <c r="H38" s="24">
         <f>INDEX(Lebenserwartung!$B$4:$B$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1))+(INDEX(Lebenserwartung!$B$4:$B$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)+1)-INDEX(Lebenserwartung!$B$4:$B$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)))*(MIN(MAX($C$34,60),95)-INDEX(Lebenserwartung!$A$4:$A$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)))/(INDEX(Lebenserwartung!$A$4:$A$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)+1)-INDEX(Lebenserwartung!$A$4:$A$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>So lange reicht das Geld (Jahre)</t>
         </is>
       </c>
-      <c r="H39" s="16">
+      <c r="H39" s="24">
         <f>IF($H$37&lt;=0,"unbegrenzt",IF($C$35=0,$C$6/$H$37,IF($H$37&lt;=$C$6*$C$35,"unbegrenzt",NPER($C$35,-$H$37,$C$6))))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>Rest nach Lebenserwartung</t>
         </is>
       </c>
-      <c r="H40" s="7">
+      <c r="H40" s="16">
         <f>MAX(0,IF($C$35=0,$C$6-$H$37*$H$38,FV($C$35,$H$38,$H$37,-$C$6)))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>Bewertung</t>
         </is>
       </c>
-      <c r="H41" s="22">
+      <c r="H41" s="30">
         <f>IF($H$39="unbegrenzt","Geld reicht sicher",IF($H$39&gt;$H$38,"Geld reicht sicher","Achtung: Geld reicht voraussichtlich nicht"))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>Kontrolle</t>
         </is>
       </c>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
+      <c r="H43" s="13" t="n"/>
+      <c r="I43" s="13" t="n"/>
     </row>
     <row r="44">
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>Prognose Jahr 1 = Monatswert × 12</t>
         </is>
       </c>
-      <c r="H44" s="23">
+      <c r="H44" s="31">
         <f>IF(ABS(Prognose!$M$5-$H$19*12)&lt;1,"OK","Abweichung prüfen")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="14" t="inlineStr">
         <is>
           <t>Restschuld nie negativ</t>
         </is>
       </c>
-      <c r="H45" s="23">
+      <c r="H45" s="31">
         <f>IF(MIN(Prognose!$I$5:$I$34)&gt;=-0.01,"OK","Abweichung prüfen")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>Tilgung Jahr 1 + Zinsen = 12 Raten</t>
         </is>
       </c>
-      <c r="H46" s="23">
+      <c r="H46" s="31">
         <f>IF($H$10=0,"OK",IF(ABS($H$26+$H$27+$H$14*12)&lt;1,"OK","Abweichung prüfen"))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>Hinweise:</t>
         </is>
@@ -1622,56 +3412,56 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H19:I19">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="2">
       <formula>$H$19&gt;=0</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="3">
       <formula>AND($H$19&lt;0,$H$19&gt;=-150)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="4">
       <formula>$H$19&lt;-150</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="expression" priority="4" dxfId="0">
+    <cfRule type="expression" priority="4" dxfId="2">
       <formula>$H$21&lt;=18</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" dxfId="1">
+    <cfRule type="expression" priority="5" dxfId="3">
       <formula>AND($H$21&gt;18,$H$21&lt;=22)</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="2">
+    <cfRule type="expression" priority="6" dxfId="4">
       <formula>$H$21&gt;22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="expression" priority="7" dxfId="2">
+    <cfRule type="expression" priority="7" dxfId="4">
       <formula>LEFT($H$41,7)="Achtung"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="0">
+    <cfRule type="expression" priority="8" dxfId="2">
       <formula>LEFT($H$41,7)&lt;&gt;"Achtung"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H44">
-    <cfRule type="expression" priority="9" dxfId="0">
+    <cfRule type="expression" priority="9" dxfId="2">
       <formula>$H$44="OK"</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="2">
+    <cfRule type="expression" priority="10" dxfId="4">
       <formula>$H$44&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45">
-    <cfRule type="expression" priority="11" dxfId="0">
+    <cfRule type="expression" priority="11" dxfId="2">
       <formula>$H$45="OK"</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" dxfId="2">
+    <cfRule type="expression" priority="12" dxfId="4">
       <formula>$H$45&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H46">
-    <cfRule type="expression" priority="13" dxfId="0">
+    <cfRule type="expression" priority="13" dxfId="2">
       <formula>$H$46="OK"</formula>
     </cfRule>
-    <cfRule type="expression" priority="14" dxfId="2">
+    <cfRule type="expression" priority="14" dxfId="4">
       <formula>$H$46&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1782,7 +3572,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1810,7 +3600,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>Prognose über 30 Jahre (Werte pro Jahr)</t>
         </is>
@@ -1824,2033 +3614,2033 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>Jahr</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>Zinssatz</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>Restschuld Anfang</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>Kaltmiete</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>Mietausfall</t>
         </is>
       </c>
-      <c r="F4" s="25" t="inlineStr">
+      <c r="F4" s="33" t="inlineStr">
         <is>
           <t>Instandh. + Kosten</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="33" t="inlineStr">
         <is>
           <t>Zinsen</t>
         </is>
       </c>
-      <c r="H4" s="25" t="inlineStr">
+      <c r="H4" s="33" t="inlineStr">
         <is>
           <t>Tilgung</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="33" t="inlineStr">
         <is>
           <t>Restschuld Ende</t>
         </is>
       </c>
-      <c r="J4" s="25" t="inlineStr">
+      <c r="J4" s="33" t="inlineStr">
         <is>
           <t>Cashflow vor Steuern</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="33" t="inlineStr">
         <is>
           <t>AfA</t>
         </is>
       </c>
-      <c r="L4" s="25" t="inlineStr">
+      <c r="L4" s="33" t="inlineStr">
         <is>
           <t>Steuereffekt</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="33" t="inlineStr">
         <is>
           <t>Cashflow nach Steuern</t>
         </is>
       </c>
-      <c r="N4" s="25" t="inlineStr">
+      <c r="N4" s="33" t="inlineStr">
         <is>
           <t>Kumulierter Cashflow</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="33" t="inlineStr">
         <is>
           <t>Immobilienwert</t>
         </is>
       </c>
-      <c r="P4" s="25" t="inlineStr">
+      <c r="P4" s="33" t="inlineStr">
         <is>
           <t>Eigenkapital im Objekt</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="34">
         <f>IF(A5&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="35">
         <f>Rechner!$H$10</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A5-1)</f>
         <v/>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="35">
         <f>-D5*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A5-1)</f>
         <v/>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="36">
         <f>IF(C5&lt;=0,0,IF(I5&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C5-I5)),IF(B5=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B5/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C5)-C5))))</f>
         <v/>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="36">
         <f>-(C5-I5)</f>
         <v/>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="36">
         <f>IF(C5&lt;=0,0,IF(B5=0,MAX(0,C5-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C5*(1+B5/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B5/12)^12-1)/(B5/12)))))</f>
         <v/>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="36">
         <f>D5+E5+F5+G5+H5</f>
         <v/>
       </c>
-      <c r="K5" s="27">
+      <c r="K5" s="35">
         <f>-Rechner!$H$28*(A5&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L5" s="28">
+      <c r="L5" s="36">
         <f>-(D5+E5+F5+G5+K5)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="37">
         <f>J5+L5</f>
         <v/>
       </c>
-      <c r="N5" s="28">
+      <c r="N5" s="36">
         <f>M5</f>
         <v/>
       </c>
-      <c r="O5" s="27">
+      <c r="O5" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A5</f>
         <v/>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="37">
         <f>O5-I5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="34">
         <f>IF(A6&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="36">
         <f>I5</f>
         <v/>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A6-1)</f>
         <v/>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="35">
         <f>-D6*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A6-1)</f>
         <v/>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="36">
         <f>IF(C6&lt;=0,0,IF(I6&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C6-I6)),IF(B6=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B6/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C6)-C6))))</f>
         <v/>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="36">
         <f>-(C6-I6)</f>
         <v/>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="36">
         <f>IF(C6&lt;=0,0,IF(B6=0,MAX(0,C6-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C6*(1+B6/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B6/12)^12-1)/(B6/12)))))</f>
         <v/>
       </c>
-      <c r="J6" s="28">
+      <c r="J6" s="36">
         <f>D6+E6+F6+G6+H6</f>
         <v/>
       </c>
-      <c r="K6" s="27">
+      <c r="K6" s="35">
         <f>-Rechner!$H$28*(A6&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="36">
         <f>-(D6+E6+F6+G6+K6)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M6" s="29">
+      <c r="M6" s="37">
         <f>J6+L6</f>
         <v/>
       </c>
-      <c r="N6" s="28">
+      <c r="N6" s="36">
         <f>N5+M6</f>
         <v/>
       </c>
-      <c r="O6" s="27">
+      <c r="O6" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A6</f>
         <v/>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="37">
         <f>O6-I6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="34">
         <f>IF(A7&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="36">
         <f>I6</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A7-1)</f>
         <v/>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="35">
         <f>-D7*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A7-1)</f>
         <v/>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="36">
         <f>IF(C7&lt;=0,0,IF(I7&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C7-I7)),IF(B7=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B7/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C7)-C7))))</f>
         <v/>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="36">
         <f>-(C7-I7)</f>
         <v/>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="36">
         <f>IF(C7&lt;=0,0,IF(B7=0,MAX(0,C7-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C7*(1+B7/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B7/12)^12-1)/(B7/12)))))</f>
         <v/>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="36">
         <f>D7+E7+F7+G7+H7</f>
         <v/>
       </c>
-      <c r="K7" s="27">
+      <c r="K7" s="35">
         <f>-Rechner!$H$28*(A7&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="36">
         <f>-(D7+E7+F7+G7+K7)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M7" s="29">
+      <c r="M7" s="37">
         <f>J7+L7</f>
         <v/>
       </c>
-      <c r="N7" s="28">
+      <c r="N7" s="36">
         <f>N6+M7</f>
         <v/>
       </c>
-      <c r="O7" s="27">
+      <c r="O7" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A7</f>
         <v/>
       </c>
-      <c r="P7" s="29">
+      <c r="P7" s="37">
         <f>O7-I7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="34">
         <f>IF(A8&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="36">
         <f>I7</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A8-1)</f>
         <v/>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="35">
         <f>-D8*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A8-1)</f>
         <v/>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="36">
         <f>IF(C8&lt;=0,0,IF(I8&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C8-I8)),IF(B8=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B8/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C8)-C8))))</f>
         <v/>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="36">
         <f>-(C8-I8)</f>
         <v/>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="36">
         <f>IF(C8&lt;=0,0,IF(B8=0,MAX(0,C8-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C8*(1+B8/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B8/12)^12-1)/(B8/12)))))</f>
         <v/>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="36">
         <f>D8+E8+F8+G8+H8</f>
         <v/>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="35">
         <f>-Rechner!$H$28*(A8&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="36">
         <f>-(D8+E8+F8+G8+K8)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M8" s="29">
+      <c r="M8" s="37">
         <f>J8+L8</f>
         <v/>
       </c>
-      <c r="N8" s="28">
+      <c r="N8" s="36">
         <f>N7+M8</f>
         <v/>
       </c>
-      <c r="O8" s="27">
+      <c r="O8" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A8</f>
         <v/>
       </c>
-      <c r="P8" s="29">
+      <c r="P8" s="37">
         <f>O8-I8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="34">
         <f>IF(A9&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="36">
         <f>I8</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A9-1)</f>
         <v/>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="35">
         <f>-D9*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A9-1)</f>
         <v/>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="36">
         <f>IF(C9&lt;=0,0,IF(I9&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C9-I9)),IF(B9=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B9/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C9)-C9))))</f>
         <v/>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="36">
         <f>-(C9-I9)</f>
         <v/>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="36">
         <f>IF(C9&lt;=0,0,IF(B9=0,MAX(0,C9-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C9*(1+B9/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B9/12)^12-1)/(B9/12)))))</f>
         <v/>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="36">
         <f>D9+E9+F9+G9+H9</f>
         <v/>
       </c>
-      <c r="K9" s="27">
+      <c r="K9" s="35">
         <f>-Rechner!$H$28*(A9&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="36">
         <f>-(D9+E9+F9+G9+K9)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M9" s="29">
+      <c r="M9" s="37">
         <f>J9+L9</f>
         <v/>
       </c>
-      <c r="N9" s="28">
+      <c r="N9" s="36">
         <f>N8+M9</f>
         <v/>
       </c>
-      <c r="O9" s="27">
+      <c r="O9" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A9</f>
         <v/>
       </c>
-      <c r="P9" s="29">
+      <c r="P9" s="37">
         <f>O9-I9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="34">
         <f>IF(A10&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="36">
         <f>I9</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A10-1)</f>
         <v/>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="35">
         <f>-D10*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A10-1)</f>
         <v/>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="36">
         <f>IF(C10&lt;=0,0,IF(I10&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C10-I10)),IF(B10=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B10/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C10)-C10))))</f>
         <v/>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="36">
         <f>-(C10-I10)</f>
         <v/>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="36">
         <f>IF(C10&lt;=0,0,IF(B10=0,MAX(0,C10-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C10*(1+B10/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B10/12)^12-1)/(B10/12)))))</f>
         <v/>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="36">
         <f>D10+E10+F10+G10+H10</f>
         <v/>
       </c>
-      <c r="K10" s="27">
+      <c r="K10" s="35">
         <f>-Rechner!$H$28*(A10&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="36">
         <f>-(D10+E10+F10+G10+K10)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M10" s="29">
+      <c r="M10" s="37">
         <f>J10+L10</f>
         <v/>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="36">
         <f>N9+M10</f>
         <v/>
       </c>
-      <c r="O10" s="27">
+      <c r="O10" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A10</f>
         <v/>
       </c>
-      <c r="P10" s="29">
+      <c r="P10" s="37">
         <f>O10-I10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="34">
         <f>IF(A11&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="36">
         <f>I10</f>
         <v/>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A11-1)</f>
         <v/>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="35">
         <f>-D11*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A11-1)</f>
         <v/>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="36">
         <f>IF(C11&lt;=0,0,IF(I11&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C11-I11)),IF(B11=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B11/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C11)-C11))))</f>
         <v/>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="36">
         <f>-(C11-I11)</f>
         <v/>
       </c>
-      <c r="I11" s="28">
+      <c r="I11" s="36">
         <f>IF(C11&lt;=0,0,IF(B11=0,MAX(0,C11-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C11*(1+B11/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B11/12)^12-1)/(B11/12)))))</f>
         <v/>
       </c>
-      <c r="J11" s="28">
+      <c r="J11" s="36">
         <f>D11+E11+F11+G11+H11</f>
         <v/>
       </c>
-      <c r="K11" s="27">
+      <c r="K11" s="35">
         <f>-Rechner!$H$28*(A11&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="36">
         <f>-(D11+E11+F11+G11+K11)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M11" s="29">
+      <c r="M11" s="37">
         <f>J11+L11</f>
         <v/>
       </c>
-      <c r="N11" s="28">
+      <c r="N11" s="36">
         <f>N10+M11</f>
         <v/>
       </c>
-      <c r="O11" s="27">
+      <c r="O11" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A11</f>
         <v/>
       </c>
-      <c r="P11" s="29">
+      <c r="P11" s="37">
         <f>O11-I11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="34">
         <f>IF(A12&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="36">
         <f>I11</f>
         <v/>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A12-1)</f>
         <v/>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="35">
         <f>-D12*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A12-1)</f>
         <v/>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="36">
         <f>IF(C12&lt;=0,0,IF(I12&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C12-I12)),IF(B12=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B12/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C12)-C12))))</f>
         <v/>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="36">
         <f>-(C12-I12)</f>
         <v/>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="36">
         <f>IF(C12&lt;=0,0,IF(B12=0,MAX(0,C12-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C12*(1+B12/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B12/12)^12-1)/(B12/12)))))</f>
         <v/>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="36">
         <f>D12+E12+F12+G12+H12</f>
         <v/>
       </c>
-      <c r="K12" s="27">
+      <c r="K12" s="35">
         <f>-Rechner!$H$28*(A12&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="36">
         <f>-(D12+E12+F12+G12+K12)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M12" s="29">
+      <c r="M12" s="37">
         <f>J12+L12</f>
         <v/>
       </c>
-      <c r="N12" s="28">
+      <c r="N12" s="36">
         <f>N11+M12</f>
         <v/>
       </c>
-      <c r="O12" s="27">
+      <c r="O12" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A12</f>
         <v/>
       </c>
-      <c r="P12" s="29">
+      <c r="P12" s="37">
         <f>O12-I12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="34">
         <f>IF(A13&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="36">
         <f>I12</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A13-1)</f>
         <v/>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="35">
         <f>-D13*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A13-1)</f>
         <v/>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="36">
         <f>IF(C13&lt;=0,0,IF(I13&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C13-I13)),IF(B13=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B13/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C13)-C13))))</f>
         <v/>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="36">
         <f>-(C13-I13)</f>
         <v/>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="36">
         <f>IF(C13&lt;=0,0,IF(B13=0,MAX(0,C13-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C13*(1+B13/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B13/12)^12-1)/(B13/12)))))</f>
         <v/>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="36">
         <f>D13+E13+F13+G13+H13</f>
         <v/>
       </c>
-      <c r="K13" s="27">
+      <c r="K13" s="35">
         <f>-Rechner!$H$28*(A13&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="36">
         <f>-(D13+E13+F13+G13+K13)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M13" s="29">
+      <c r="M13" s="37">
         <f>J13+L13</f>
         <v/>
       </c>
-      <c r="N13" s="28">
+      <c r="N13" s="36">
         <f>N12+M13</f>
         <v/>
       </c>
-      <c r="O13" s="27">
+      <c r="O13" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A13</f>
         <v/>
       </c>
-      <c r="P13" s="29">
+      <c r="P13" s="37">
         <f>O13-I13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="34">
         <f>IF(A14&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="36">
         <f>I13</f>
         <v/>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A14-1)</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="35">
         <f>-D14*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A14-1)</f>
         <v/>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="36">
         <f>IF(C14&lt;=0,0,IF(I14&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C14-I14)),IF(B14=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B14/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C14)-C14))))</f>
         <v/>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="36">
         <f>-(C14-I14)</f>
         <v/>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="36">
         <f>IF(C14&lt;=0,0,IF(B14=0,MAX(0,C14-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C14*(1+B14/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B14/12)^12-1)/(B14/12)))))</f>
         <v/>
       </c>
-      <c r="J14" s="28">
+      <c r="J14" s="36">
         <f>D14+E14+F14+G14+H14</f>
         <v/>
       </c>
-      <c r="K14" s="27">
+      <c r="K14" s="35">
         <f>-Rechner!$H$28*(A14&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="36">
         <f>-(D14+E14+F14+G14+K14)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M14" s="29">
+      <c r="M14" s="37">
         <f>J14+L14</f>
         <v/>
       </c>
-      <c r="N14" s="28">
+      <c r="N14" s="36">
         <f>N13+M14</f>
         <v/>
       </c>
-      <c r="O14" s="27">
+      <c r="O14" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A14</f>
         <v/>
       </c>
-      <c r="P14" s="29">
+      <c r="P14" s="37">
         <f>O14-I14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="34">
         <f>IF(A15&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="36">
         <f>I14</f>
         <v/>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A15-1)</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="35">
         <f>-D15*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A15-1)</f>
         <v/>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="36">
         <f>IF(C15&lt;=0,0,IF(I15&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C15-I15)),IF(B15=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B15/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C15)-C15))))</f>
         <v/>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="36">
         <f>-(C15-I15)</f>
         <v/>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="36">
         <f>IF(C15&lt;=0,0,IF(B15=0,MAX(0,C15-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C15*(1+B15/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B15/12)^12-1)/(B15/12)))))</f>
         <v/>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="36">
         <f>D15+E15+F15+G15+H15</f>
         <v/>
       </c>
-      <c r="K15" s="27">
+      <c r="K15" s="35">
         <f>-Rechner!$H$28*(A15&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="36">
         <f>-(D15+E15+F15+G15+K15)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M15" s="29">
+      <c r="M15" s="37">
         <f>J15+L15</f>
         <v/>
       </c>
-      <c r="N15" s="28">
+      <c r="N15" s="36">
         <f>N14+M15</f>
         <v/>
       </c>
-      <c r="O15" s="27">
+      <c r="O15" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A15</f>
         <v/>
       </c>
-      <c r="P15" s="29">
+      <c r="P15" s="37">
         <f>O15-I15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="34">
         <f>IF(A16&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="36">
         <f>I15</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A16-1)</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="35">
         <f>-D16*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A16-1)</f>
         <v/>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="36">
         <f>IF(C16&lt;=0,0,IF(I16&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C16-I16)),IF(B16=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B16/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C16)-C16))))</f>
         <v/>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="36">
         <f>-(C16-I16)</f>
         <v/>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="36">
         <f>IF(C16&lt;=0,0,IF(B16=0,MAX(0,C16-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C16*(1+B16/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B16/12)^12-1)/(B16/12)))))</f>
         <v/>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="36">
         <f>D16+E16+F16+G16+H16</f>
         <v/>
       </c>
-      <c r="K16" s="27">
+      <c r="K16" s="35">
         <f>-Rechner!$H$28*(A16&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="36">
         <f>-(D16+E16+F16+G16+K16)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M16" s="29">
+      <c r="M16" s="37">
         <f>J16+L16</f>
         <v/>
       </c>
-      <c r="N16" s="28">
+      <c r="N16" s="36">
         <f>N15+M16</f>
         <v/>
       </c>
-      <c r="O16" s="27">
+      <c r="O16" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A16</f>
         <v/>
       </c>
-      <c r="P16" s="29">
+      <c r="P16" s="37">
         <f>O16-I16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="34">
         <f>IF(A17&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="36">
         <f>I16</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A17-1)</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="35">
         <f>-D17*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A17-1)</f>
         <v/>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="36">
         <f>IF(C17&lt;=0,0,IF(I17&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C17-I17)),IF(B17=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B17/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C17)-C17))))</f>
         <v/>
       </c>
-      <c r="H17" s="28">
+      <c r="H17" s="36">
         <f>-(C17-I17)</f>
         <v/>
       </c>
-      <c r="I17" s="28">
+      <c r="I17" s="36">
         <f>IF(C17&lt;=0,0,IF(B17=0,MAX(0,C17-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C17*(1+B17/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B17/12)^12-1)/(B17/12)))))</f>
         <v/>
       </c>
-      <c r="J17" s="28">
+      <c r="J17" s="36">
         <f>D17+E17+F17+G17+H17</f>
         <v/>
       </c>
-      <c r="K17" s="27">
+      <c r="K17" s="35">
         <f>-Rechner!$H$28*(A17&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L17" s="28">
+      <c r="L17" s="36">
         <f>-(D17+E17+F17+G17+K17)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M17" s="29">
+      <c r="M17" s="37">
         <f>J17+L17</f>
         <v/>
       </c>
-      <c r="N17" s="28">
+      <c r="N17" s="36">
         <f>N16+M17</f>
         <v/>
       </c>
-      <c r="O17" s="27">
+      <c r="O17" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A17</f>
         <v/>
       </c>
-      <c r="P17" s="29">
+      <c r="P17" s="37">
         <f>O17-I17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="34">
         <f>IF(A18&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="36">
         <f>I17</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A18-1)</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="35">
         <f>-D18*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A18-1)</f>
         <v/>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="36">
         <f>IF(C18&lt;=0,0,IF(I18&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C18-I18)),IF(B18=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B18/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C18)-C18))))</f>
         <v/>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="36">
         <f>-(C18-I18)</f>
         <v/>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="36">
         <f>IF(C18&lt;=0,0,IF(B18=0,MAX(0,C18-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C18*(1+B18/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B18/12)^12-1)/(B18/12)))))</f>
         <v/>
       </c>
-      <c r="J18" s="28">
+      <c r="J18" s="36">
         <f>D18+E18+F18+G18+H18</f>
         <v/>
       </c>
-      <c r="K18" s="27">
+      <c r="K18" s="35">
         <f>-Rechner!$H$28*(A18&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L18" s="28">
+      <c r="L18" s="36">
         <f>-(D18+E18+F18+G18+K18)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M18" s="29">
+      <c r="M18" s="37">
         <f>J18+L18</f>
         <v/>
       </c>
-      <c r="N18" s="28">
+      <c r="N18" s="36">
         <f>N17+M18</f>
         <v/>
       </c>
-      <c r="O18" s="27">
+      <c r="O18" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A18</f>
         <v/>
       </c>
-      <c r="P18" s="29">
+      <c r="P18" s="37">
         <f>O18-I18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="34">
         <f>IF(A19&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="36">
         <f>I18</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A19-1)</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="35">
         <f>-D19*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A19-1)</f>
         <v/>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="36">
         <f>IF(C19&lt;=0,0,IF(I19&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C19-I19)),IF(B19=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B19/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C19)-C19))))</f>
         <v/>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="36">
         <f>-(C19-I19)</f>
         <v/>
       </c>
-      <c r="I19" s="28">
+      <c r="I19" s="36">
         <f>IF(C19&lt;=0,0,IF(B19=0,MAX(0,C19-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C19*(1+B19/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B19/12)^12-1)/(B19/12)))))</f>
         <v/>
       </c>
-      <c r="J19" s="28">
+      <c r="J19" s="36">
         <f>D19+E19+F19+G19+H19</f>
         <v/>
       </c>
-      <c r="K19" s="27">
+      <c r="K19" s="35">
         <f>-Rechner!$H$28*(A19&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L19" s="28">
+      <c r="L19" s="36">
         <f>-(D19+E19+F19+G19+K19)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M19" s="29">
+      <c r="M19" s="37">
         <f>J19+L19</f>
         <v/>
       </c>
-      <c r="N19" s="28">
+      <c r="N19" s="36">
         <f>N18+M19</f>
         <v/>
       </c>
-      <c r="O19" s="27">
+      <c r="O19" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A19</f>
         <v/>
       </c>
-      <c r="P19" s="29">
+      <c r="P19" s="37">
         <f>O19-I19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="34">
         <f>IF(A20&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="36">
         <f>I19</f>
         <v/>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A20-1)</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="35">
         <f>-D20*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A20-1)</f>
         <v/>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="36">
         <f>IF(C20&lt;=0,0,IF(I20&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C20-I20)),IF(B20=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B20/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C20)-C20))))</f>
         <v/>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="36">
         <f>-(C20-I20)</f>
         <v/>
       </c>
-      <c r="I20" s="28">
+      <c r="I20" s="36">
         <f>IF(C20&lt;=0,0,IF(B20=0,MAX(0,C20-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C20*(1+B20/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B20/12)^12-1)/(B20/12)))))</f>
         <v/>
       </c>
-      <c r="J20" s="28">
+      <c r="J20" s="36">
         <f>D20+E20+F20+G20+H20</f>
         <v/>
       </c>
-      <c r="K20" s="27">
+      <c r="K20" s="35">
         <f>-Rechner!$H$28*(A20&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L20" s="28">
+      <c r="L20" s="36">
         <f>-(D20+E20+F20+G20+K20)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M20" s="29">
+      <c r="M20" s="37">
         <f>J20+L20</f>
         <v/>
       </c>
-      <c r="N20" s="28">
+      <c r="N20" s="36">
         <f>N19+M20</f>
         <v/>
       </c>
-      <c r="O20" s="27">
+      <c r="O20" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A20</f>
         <v/>
       </c>
-      <c r="P20" s="29">
+      <c r="P20" s="37">
         <f>O20-I20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="34">
         <f>IF(A21&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="36">
         <f>I20</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A21-1)</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="35">
         <f>-D21*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A21-1)</f>
         <v/>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="36">
         <f>IF(C21&lt;=0,0,IF(I21&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C21-I21)),IF(B21=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B21/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C21)-C21))))</f>
         <v/>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="36">
         <f>-(C21-I21)</f>
         <v/>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="36">
         <f>IF(C21&lt;=0,0,IF(B21=0,MAX(0,C21-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C21*(1+B21/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B21/12)^12-1)/(B21/12)))))</f>
         <v/>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="36">
         <f>D21+E21+F21+G21+H21</f>
         <v/>
       </c>
-      <c r="K21" s="27">
+      <c r="K21" s="35">
         <f>-Rechner!$H$28*(A21&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="36">
         <f>-(D21+E21+F21+G21+K21)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M21" s="29">
+      <c r="M21" s="37">
         <f>J21+L21</f>
         <v/>
       </c>
-      <c r="N21" s="28">
+      <c r="N21" s="36">
         <f>N20+M21</f>
         <v/>
       </c>
-      <c r="O21" s="27">
+      <c r="O21" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A21</f>
         <v/>
       </c>
-      <c r="P21" s="29">
+      <c r="P21" s="37">
         <f>O21-I21</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="34">
         <f>IF(A22&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="36">
         <f>I21</f>
         <v/>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A22-1)</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="35">
         <f>-D22*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A22-1)</f>
         <v/>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="36">
         <f>IF(C22&lt;=0,0,IF(I22&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C22-I22)),IF(B22=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B22/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C22)-C22))))</f>
         <v/>
       </c>
-      <c r="H22" s="28">
+      <c r="H22" s="36">
         <f>-(C22-I22)</f>
         <v/>
       </c>
-      <c r="I22" s="28">
+      <c r="I22" s="36">
         <f>IF(C22&lt;=0,0,IF(B22=0,MAX(0,C22-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C22*(1+B22/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B22/12)^12-1)/(B22/12)))))</f>
         <v/>
       </c>
-      <c r="J22" s="28">
+      <c r="J22" s="36">
         <f>D22+E22+F22+G22+H22</f>
         <v/>
       </c>
-      <c r="K22" s="27">
+      <c r="K22" s="35">
         <f>-Rechner!$H$28*(A22&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L22" s="28">
+      <c r="L22" s="36">
         <f>-(D22+E22+F22+G22+K22)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M22" s="29">
+      <c r="M22" s="37">
         <f>J22+L22</f>
         <v/>
       </c>
-      <c r="N22" s="28">
+      <c r="N22" s="36">
         <f>N21+M22</f>
         <v/>
       </c>
-      <c r="O22" s="27">
+      <c r="O22" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A22</f>
         <v/>
       </c>
-      <c r="P22" s="29">
+      <c r="P22" s="37">
         <f>O22-I22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="34">
         <f>IF(A23&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="36">
         <f>I22</f>
         <v/>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A23-1)</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="35">
         <f>-D23*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A23-1)</f>
         <v/>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="36">
         <f>IF(C23&lt;=0,0,IF(I23&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C23-I23)),IF(B23=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B23/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C23)-C23))))</f>
         <v/>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="36">
         <f>-(C23-I23)</f>
         <v/>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="36">
         <f>IF(C23&lt;=0,0,IF(B23=0,MAX(0,C23-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C23*(1+B23/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B23/12)^12-1)/(B23/12)))))</f>
         <v/>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="36">
         <f>D23+E23+F23+G23+H23</f>
         <v/>
       </c>
-      <c r="K23" s="27">
+      <c r="K23" s="35">
         <f>-Rechner!$H$28*(A23&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="36">
         <f>-(D23+E23+F23+G23+K23)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M23" s="29">
+      <c r="M23" s="37">
         <f>J23+L23</f>
         <v/>
       </c>
-      <c r="N23" s="28">
+      <c r="N23" s="36">
         <f>N22+M23</f>
         <v/>
       </c>
-      <c r="O23" s="27">
+      <c r="O23" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A23</f>
         <v/>
       </c>
-      <c r="P23" s="29">
+      <c r="P23" s="37">
         <f>O23-I23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="34">
         <f>IF(A24&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="36">
         <f>I23</f>
         <v/>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A24-1)</f>
         <v/>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="35">
         <f>-D24*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A24-1)</f>
         <v/>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="36">
         <f>IF(C24&lt;=0,0,IF(I24&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C24-I24)),IF(B24=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B24/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C24)-C24))))</f>
         <v/>
       </c>
-      <c r="H24" s="28">
+      <c r="H24" s="36">
         <f>-(C24-I24)</f>
         <v/>
       </c>
-      <c r="I24" s="28">
+      <c r="I24" s="36">
         <f>IF(C24&lt;=0,0,IF(B24=0,MAX(0,C24-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C24*(1+B24/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B24/12)^12-1)/(B24/12)))))</f>
         <v/>
       </c>
-      <c r="J24" s="28">
+      <c r="J24" s="36">
         <f>D24+E24+F24+G24+H24</f>
         <v/>
       </c>
-      <c r="K24" s="27">
+      <c r="K24" s="35">
         <f>-Rechner!$H$28*(A24&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L24" s="28">
+      <c r="L24" s="36">
         <f>-(D24+E24+F24+G24+K24)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M24" s="29">
+      <c r="M24" s="37">
         <f>J24+L24</f>
         <v/>
       </c>
-      <c r="N24" s="28">
+      <c r="N24" s="36">
         <f>N23+M24</f>
         <v/>
       </c>
-      <c r="O24" s="27">
+      <c r="O24" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A24</f>
         <v/>
       </c>
-      <c r="P24" s="29">
+      <c r="P24" s="37">
         <f>O24-I24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="34">
         <f>IF(A25&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="36">
         <f>I24</f>
         <v/>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A25-1)</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="35">
         <f>-D25*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A25-1)</f>
         <v/>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="36">
         <f>IF(C25&lt;=0,0,IF(I25&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C25-I25)),IF(B25=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B25/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C25)-C25))))</f>
         <v/>
       </c>
-      <c r="H25" s="28">
+      <c r="H25" s="36">
         <f>-(C25-I25)</f>
         <v/>
       </c>
-      <c r="I25" s="28">
+      <c r="I25" s="36">
         <f>IF(C25&lt;=0,0,IF(B25=0,MAX(0,C25-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C25*(1+B25/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B25/12)^12-1)/(B25/12)))))</f>
         <v/>
       </c>
-      <c r="J25" s="28">
+      <c r="J25" s="36">
         <f>D25+E25+F25+G25+H25</f>
         <v/>
       </c>
-      <c r="K25" s="27">
+      <c r="K25" s="35">
         <f>-Rechner!$H$28*(A25&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L25" s="28">
+      <c r="L25" s="36">
         <f>-(D25+E25+F25+G25+K25)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M25" s="29">
+      <c r="M25" s="37">
         <f>J25+L25</f>
         <v/>
       </c>
-      <c r="N25" s="28">
+      <c r="N25" s="36">
         <f>N24+M25</f>
         <v/>
       </c>
-      <c r="O25" s="27">
+      <c r="O25" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A25</f>
         <v/>
       </c>
-      <c r="P25" s="29">
+      <c r="P25" s="37">
         <f>O25-I25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="34">
         <f>IF(A26&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="36">
         <f>I25</f>
         <v/>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A26-1)</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="35">
         <f>-D26*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A26-1)</f>
         <v/>
       </c>
-      <c r="G26" s="28">
+      <c r="G26" s="36">
         <f>IF(C26&lt;=0,0,IF(I26&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C26-I26)),IF(B26=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B26/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C26)-C26))))</f>
         <v/>
       </c>
-      <c r="H26" s="28">
+      <c r="H26" s="36">
         <f>-(C26-I26)</f>
         <v/>
       </c>
-      <c r="I26" s="28">
+      <c r="I26" s="36">
         <f>IF(C26&lt;=0,0,IF(B26=0,MAX(0,C26-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C26*(1+B26/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B26/12)^12-1)/(B26/12)))))</f>
         <v/>
       </c>
-      <c r="J26" s="28">
+      <c r="J26" s="36">
         <f>D26+E26+F26+G26+H26</f>
         <v/>
       </c>
-      <c r="K26" s="27">
+      <c r="K26" s="35">
         <f>-Rechner!$H$28*(A26&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L26" s="28">
+      <c r="L26" s="36">
         <f>-(D26+E26+F26+G26+K26)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M26" s="29">
+      <c r="M26" s="37">
         <f>J26+L26</f>
         <v/>
       </c>
-      <c r="N26" s="28">
+      <c r="N26" s="36">
         <f>N25+M26</f>
         <v/>
       </c>
-      <c r="O26" s="27">
+      <c r="O26" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A26</f>
         <v/>
       </c>
-      <c r="P26" s="29">
+      <c r="P26" s="37">
         <f>O26-I26</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="26">
+      <c r="B27" s="34">
         <f>IF(A27&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="36">
         <f>I26</f>
         <v/>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A27-1)</f>
         <v/>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="35">
         <f>-D27*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F27" s="27">
+      <c r="F27" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A27-1)</f>
         <v/>
       </c>
-      <c r="G27" s="28">
+      <c r="G27" s="36">
         <f>IF(C27&lt;=0,0,IF(I27&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C27-I27)),IF(B27=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B27/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C27)-C27))))</f>
         <v/>
       </c>
-      <c r="H27" s="28">
+      <c r="H27" s="36">
         <f>-(C27-I27)</f>
         <v/>
       </c>
-      <c r="I27" s="28">
+      <c r="I27" s="36">
         <f>IF(C27&lt;=0,0,IF(B27=0,MAX(0,C27-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C27*(1+B27/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B27/12)^12-1)/(B27/12)))))</f>
         <v/>
       </c>
-      <c r="J27" s="28">
+      <c r="J27" s="36">
         <f>D27+E27+F27+G27+H27</f>
         <v/>
       </c>
-      <c r="K27" s="27">
+      <c r="K27" s="35">
         <f>-Rechner!$H$28*(A27&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L27" s="28">
+      <c r="L27" s="36">
         <f>-(D27+E27+F27+G27+K27)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M27" s="29">
+      <c r="M27" s="37">
         <f>J27+L27</f>
         <v/>
       </c>
-      <c r="N27" s="28">
+      <c r="N27" s="36">
         <f>N26+M27</f>
         <v/>
       </c>
-      <c r="O27" s="27">
+      <c r="O27" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A27</f>
         <v/>
       </c>
-      <c r="P27" s="29">
+      <c r="P27" s="37">
         <f>O27-I27</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="34">
         <f>IF(A28&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="36">
         <f>I27</f>
         <v/>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A28-1)</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="35">
         <f>-D28*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A28-1)</f>
         <v/>
       </c>
-      <c r="G28" s="28">
+      <c r="G28" s="36">
         <f>IF(C28&lt;=0,0,IF(I28&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C28-I28)),IF(B28=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B28/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C28)-C28))))</f>
         <v/>
       </c>
-      <c r="H28" s="28">
+      <c r="H28" s="36">
         <f>-(C28-I28)</f>
         <v/>
       </c>
-      <c r="I28" s="28">
+      <c r="I28" s="36">
         <f>IF(C28&lt;=0,0,IF(B28=0,MAX(0,C28-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C28*(1+B28/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B28/12)^12-1)/(B28/12)))))</f>
         <v/>
       </c>
-      <c r="J28" s="28">
+      <c r="J28" s="36">
         <f>D28+E28+F28+G28+H28</f>
         <v/>
       </c>
-      <c r="K28" s="27">
+      <c r="K28" s="35">
         <f>-Rechner!$H$28*(A28&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L28" s="28">
+      <c r="L28" s="36">
         <f>-(D28+E28+F28+G28+K28)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M28" s="29">
+      <c r="M28" s="37">
         <f>J28+L28</f>
         <v/>
       </c>
-      <c r="N28" s="28">
+      <c r="N28" s="36">
         <f>N27+M28</f>
         <v/>
       </c>
-      <c r="O28" s="27">
+      <c r="O28" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A28</f>
         <v/>
       </c>
-      <c r="P28" s="29">
+      <c r="P28" s="37">
         <f>O28-I28</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="34">
         <f>IF(A29&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="36">
         <f>I28</f>
         <v/>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A29-1)</f>
         <v/>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="35">
         <f>-D29*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A29-1)</f>
         <v/>
       </c>
-      <c r="G29" s="28">
+      <c r="G29" s="36">
         <f>IF(C29&lt;=0,0,IF(I29&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C29-I29)),IF(B29=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B29/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C29)-C29))))</f>
         <v/>
       </c>
-      <c r="H29" s="28">
+      <c r="H29" s="36">
         <f>-(C29-I29)</f>
         <v/>
       </c>
-      <c r="I29" s="28">
+      <c r="I29" s="36">
         <f>IF(C29&lt;=0,0,IF(B29=0,MAX(0,C29-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C29*(1+B29/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B29/12)^12-1)/(B29/12)))))</f>
         <v/>
       </c>
-      <c r="J29" s="28">
+      <c r="J29" s="36">
         <f>D29+E29+F29+G29+H29</f>
         <v/>
       </c>
-      <c r="K29" s="27">
+      <c r="K29" s="35">
         <f>-Rechner!$H$28*(A29&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="36">
         <f>-(D29+E29+F29+G29+K29)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M29" s="29">
+      <c r="M29" s="37">
         <f>J29+L29</f>
         <v/>
       </c>
-      <c r="N29" s="28">
+      <c r="N29" s="36">
         <f>N28+M29</f>
         <v/>
       </c>
-      <c r="O29" s="27">
+      <c r="O29" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A29</f>
         <v/>
       </c>
-      <c r="P29" s="29">
+      <c r="P29" s="37">
         <f>O29-I29</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="34">
         <f>IF(A30&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="36">
         <f>I29</f>
         <v/>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A30-1)</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="35">
         <f>-D30*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F30" s="27">
+      <c r="F30" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A30-1)</f>
         <v/>
       </c>
-      <c r="G30" s="28">
+      <c r="G30" s="36">
         <f>IF(C30&lt;=0,0,IF(I30&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C30-I30)),IF(B30=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B30/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C30)-C30))))</f>
         <v/>
       </c>
-      <c r="H30" s="28">
+      <c r="H30" s="36">
         <f>-(C30-I30)</f>
         <v/>
       </c>
-      <c r="I30" s="28">
+      <c r="I30" s="36">
         <f>IF(C30&lt;=0,0,IF(B30=0,MAX(0,C30-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C30*(1+B30/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B30/12)^12-1)/(B30/12)))))</f>
         <v/>
       </c>
-      <c r="J30" s="28">
+      <c r="J30" s="36">
         <f>D30+E30+F30+G30+H30</f>
         <v/>
       </c>
-      <c r="K30" s="27">
+      <c r="K30" s="35">
         <f>-Rechner!$H$28*(A30&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L30" s="28">
+      <c r="L30" s="36">
         <f>-(D30+E30+F30+G30+K30)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M30" s="29">
+      <c r="M30" s="37">
         <f>J30+L30</f>
         <v/>
       </c>
-      <c r="N30" s="28">
+      <c r="N30" s="36">
         <f>N29+M30</f>
         <v/>
       </c>
-      <c r="O30" s="27">
+      <c r="O30" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A30</f>
         <v/>
       </c>
-      <c r="P30" s="29">
+      <c r="P30" s="37">
         <f>O30-I30</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="26">
+      <c r="B31" s="34">
         <f>IF(A31&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="36">
         <f>I30</f>
         <v/>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A31-1)</f>
         <v/>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="35">
         <f>-D31*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A31-1)</f>
         <v/>
       </c>
-      <c r="G31" s="28">
+      <c r="G31" s="36">
         <f>IF(C31&lt;=0,0,IF(I31&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C31-I31)),IF(B31=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B31/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C31)-C31))))</f>
         <v/>
       </c>
-      <c r="H31" s="28">
+      <c r="H31" s="36">
         <f>-(C31-I31)</f>
         <v/>
       </c>
-      <c r="I31" s="28">
+      <c r="I31" s="36">
         <f>IF(C31&lt;=0,0,IF(B31=0,MAX(0,C31-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C31*(1+B31/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B31/12)^12-1)/(B31/12)))))</f>
         <v/>
       </c>
-      <c r="J31" s="28">
+      <c r="J31" s="36">
         <f>D31+E31+F31+G31+H31</f>
         <v/>
       </c>
-      <c r="K31" s="27">
+      <c r="K31" s="35">
         <f>-Rechner!$H$28*(A31&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="36">
         <f>-(D31+E31+F31+G31+K31)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M31" s="29">
+      <c r="M31" s="37">
         <f>J31+L31</f>
         <v/>
       </c>
-      <c r="N31" s="28">
+      <c r="N31" s="36">
         <f>N30+M31</f>
         <v/>
       </c>
-      <c r="O31" s="27">
+      <c r="O31" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A31</f>
         <v/>
       </c>
-      <c r="P31" s="29">
+      <c r="P31" s="37">
         <f>O31-I31</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="34">
         <f>IF(A32&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="36">
         <f>I31</f>
         <v/>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A32-1)</f>
         <v/>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="35">
         <f>-D32*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F32" s="27">
+      <c r="F32" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A32-1)</f>
         <v/>
       </c>
-      <c r="G32" s="28">
+      <c r="G32" s="36">
         <f>IF(C32&lt;=0,0,IF(I32&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C32-I32)),IF(B32=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B32/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C32)-C32))))</f>
         <v/>
       </c>
-      <c r="H32" s="28">
+      <c r="H32" s="36">
         <f>-(C32-I32)</f>
         <v/>
       </c>
-      <c r="I32" s="28">
+      <c r="I32" s="36">
         <f>IF(C32&lt;=0,0,IF(B32=0,MAX(0,C32-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C32*(1+B32/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B32/12)^12-1)/(B32/12)))))</f>
         <v/>
       </c>
-      <c r="J32" s="28">
+      <c r="J32" s="36">
         <f>D32+E32+F32+G32+H32</f>
         <v/>
       </c>
-      <c r="K32" s="27">
+      <c r="K32" s="35">
         <f>-Rechner!$H$28*(A32&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L32" s="28">
+      <c r="L32" s="36">
         <f>-(D32+E32+F32+G32+K32)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M32" s="29">
+      <c r="M32" s="37">
         <f>J32+L32</f>
         <v/>
       </c>
-      <c r="N32" s="28">
+      <c r="N32" s="36">
         <f>N31+M32</f>
         <v/>
       </c>
-      <c r="O32" s="27">
+      <c r="O32" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A32</f>
         <v/>
       </c>
-      <c r="P32" s="29">
+      <c r="P32" s="37">
         <f>O32-I32</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="14" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="26">
+      <c r="B33" s="34">
         <f>IF(A33&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="36">
         <f>I32</f>
         <v/>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A33-1)</f>
         <v/>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="35">
         <f>-D33*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F33" s="27">
+      <c r="F33" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A33-1)</f>
         <v/>
       </c>
-      <c r="G33" s="28">
+      <c r="G33" s="36">
         <f>IF(C33&lt;=0,0,IF(I33&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C33-I33)),IF(B33=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B33/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C33)-C33))))</f>
         <v/>
       </c>
-      <c r="H33" s="28">
+      <c r="H33" s="36">
         <f>-(C33-I33)</f>
         <v/>
       </c>
-      <c r="I33" s="28">
+      <c r="I33" s="36">
         <f>IF(C33&lt;=0,0,IF(B33=0,MAX(0,C33-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C33*(1+B33/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B33/12)^12-1)/(B33/12)))))</f>
         <v/>
       </c>
-      <c r="J33" s="28">
+      <c r="J33" s="36">
         <f>D33+E33+F33+G33+H33</f>
         <v/>
       </c>
-      <c r="K33" s="27">
+      <c r="K33" s="35">
         <f>-Rechner!$H$28*(A33&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="36">
         <f>-(D33+E33+F33+G33+K33)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M33" s="29">
+      <c r="M33" s="37">
         <f>J33+L33</f>
         <v/>
       </c>
-      <c r="N33" s="28">
+      <c r="N33" s="36">
         <f>N32+M33</f>
         <v/>
       </c>
-      <c r="O33" s="27">
+      <c r="O33" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A33</f>
         <v/>
       </c>
-      <c r="P33" s="29">
+      <c r="P33" s="37">
         <f>O33-I33</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="34">
         <f>IF(A34&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
         <v/>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="36">
         <f>I33</f>
         <v/>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A34-1)</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="35">
         <f>-D34*Rechner!$C$25</f>
         <v/>
       </c>
-      <c r="F34" s="27">
+      <c r="F34" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A34-1)</f>
         <v/>
       </c>
-      <c r="G34" s="28">
+      <c r="G34" s="36">
         <f>IF(C34&lt;=0,0,IF(I34&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C34-I34)),IF(B34=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B34/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C34)-C34))))</f>
         <v/>
       </c>
-      <c r="H34" s="28">
+      <c r="H34" s="36">
         <f>-(C34-I34)</f>
         <v/>
       </c>
-      <c r="I34" s="28">
+      <c r="I34" s="36">
         <f>IF(C34&lt;=0,0,IF(B34=0,MAX(0,C34-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C34*(1+B34/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B34/12)^12-1)/(B34/12)))))</f>
         <v/>
       </c>
-      <c r="J34" s="28">
+      <c r="J34" s="36">
         <f>D34+E34+F34+G34+H34</f>
         <v/>
       </c>
-      <c r="K34" s="27">
+      <c r="K34" s="35">
         <f>-Rechner!$H$28*(A34&lt;=1/Rechner!$C$27)</f>
         <v/>
       </c>
-      <c r="L34" s="28">
+      <c r="L34" s="36">
         <f>-(D34+E34+F34+G34+K34)*Rechner!$C$28</f>
         <v/>
       </c>
-      <c r="M34" s="29">
+      <c r="M34" s="37">
         <f>J34+L34</f>
         <v/>
       </c>
-      <c r="N34" s="28">
+      <c r="N34" s="36">
         <f>N33+M34</f>
         <v/>
       </c>
-      <c r="O34" s="27">
+      <c r="O34" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A34</f>
         <v/>
       </c>
-      <c r="P34" s="29">
+      <c r="P34" s="37">
         <f>O34-I34</f>
         <v/>
       </c>
@@ -3864,12 +5654,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="M5:N34">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="2">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B34">
-    <cfRule type="expression" priority="2" dxfId="3">
+    <cfRule type="expression" priority="2" dxfId="5">
       <formula>A5&gt;Rechner!$C$20</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3877,7 +5667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3891,7 +5681,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>Fernere Lebenserwartung (Frauen, gerundet)</t>
         </is>
@@ -3905,79 +5695,846 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Alter</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Weitere Lebensjahre</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="n">
+      <c r="A4" s="38" t="n">
         <v>60</v>
       </c>
-      <c r="B4" s="31" t="n">
+      <c r="B4" s="39" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="n">
+      <c r="A5" s="38" t="n">
         <v>65</v>
       </c>
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="39" t="n">
         <v>20.9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="n">
+      <c r="A6" s="38" t="n">
         <v>70</v>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="39" t="n">
         <v>16.9</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="38" t="n">
         <v>75</v>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="39" t="n">
         <v>13.2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="n">
+      <c r="A8" s="38" t="n">
         <v>80</v>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="39" t="n">
         <v>9.800000000000001</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="n">
+      <c r="A9" s="38" t="n">
         <v>85</v>
       </c>
-      <c r="B9" s="31" t="n">
+      <c r="B9" s="39" t="n">
         <v>6.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="n">
+      <c r="A10" s="38" t="n">
         <v>90</v>
       </c>
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="39" t="n">
         <v>4.6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="38" t="n">
         <v>95</v>
       </c>
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="39" t="n">
         <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="40" t="inlineStr">
+        <is>
+          <t>Hilfstabellen für die Diagramme im Dashboard (werden automatisch berechnet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Monatliche Rechnung</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>€ / Monat</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Kaufpreis</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Cashflow nach Steuern / Monat</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Abweichung</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>Jahr</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>Zinsen</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>Tilgung</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>Guthaben Verkäufer (Ende Jahr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Kaltmiete</t>
+        </is>
+      </c>
+      <c r="B4" s="35">
+        <f>Rechner!$H$12</f>
+        <v/>
+      </c>
+      <c r="D4" s="41">
+        <f>Rechner!$C$6*(1+F4)</f>
+        <v/>
+      </c>
+      <c r="E4" s="41">
+        <f>Rechner!$H$19-$E$14*(D4-Rechner!$C$6)</f>
+        <v/>
+      </c>
+      <c r="F4" s="42" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="41">
+        <f>-Prognose!G5</f>
+        <v/>
+      </c>
+      <c r="J4" s="41">
+        <f>-Prognose!H5</f>
+        <v/>
+      </c>
+      <c r="K4" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H4,FV(Rechner!$C$35,H4,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Mietausfall</t>
+        </is>
+      </c>
+      <c r="B5" s="35">
+        <f>Rechner!$H$13</f>
+        <v/>
+      </c>
+      <c r="D5" s="41">
+        <f>Rechner!$C$6*(1+F5)</f>
+        <v/>
+      </c>
+      <c r="E5" s="41">
+        <f>Rechner!$H$19-$E$14*(D5-Rechner!$C$6)</f>
+        <v/>
+      </c>
+      <c r="F5" s="42" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="41">
+        <f>-Prognose!G6</f>
+        <v/>
+      </c>
+      <c r="J5" s="41">
+        <f>-Prognose!H6</f>
+        <v/>
+      </c>
+      <c r="K5" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H5,FV(Rechner!$C$35,H5,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Kreditrate</t>
+        </is>
+      </c>
+      <c r="B6" s="35">
+        <f>Rechner!$H$14</f>
+        <v/>
+      </c>
+      <c r="D6" s="41">
+        <f>Rechner!$C$6*(1+F6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="41">
+        <f>Rechner!$H$19-$E$14*(D6-Rechner!$C$6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="42" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="41">
+        <f>-Prognose!G7</f>
+        <v/>
+      </c>
+      <c r="J6" s="41">
+        <f>-Prognose!H7</f>
+        <v/>
+      </c>
+      <c r="K6" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H6,FV(Rechner!$C$35,H6,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Instandhaltung</t>
+        </is>
+      </c>
+      <c r="B7" s="35">
+        <f>Rechner!$H$15</f>
+        <v/>
+      </c>
+      <c r="D7" s="41">
+        <f>Rechner!$C$6*(1+F7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="41">
+        <f>Rechner!$H$19-$E$14*(D7-Rechner!$C$6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="42" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="41">
+        <f>-Prognose!G8</f>
+        <v/>
+      </c>
+      <c r="J7" s="41">
+        <f>-Prognose!H8</f>
+        <v/>
+      </c>
+      <c r="K7" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H7,FV(Rechner!$C$35,H7,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten</t>
+        </is>
+      </c>
+      <c r="B8" s="35">
+        <f>Rechner!$H$16</f>
+        <v/>
+      </c>
+      <c r="D8" s="41">
+        <f>Rechner!$C$6*(1+F8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="41">
+        <f>Rechner!$H$19-$E$14*(D8-Rechner!$C$6)</f>
+        <v/>
+      </c>
+      <c r="F8" s="42" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="41">
+        <f>-Prognose!G9</f>
+        <v/>
+      </c>
+      <c r="J8" s="41">
+        <f>-Prognose!H9</f>
+        <v/>
+      </c>
+      <c r="K8" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H8,FV(Rechner!$C$35,H8,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Steuereffekt</t>
+        </is>
+      </c>
+      <c r="B9" s="35">
+        <f>Rechner!$H$18</f>
+        <v/>
+      </c>
+      <c r="D9" s="41">
+        <f>Rechner!$C$6*(1+F9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="41">
+        <f>Rechner!$H$19-$E$14*(D9-Rechner!$C$6)</f>
+        <v/>
+      </c>
+      <c r="F9" s="42" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" s="41">
+        <f>-Prognose!G10</f>
+        <v/>
+      </c>
+      <c r="J9" s="41">
+        <f>-Prognose!H10</f>
+        <v/>
+      </c>
+      <c r="K9" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H9,FV(Rechner!$C$35,H9,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Cashflow nach Steuern</t>
+        </is>
+      </c>
+      <c r="B10" s="35">
+        <f>Rechner!$H$19</f>
+        <v/>
+      </c>
+      <c r="D10" s="41">
+        <f>Rechner!$C$6*(1+F10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="41">
+        <f>Rechner!$H$19-$E$14*(D10-Rechner!$C$6)</f>
+        <v/>
+      </c>
+      <c r="F10" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" s="41">
+        <f>-Prognose!G11</f>
+        <v/>
+      </c>
+      <c r="J10" s="41">
+        <f>-Prognose!H11</f>
+        <v/>
+      </c>
+      <c r="K10" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H10,FV(Rechner!$C$35,H10,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" s="41">
+        <f>Rechner!$C$6*(1+F11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="41">
+        <f>Rechner!$H$19-$E$14*(D11-Rechner!$C$6)</f>
+        <v/>
+      </c>
+      <c r="F11" s="42" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" s="41">
+        <f>-Prognose!G12</f>
+        <v/>
+      </c>
+      <c r="J11" s="41">
+        <f>-Prognose!H12</f>
+        <v/>
+      </c>
+      <c r="K11" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H11,FV(Rechner!$C$35,H11,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" s="41">
+        <f>Rechner!$C$6*(1+F12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="41">
+        <f>Rechner!$H$19-$E$14*(D12-Rechner!$C$6)</f>
+        <v/>
+      </c>
+      <c r="F12" s="42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I12" s="41">
+        <f>-Prognose!G13</f>
+        <v/>
+      </c>
+      <c r="J12" s="41">
+        <f>-Prognose!H13</f>
+        <v/>
+      </c>
+      <c r="K12" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H12,FV(Rechner!$C$35,H12,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" s="41">
+        <f>-Prognose!G14</f>
+        <v/>
+      </c>
+      <c r="J13" s="41">
+        <f>-Prognose!H14</f>
+        <v/>
+      </c>
+      <c r="K13" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H13,FV(Rechner!$C$35,H13,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Steigung (€ Cashflow je € Kaufpreis)</t>
+        </is>
+      </c>
+      <c r="E14" s="43">
+        <f>IF(Rechner!$H$10&lt;=0,0,(1+Rechner!$C$13+Rechner!$C$14+Rechner!$C$15)/12*((Rechner!$C$18+Rechner!$C$19)-Rechner!$C$28*(Rechner!$H$26/Rechner!$H$10+Rechner!$C$26*Rechner!$C$27)))</f>
+        <v/>
+      </c>
+      <c r="H14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I14" s="41">
+        <f>-Prognose!G15</f>
+        <v/>
+      </c>
+      <c r="J14" s="41">
+        <f>-Prognose!H15</f>
+        <v/>
+      </c>
+      <c r="K14" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H14,FV(Rechner!$C$35,H14,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Gilt, solange ein Darlehen nötig ist (Cashflow hängt linear vom Kaufpreis ab).</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" s="41">
+        <f>-Prognose!G16</f>
+        <v/>
+      </c>
+      <c r="J15" s="41">
+        <f>-Prognose!H16</f>
+        <v/>
+      </c>
+      <c r="K15" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H15,FV(Rechner!$C$35,H15,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="H16" t="n">
+        <v>13</v>
+      </c>
+      <c r="I16" s="41">
+        <f>-Prognose!G17</f>
+        <v/>
+      </c>
+      <c r="J16" s="41">
+        <f>-Prognose!H17</f>
+        <v/>
+      </c>
+      <c r="K16" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H16,FV(Rechner!$C$35,H16,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="H17" t="n">
+        <v>14</v>
+      </c>
+      <c r="I17" s="41">
+        <f>-Prognose!G18</f>
+        <v/>
+      </c>
+      <c r="J17" s="41">
+        <f>-Prognose!H18</f>
+        <v/>
+      </c>
+      <c r="K17" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H17,FV(Rechner!$C$35,H17,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" t="n">
+        <v>15</v>
+      </c>
+      <c r="I18" s="41">
+        <f>-Prognose!G19</f>
+        <v/>
+      </c>
+      <c r="J18" s="41">
+        <f>-Prognose!H19</f>
+        <v/>
+      </c>
+      <c r="K18" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H18,FV(Rechner!$C$35,H18,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="H19" t="n">
+        <v>16</v>
+      </c>
+      <c r="I19" s="41">
+        <f>-Prognose!G20</f>
+        <v/>
+      </c>
+      <c r="J19" s="41">
+        <f>-Prognose!H20</f>
+        <v/>
+      </c>
+      <c r="K19" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H19,FV(Rechner!$C$35,H19,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" t="n">
+        <v>17</v>
+      </c>
+      <c r="I20" s="41">
+        <f>-Prognose!G21</f>
+        <v/>
+      </c>
+      <c r="J20" s="41">
+        <f>-Prognose!H21</f>
+        <v/>
+      </c>
+      <c r="K20" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H20,FV(Rechner!$C$35,H20,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" t="n">
+        <v>18</v>
+      </c>
+      <c r="I21" s="41">
+        <f>-Prognose!G22</f>
+        <v/>
+      </c>
+      <c r="J21" s="41">
+        <f>-Prognose!H22</f>
+        <v/>
+      </c>
+      <c r="K21" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H21,FV(Rechner!$C$35,H21,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="H22" t="n">
+        <v>19</v>
+      </c>
+      <c r="I22" s="41">
+        <f>-Prognose!G23</f>
+        <v/>
+      </c>
+      <c r="J22" s="41">
+        <f>-Prognose!H23</f>
+        <v/>
+      </c>
+      <c r="K22" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H22,FV(Rechner!$C$35,H22,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="H23" t="n">
+        <v>20</v>
+      </c>
+      <c r="I23" s="41">
+        <f>-Prognose!G24</f>
+        <v/>
+      </c>
+      <c r="J23" s="41">
+        <f>-Prognose!H24</f>
+        <v/>
+      </c>
+      <c r="K23" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H23,FV(Rechner!$C$35,H23,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" t="n">
+        <v>21</v>
+      </c>
+      <c r="I24" s="41">
+        <f>-Prognose!G25</f>
+        <v/>
+      </c>
+      <c r="J24" s="41">
+        <f>-Prognose!H25</f>
+        <v/>
+      </c>
+      <c r="K24" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H24,FV(Rechner!$C$35,H24,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="H25" t="n">
+        <v>22</v>
+      </c>
+      <c r="I25" s="41">
+        <f>-Prognose!G26</f>
+        <v/>
+      </c>
+      <c r="J25" s="41">
+        <f>-Prognose!H26</f>
+        <v/>
+      </c>
+      <c r="K25" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H25,FV(Rechner!$C$35,H25,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" t="n">
+        <v>23</v>
+      </c>
+      <c r="I26" s="41">
+        <f>-Prognose!G27</f>
+        <v/>
+      </c>
+      <c r="J26" s="41">
+        <f>-Prognose!H27</f>
+        <v/>
+      </c>
+      <c r="K26" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H26,FV(Rechner!$C$35,H26,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27" t="n">
+        <v>24</v>
+      </c>
+      <c r="I27" s="41">
+        <f>-Prognose!G28</f>
+        <v/>
+      </c>
+      <c r="J27" s="41">
+        <f>-Prognose!H28</f>
+        <v/>
+      </c>
+      <c r="K27" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H27,FV(Rechner!$C$35,H27,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" t="n">
+        <v>25</v>
+      </c>
+      <c r="I28" s="41">
+        <f>-Prognose!G29</f>
+        <v/>
+      </c>
+      <c r="J28" s="41">
+        <f>-Prognose!H29</f>
+        <v/>
+      </c>
+      <c r="K28" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H28,FV(Rechner!$C$35,H28,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="H29" t="n">
+        <v>26</v>
+      </c>
+      <c r="I29" s="41">
+        <f>-Prognose!G30</f>
+        <v/>
+      </c>
+      <c r="J29" s="41">
+        <f>-Prognose!H30</f>
+        <v/>
+      </c>
+      <c r="K29" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H29,FV(Rechner!$C$35,H29,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="H30" t="n">
+        <v>27</v>
+      </c>
+      <c r="I30" s="41">
+        <f>-Prognose!G31</f>
+        <v/>
+      </c>
+      <c r="J30" s="41">
+        <f>-Prognose!H31</f>
+        <v/>
+      </c>
+      <c r="K30" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H30,FV(Rechner!$C$35,H30,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31" t="n">
+        <v>28</v>
+      </c>
+      <c r="I31" s="41">
+        <f>-Prognose!G32</f>
+        <v/>
+      </c>
+      <c r="J31" s="41">
+        <f>-Prognose!H32</f>
+        <v/>
+      </c>
+      <c r="K31" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H31,FV(Rechner!$C$35,H31,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32" t="n">
+        <v>29</v>
+      </c>
+      <c r="I32" s="41">
+        <f>-Prognose!G33</f>
+        <v/>
+      </c>
+      <c r="J32" s="41">
+        <f>-Prognose!H33</f>
+        <v/>
+      </c>
+      <c r="K32" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H32,FV(Rechner!$C$35,H32,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="41">
+        <f>-Prognose!G34</f>
+        <v/>
+      </c>
+      <c r="J33" s="41">
+        <f>-Prognose!H34</f>
+        <v/>
+      </c>
+      <c r="K33" s="41">
+        <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H33,FV(Rechner!$C$35,H33,Rechner!$H$37,-Rechner!$C$6)))</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/immobilien/Hauskauf_Rechner_Damme.xlsx
+++ b/immobilien/Hauskauf_Rechner_Damme.xlsx
@@ -394,6 +394,12 @@
           <tx>
             <strRef>
               <f>'Prognose'!M4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Cashflow nach Steuern</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -410,11 +416,199 @@
           <cat>
             <numRef>
               <f>'Prognose'!$A$5:$A$34</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>1.0</v>
+                </pt>
+                <pt idx="1">
+                  <v>2.0</v>
+                </pt>
+                <pt idx="2">
+                  <v>3.0</v>
+                </pt>
+                <pt idx="3">
+                  <v>4.0</v>
+                </pt>
+                <pt idx="4">
+                  <v>5.0</v>
+                </pt>
+                <pt idx="5">
+                  <v>6.0</v>
+                </pt>
+                <pt idx="6">
+                  <v>7.0</v>
+                </pt>
+                <pt idx="7">
+                  <v>8.0</v>
+                </pt>
+                <pt idx="8">
+                  <v>9.0</v>
+                </pt>
+                <pt idx="9">
+                  <v>10.0</v>
+                </pt>
+                <pt idx="10">
+                  <v>11.0</v>
+                </pt>
+                <pt idx="11">
+                  <v>12.0</v>
+                </pt>
+                <pt idx="12">
+                  <v>13.0</v>
+                </pt>
+                <pt idx="13">
+                  <v>14.0</v>
+                </pt>
+                <pt idx="14">
+                  <v>15.0</v>
+                </pt>
+                <pt idx="15">
+                  <v>16.0</v>
+                </pt>
+                <pt idx="16">
+                  <v>17.0</v>
+                </pt>
+                <pt idx="17">
+                  <v>18.0</v>
+                </pt>
+                <pt idx="18">
+                  <v>19.0</v>
+                </pt>
+                <pt idx="19">
+                  <v>20.0</v>
+                </pt>
+                <pt idx="20">
+                  <v>21.0</v>
+                </pt>
+                <pt idx="21">
+                  <v>22.0</v>
+                </pt>
+                <pt idx="22">
+                  <v>23.0</v>
+                </pt>
+                <pt idx="23">
+                  <v>24.0</v>
+                </pt>
+                <pt idx="24">
+                  <v>25.0</v>
+                </pt>
+                <pt idx="25">
+                  <v>26.0</v>
+                </pt>
+                <pt idx="26">
+                  <v>27.0</v>
+                </pt>
+                <pt idx="27">
+                  <v>28.0</v>
+                </pt>
+                <pt idx="28">
+                  <v>29.0</v>
+                </pt>
+                <pt idx="29">
+                  <v>30.0</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Prognose'!$M$5:$M$34</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>-2931.75236511011</v>
+                </pt>
+                <pt idx="1">
+                  <v>-2896.54673169172</v>
+                </pt>
+                <pt idx="2">
+                  <v>-2862.19958902394</v>
+                </pt>
+                <pt idx="3">
+                  <v>-2828.77483119181</v>
+                </pt>
+                <pt idx="4">
+                  <v>-2796.33923143922</v>
+                </pt>
+                <pt idx="5">
+                  <v>-2764.96255858919</v>
+                </pt>
+                <pt idx="6">
+                  <v>-2734.71769802147</v>
+                </pt>
+                <pt idx="7">
+                  <v>-2705.68077738418</v>
+                </pt>
+                <pt idx="8">
+                  <v>-2677.93129722282</v>
+                </pt>
+                <pt idx="9">
+                  <v>-2651.55226671734</v>
+                </pt>
+                <pt idx="10">
+                  <v>-2270.75060505486</v>
+                </pt>
+                <pt idx="11">
+                  <v>-2245.50777402486</v>
+                </pt>
+                <pt idx="12">
+                  <v>-2222.3810205619</v>
+                </pt>
+                <pt idx="13">
+                  <v>-2201.51228809536</v>
+                </pt>
+                <pt idx="14">
+                  <v>-2183.05062378418</v>
+                </pt>
+                <pt idx="15">
+                  <v>-2167.15251184212</v>
+                </pt>
+                <pt idx="16">
+                  <v>-2153.98222224546</v>
+                </pt>
+                <pt idx="17">
+                  <v>-2143.71217553007</v>
+                </pt>
+                <pt idx="18">
+                  <v>-2136.52332441733</v>
+                </pt>
+                <pt idx="19">
+                  <v>-2132.60555304235</v>
+                </pt>
+                <pt idx="20">
+                  <v>-2132.15809459345</v>
+                </pt>
+                <pt idx="21">
+                  <v>-2135.38996820898</v>
+                </pt>
+                <pt idx="22">
+                  <v>-2142.5204360165</v>
+                </pt>
+                <pt idx="23">
+                  <v>-2153.77948123982</v>
+                </pt>
+                <pt idx="24">
+                  <v>-2169.40830834218</v>
+                </pt>
+                <pt idx="25">
+                  <v>-2189.65986621806</v>
+                </pt>
+                <pt idx="26">
+                  <v>-2214.79939549266</v>
+                </pt>
+                <pt idx="27">
+                  <v>-2245.10500103694</v>
+                </pt>
+                <pt idx="28">
+                  <v>-2280.86825085662</v>
+                </pt>
+                <pt idx="29">
+                  <v>1408.11537162878</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -556,6 +750,12 @@
           <tx>
             <strRef>
               <f>'Prognose'!O4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Immobilienwert</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -577,11 +777,199 @@
           <cat>
             <numRef>
               <f>'Prognose'!$A$5:$A$34</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>1.0</v>
+                </pt>
+                <pt idx="1">
+                  <v>2.0</v>
+                </pt>
+                <pt idx="2">
+                  <v>3.0</v>
+                </pt>
+                <pt idx="3">
+                  <v>4.0</v>
+                </pt>
+                <pt idx="4">
+                  <v>5.0</v>
+                </pt>
+                <pt idx="5">
+                  <v>6.0</v>
+                </pt>
+                <pt idx="6">
+                  <v>7.0</v>
+                </pt>
+                <pt idx="7">
+                  <v>8.0</v>
+                </pt>
+                <pt idx="8">
+                  <v>9.0</v>
+                </pt>
+                <pt idx="9">
+                  <v>10.0</v>
+                </pt>
+                <pt idx="10">
+                  <v>11.0</v>
+                </pt>
+                <pt idx="11">
+                  <v>12.0</v>
+                </pt>
+                <pt idx="12">
+                  <v>13.0</v>
+                </pt>
+                <pt idx="13">
+                  <v>14.0</v>
+                </pt>
+                <pt idx="14">
+                  <v>15.0</v>
+                </pt>
+                <pt idx="15">
+                  <v>16.0</v>
+                </pt>
+                <pt idx="16">
+                  <v>17.0</v>
+                </pt>
+                <pt idx="17">
+                  <v>18.0</v>
+                </pt>
+                <pt idx="18">
+                  <v>19.0</v>
+                </pt>
+                <pt idx="19">
+                  <v>20.0</v>
+                </pt>
+                <pt idx="20">
+                  <v>21.0</v>
+                </pt>
+                <pt idx="21">
+                  <v>22.0</v>
+                </pt>
+                <pt idx="22">
+                  <v>23.0</v>
+                </pt>
+                <pt idx="23">
+                  <v>24.0</v>
+                </pt>
+                <pt idx="24">
+                  <v>25.0</v>
+                </pt>
+                <pt idx="25">
+                  <v>26.0</v>
+                </pt>
+                <pt idx="26">
+                  <v>27.0</v>
+                </pt>
+                <pt idx="27">
+                  <v>28.0</v>
+                </pt>
+                <pt idx="28">
+                  <v>29.0</v>
+                </pt>
+                <pt idx="29">
+                  <v>30.0</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Prognose'!$O$5:$O$34</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>263900.0</v>
+                </pt>
+                <pt idx="1">
+                  <v>267858.5</v>
+                </pt>
+                <pt idx="2">
+                  <v>271876.3775</v>
+                </pt>
+                <pt idx="3">
+                  <v>275954.5231625</v>
+                </pt>
+                <pt idx="4">
+                  <v>280093.841009937</v>
+                </pt>
+                <pt idx="5">
+                  <v>284295.248625086</v>
+                </pt>
+                <pt idx="6">
+                  <v>288559.677354463</v>
+                </pt>
+                <pt idx="7">
+                  <v>292888.07251478</v>
+                </pt>
+                <pt idx="8">
+                  <v>297281.393602501</v>
+                </pt>
+                <pt idx="9">
+                  <v>301740.614506539</v>
+                </pt>
+                <pt idx="10">
+                  <v>306266.723724137</v>
+                </pt>
+                <pt idx="11">
+                  <v>310860.724579999</v>
+                </pt>
+                <pt idx="12">
+                  <v>315523.635448699</v>
+                </pt>
+                <pt idx="13">
+                  <v>320256.489980429</v>
+                </pt>
+                <pt idx="14">
+                  <v>325060.337330136</v>
+                </pt>
+                <pt idx="15">
+                  <v>329936.242390088</v>
+                </pt>
+                <pt idx="16">
+                  <v>334885.286025939</v>
+                </pt>
+                <pt idx="17">
+                  <v>339908.565316328</v>
+                </pt>
+                <pt idx="18">
+                  <v>345007.193796073</v>
+                </pt>
+                <pt idx="19">
+                  <v>350182.301703014</v>
+                </pt>
+                <pt idx="20">
+                  <v>355435.036228559</v>
+                </pt>
+                <pt idx="21">
+                  <v>360766.561771987</v>
+                </pt>
+                <pt idx="22">
+                  <v>366178.060198567</v>
+                </pt>
+                <pt idx="23">
+                  <v>371670.731101546</v>
+                </pt>
+                <pt idx="24">
+                  <v>377245.792068069</v>
+                </pt>
+                <pt idx="25">
+                  <v>382904.47894909</v>
+                </pt>
+                <pt idx="26">
+                  <v>388648.046133326</v>
+                </pt>
+                <pt idx="27">
+                  <v>394477.766825326</v>
+                </pt>
+                <pt idx="28">
+                  <v>400394.933327706</v>
+                </pt>
+                <pt idx="29">
+                  <v>406400.857327621</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -592,6 +980,12 @@
           <tx>
             <strRef>
               <f>'Prognose'!I4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Restschuld Ende</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -613,11 +1007,199 @@
           <cat>
             <numRef>
               <f>'Prognose'!$A$5:$A$34</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>1.0</v>
+                </pt>
+                <pt idx="1">
+                  <v>2.0</v>
+                </pt>
+                <pt idx="2">
+                  <v>3.0</v>
+                </pt>
+                <pt idx="3">
+                  <v>4.0</v>
+                </pt>
+                <pt idx="4">
+                  <v>5.0</v>
+                </pt>
+                <pt idx="5">
+                  <v>6.0</v>
+                </pt>
+                <pt idx="6">
+                  <v>7.0</v>
+                </pt>
+                <pt idx="7">
+                  <v>8.0</v>
+                </pt>
+                <pt idx="8">
+                  <v>9.0</v>
+                </pt>
+                <pt idx="9">
+                  <v>10.0</v>
+                </pt>
+                <pt idx="10">
+                  <v>11.0</v>
+                </pt>
+                <pt idx="11">
+                  <v>12.0</v>
+                </pt>
+                <pt idx="12">
+                  <v>13.0</v>
+                </pt>
+                <pt idx="13">
+                  <v>14.0</v>
+                </pt>
+                <pt idx="14">
+                  <v>15.0</v>
+                </pt>
+                <pt idx="15">
+                  <v>16.0</v>
+                </pt>
+                <pt idx="16">
+                  <v>17.0</v>
+                </pt>
+                <pt idx="17">
+                  <v>18.0</v>
+                </pt>
+                <pt idx="18">
+                  <v>19.0</v>
+                </pt>
+                <pt idx="19">
+                  <v>20.0</v>
+                </pt>
+                <pt idx="20">
+                  <v>21.0</v>
+                </pt>
+                <pt idx="21">
+                  <v>22.0</v>
+                </pt>
+                <pt idx="22">
+                  <v>23.0</v>
+                </pt>
+                <pt idx="23">
+                  <v>24.0</v>
+                </pt>
+                <pt idx="24">
+                  <v>25.0</v>
+                </pt>
+                <pt idx="25">
+                  <v>26.0</v>
+                </pt>
+                <pt idx="26">
+                  <v>27.0</v>
+                </pt>
+                <pt idx="27">
+                  <v>28.0</v>
+                </pt>
+                <pt idx="28">
+                  <v>29.0</v>
+                </pt>
+                <pt idx="29">
+                  <v>30.0</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Prognose'!$I$5:$I$34</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>218657.425449633</v>
+                </pt>
+                <pt idx="1">
+                  <v>213939.194677327</v>
+                </pt>
+                <pt idx="2">
+                  <v>209038.515255581</v>
+                </pt>
+                <pt idx="3">
+                  <v>203948.3321014</v>
+                </pt>
+                <pt idx="4">
+                  <v>198661.317319708</v>
+                </pt>
+                <pt idx="5">
+                  <v>193169.85965401</v>
+                </pt>
+                <pt idx="6">
+                  <v>187466.05352913</v>
+                </pt>
+                <pt idx="7">
+                  <v>181541.687670236</v>
+                </pt>
+                <pt idx="8">
+                  <v>175388.233281783</v>
+                </pt>
+                <pt idx="9">
+                  <v>168996.831769344</v>
+                </pt>
+                <pt idx="10">
+                  <v>163544.547785565</v>
+                </pt>
+                <pt idx="11">
+                  <v>157841.7868295</v>
+                </pt>
+                <pt idx="12">
+                  <v>151877.042032864</v>
+                </pt>
+                <pt idx="13">
+                  <v>145638.277903859</v>
+                </pt>
+                <pt idx="14">
+                  <v>139112.906042299</v>
+                </pt>
+                <pt idx="15">
+                  <v>132287.759739093</v>
+                </pt>
+                <pt idx="16">
+                  <v>125149.067408842</v>
+                </pt>
+                <pt idx="17">
+                  <v>117682.42480192</v>
+                </pt>
+                <pt idx="18">
+                  <v>109872.765939996</v>
+                </pt>
+                <pt idx="19">
+                  <v>101704.332716328</v>
+                </pt>
+                <pt idx="20">
+                  <v>93160.6430995092</v>
+                </pt>
+                <pt idx="21">
+                  <v>84224.4578764927</v>
+                </pt>
+                <pt idx="22">
+                  <v>74877.7458678004</v>
+                </pt>
+                <pt idx="23">
+                  <v>65101.6475447241</v>
+                </pt>
+                <pt idx="24">
+                  <v>54876.436975106</v>
+                </pt>
+                <pt idx="25">
+                  <v>44181.4820209165</v>
+                </pt>
+                <pt idx="26">
+                  <v>32995.2027073146</v>
+                </pt>
+                <pt idx="27">
+                  <v>21295.0276791906</v>
+                </pt>
+                <pt idx="28">
+                  <v>9057.34865733028</v>
+                </pt>
+                <pt idx="29">
+                  <v>0.0</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -783,6 +1365,12 @@
           <tx>
             <strRef>
               <f>'Diagrammdaten'!I3</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Zinsen</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -799,11 +1387,199 @@
           <cat>
             <numRef>
               <f>'Diagrammdaten'!$H$4:$H$33</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>1.0</v>
+                </pt>
+                <pt idx="1">
+                  <v>2.0</v>
+                </pt>
+                <pt idx="2">
+                  <v>3.0</v>
+                </pt>
+                <pt idx="3">
+                  <v>4.0</v>
+                </pt>
+                <pt idx="4">
+                  <v>5.0</v>
+                </pt>
+                <pt idx="5">
+                  <v>6.0</v>
+                </pt>
+                <pt idx="6">
+                  <v>7.0</v>
+                </pt>
+                <pt idx="7">
+                  <v>8.0</v>
+                </pt>
+                <pt idx="8">
+                  <v>9.0</v>
+                </pt>
+                <pt idx="9">
+                  <v>10.0</v>
+                </pt>
+                <pt idx="10">
+                  <v>11.0</v>
+                </pt>
+                <pt idx="11">
+                  <v>12.0</v>
+                </pt>
+                <pt idx="12">
+                  <v>13.0</v>
+                </pt>
+                <pt idx="13">
+                  <v>14.0</v>
+                </pt>
+                <pt idx="14">
+                  <v>15.0</v>
+                </pt>
+                <pt idx="15">
+                  <v>16.0</v>
+                </pt>
+                <pt idx="16">
+                  <v>17.0</v>
+                </pt>
+                <pt idx="17">
+                  <v>18.0</v>
+                </pt>
+                <pt idx="18">
+                  <v>19.0</v>
+                </pt>
+                <pt idx="19">
+                  <v>20.0</v>
+                </pt>
+                <pt idx="20">
+                  <v>21.0</v>
+                </pt>
+                <pt idx="21">
+                  <v>22.0</v>
+                </pt>
+                <pt idx="22">
+                  <v>23.0</v>
+                </pt>
+                <pt idx="23">
+                  <v>24.0</v>
+                </pt>
+                <pt idx="24">
+                  <v>25.0</v>
+                </pt>
+                <pt idx="25">
+                  <v>26.0</v>
+                </pt>
+                <pt idx="26">
+                  <v>27.0</v>
+                </pt>
+                <pt idx="27">
+                  <v>28.0</v>
+                </pt>
+                <pt idx="28">
+                  <v>29.0</v>
+                </pt>
+                <pt idx="29">
+                  <v>30.0</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Diagrammdaten'!$I$4:$I$33</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>8403.02544963295</v>
+                </pt>
+                <pt idx="1">
+                  <v>8227.36922769425</v>
+                </pt>
+                <pt idx="2">
+                  <v>8044.92057825354</v>
+                </pt>
+                <pt idx="3">
+                  <v>7855.41684581897</v>
+                </pt>
+                <pt idx="4">
+                  <v>7658.58521830782</v>
+                </pt>
+                <pt idx="5">
+                  <v>7454.1423343025</v>
+                </pt>
+                <pt idx="6">
+                  <v>7241.79387511985</v>
+                </pt>
+                <pt idx="7">
+                  <v>7021.23414110595</v>
+                </pt>
+                <pt idx="8">
+                  <v>6792.14561154687</v>
+                </pt>
+                <pt idx="9">
+                  <v>6554.19848756174</v>
+                </pt>
+                <pt idx="10">
+                  <v>7493.31601622083</v>
+                </pt>
+                <pt idx="11">
+                  <v>7242.83904393442</v>
+                </pt>
+                <pt idx="12">
+                  <v>6980.85520336445</v>
+                </pt>
+                <pt idx="13">
+                  <v>6706.83587099524</v>
+                </pt>
+                <pt idx="14">
+                  <v>6420.22813843926</v>
+                </pt>
+                <pt idx="15">
+                  <v>6120.45369679436</v>
+                </pt>
+                <pt idx="16">
+                  <v>5806.90766974868</v>
+                </pt>
+                <pt idx="17">
+                  <v>5478.95739307833</v>
+                </pt>
+                <pt idx="18">
+                  <v>5135.94113807573</v>
+                </pt>
+                <pt idx="19">
+                  <v>4777.16677633224</v>
+                </pt>
+                <pt idx="20">
+                  <v>4401.9103831812</v>
+                </pt>
+                <pt idx="21">
+                  <v>4009.41477698345</v>
+                </pt>
+                <pt idx="22">
+                  <v>3598.88799130776</v>
+                </pt>
+                <pt idx="23">
+                  <v>3169.50167692366</v>
+                </pt>
+                <pt idx="24">
+                  <v>2720.38943038193</v>
+                </pt>
+                <pt idx="25">
+                  <v>2250.6450458105</v>
+                </pt>
+                <pt idx="26">
+                  <v>1759.32068639805</v>
+                </pt>
+                <pt idx="27">
+                  <v>1245.424971876</v>
+                </pt>
+                <pt idx="28">
+                  <v>707.920978139713</v>
+                </pt>
+                <pt idx="29">
+                  <v>162.891321402753</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -813,6 +1589,12 @@
           <tx>
             <strRef>
               <f>'Diagrammdaten'!J3</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Tilgung</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -829,11 +1611,199 @@
           <cat>
             <numRef>
               <f>'Diagrammdaten'!$H$4:$H$33</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>1.0</v>
+                </pt>
+                <pt idx="1">
+                  <v>2.0</v>
+                </pt>
+                <pt idx="2">
+                  <v>3.0</v>
+                </pt>
+                <pt idx="3">
+                  <v>4.0</v>
+                </pt>
+                <pt idx="4">
+                  <v>5.0</v>
+                </pt>
+                <pt idx="5">
+                  <v>6.0</v>
+                </pt>
+                <pt idx="6">
+                  <v>7.0</v>
+                </pt>
+                <pt idx="7">
+                  <v>8.0</v>
+                </pt>
+                <pt idx="8">
+                  <v>9.0</v>
+                </pt>
+                <pt idx="9">
+                  <v>10.0</v>
+                </pt>
+                <pt idx="10">
+                  <v>11.0</v>
+                </pt>
+                <pt idx="11">
+                  <v>12.0</v>
+                </pt>
+                <pt idx="12">
+                  <v>13.0</v>
+                </pt>
+                <pt idx="13">
+                  <v>14.0</v>
+                </pt>
+                <pt idx="14">
+                  <v>15.0</v>
+                </pt>
+                <pt idx="15">
+                  <v>16.0</v>
+                </pt>
+                <pt idx="16">
+                  <v>17.0</v>
+                </pt>
+                <pt idx="17">
+                  <v>18.0</v>
+                </pt>
+                <pt idx="18">
+                  <v>19.0</v>
+                </pt>
+                <pt idx="19">
+                  <v>20.0</v>
+                </pt>
+                <pt idx="20">
+                  <v>21.0</v>
+                </pt>
+                <pt idx="21">
+                  <v>22.0</v>
+                </pt>
+                <pt idx="22">
+                  <v>23.0</v>
+                </pt>
+                <pt idx="23">
+                  <v>24.0</v>
+                </pt>
+                <pt idx="24">
+                  <v>25.0</v>
+                </pt>
+                <pt idx="25">
+                  <v>26.0</v>
+                </pt>
+                <pt idx="26">
+                  <v>27.0</v>
+                </pt>
+                <pt idx="27">
+                  <v>28.0</v>
+                </pt>
+                <pt idx="28">
+                  <v>29.0</v>
+                </pt>
+                <pt idx="29">
+                  <v>30.0</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Diagrammdaten'!$J$4:$J$33</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>4542.57455036705</v>
+                </pt>
+                <pt idx="1">
+                  <v>4718.23077230575</v>
+                </pt>
+                <pt idx="2">
+                  <v>4900.67942174646</v>
+                </pt>
+                <pt idx="3">
+                  <v>5090.18315418102</v>
+                </pt>
+                <pt idx="4">
+                  <v>5287.01478169218</v>
+                </pt>
+                <pt idx="5">
+                  <v>5491.4576656975</v>
+                </pt>
+                <pt idx="6">
+                  <v>5703.80612488015</v>
+                </pt>
+                <pt idx="7">
+                  <v>5924.36585889405</v>
+                </pt>
+                <pt idx="8">
+                  <v>6153.45438845313</v>
+                </pt>
+                <pt idx="9">
+                  <v>6391.40151243826</v>
+                </pt>
+                <pt idx="10">
+                  <v>5452.28398377917</v>
+                </pt>
+                <pt idx="11">
+                  <v>5702.76095606558</v>
+                </pt>
+                <pt idx="12">
+                  <v>5964.74479663555</v>
+                </pt>
+                <pt idx="13">
+                  <v>6238.76412900476</v>
+                </pt>
+                <pt idx="14">
+                  <v>6525.37186156074</v>
+                </pt>
+                <pt idx="15">
+                  <v>6825.14630320563</v>
+                </pt>
+                <pt idx="16">
+                  <v>7138.69233025132</v>
+                </pt>
+                <pt idx="17">
+                  <v>7466.64260692167</v>
+                </pt>
+                <pt idx="18">
+                  <v>7809.65886192427</v>
+                </pt>
+                <pt idx="19">
+                  <v>8168.43322366776</v>
+                </pt>
+                <pt idx="20">
+                  <v>8543.6896168188</v>
+                </pt>
+                <pt idx="21">
+                  <v>8936.18522301655</v>
+                </pt>
+                <pt idx="22">
+                  <v>9346.71200869224</v>
+                </pt>
+                <pt idx="23">
+                  <v>9776.09832307634</v>
+                </pt>
+                <pt idx="24">
+                  <v>10225.2105696181</v>
+                </pt>
+                <pt idx="25">
+                  <v>10694.9549541895</v>
+                </pt>
+                <pt idx="26">
+                  <v>11186.279313602</v>
+                </pt>
+                <pt idx="27">
+                  <v>11700.175028124</v>
+                </pt>
+                <pt idx="28">
+                  <v>12237.6790218603</v>
+                </pt>
+                <pt idx="29">
+                  <v>9057.34865733028</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -999,6 +1969,12 @@
           <tx>
             <strRef>
               <f>'Prognose'!N4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Kumulierter Cashflow</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -1020,11 +1996,199 @@
           <cat>
             <numRef>
               <f>'Prognose'!$A$5:$A$34</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>1.0</v>
+                </pt>
+                <pt idx="1">
+                  <v>2.0</v>
+                </pt>
+                <pt idx="2">
+                  <v>3.0</v>
+                </pt>
+                <pt idx="3">
+                  <v>4.0</v>
+                </pt>
+                <pt idx="4">
+                  <v>5.0</v>
+                </pt>
+                <pt idx="5">
+                  <v>6.0</v>
+                </pt>
+                <pt idx="6">
+                  <v>7.0</v>
+                </pt>
+                <pt idx="7">
+                  <v>8.0</v>
+                </pt>
+                <pt idx="8">
+                  <v>9.0</v>
+                </pt>
+                <pt idx="9">
+                  <v>10.0</v>
+                </pt>
+                <pt idx="10">
+                  <v>11.0</v>
+                </pt>
+                <pt idx="11">
+                  <v>12.0</v>
+                </pt>
+                <pt idx="12">
+                  <v>13.0</v>
+                </pt>
+                <pt idx="13">
+                  <v>14.0</v>
+                </pt>
+                <pt idx="14">
+                  <v>15.0</v>
+                </pt>
+                <pt idx="15">
+                  <v>16.0</v>
+                </pt>
+                <pt idx="16">
+                  <v>17.0</v>
+                </pt>
+                <pt idx="17">
+                  <v>18.0</v>
+                </pt>
+                <pt idx="18">
+                  <v>19.0</v>
+                </pt>
+                <pt idx="19">
+                  <v>20.0</v>
+                </pt>
+                <pt idx="20">
+                  <v>21.0</v>
+                </pt>
+                <pt idx="21">
+                  <v>22.0</v>
+                </pt>
+                <pt idx="22">
+                  <v>23.0</v>
+                </pt>
+                <pt idx="23">
+                  <v>24.0</v>
+                </pt>
+                <pt idx="24">
+                  <v>25.0</v>
+                </pt>
+                <pt idx="25">
+                  <v>26.0</v>
+                </pt>
+                <pt idx="26">
+                  <v>27.0</v>
+                </pt>
+                <pt idx="27">
+                  <v>28.0</v>
+                </pt>
+                <pt idx="28">
+                  <v>29.0</v>
+                </pt>
+                <pt idx="29">
+                  <v>30.0</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Prognose'!$N$5:$N$34</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>-2931.75236511011</v>
+                </pt>
+                <pt idx="1">
+                  <v>-5828.29909680184</v>
+                </pt>
+                <pt idx="2">
+                  <v>-8690.49868582578</v>
+                </pt>
+                <pt idx="3">
+                  <v>-11519.2735170176</v>
+                </pt>
+                <pt idx="4">
+                  <v>-14315.6127484568</v>
+                </pt>
+                <pt idx="5">
+                  <v>-17080.575307046</v>
+                </pt>
+                <pt idx="6">
+                  <v>-19815.2930050675</v>
+                </pt>
+                <pt idx="7">
+                  <v>-22520.9737824516</v>
+                </pt>
+                <pt idx="8">
+                  <v>-25198.9050796745</v>
+                </pt>
+                <pt idx="9">
+                  <v>-27850.4573463918</v>
+                </pt>
+                <pt idx="10">
+                  <v>-30121.2079514467</v>
+                </pt>
+                <pt idx="11">
+                  <v>-32366.7157254715</v>
+                </pt>
+                <pt idx="12">
+                  <v>-34589.0967460334</v>
+                </pt>
+                <pt idx="13">
+                  <v>-36790.6090341288</v>
+                </pt>
+                <pt idx="14">
+                  <v>-38973.659657913</v>
+                </pt>
+                <pt idx="15">
+                  <v>-41140.8121697551</v>
+                </pt>
+                <pt idx="16">
+                  <v>-43294.7943920006</v>
+                </pt>
+                <pt idx="17">
+                  <v>-45438.5065675306</v>
+                </pt>
+                <pt idx="18">
+                  <v>-47575.029891948</v>
+                </pt>
+                <pt idx="19">
+                  <v>-49707.6354449903</v>
+                </pt>
+                <pt idx="20">
+                  <v>-51839.7935395838</v>
+                </pt>
+                <pt idx="21">
+                  <v>-53975.1835077927</v>
+                </pt>
+                <pt idx="22">
+                  <v>-56117.7039438092</v>
+                </pt>
+                <pt idx="23">
+                  <v>-58271.4834250491</v>
+                </pt>
+                <pt idx="24">
+                  <v>-60440.8917333912</v>
+                </pt>
+                <pt idx="25">
+                  <v>-62630.5515996093</v>
+                </pt>
+                <pt idx="26">
+                  <v>-64845.350995102</v>
+                </pt>
+                <pt idx="27">
+                  <v>-67090.4559961389</v>
+                </pt>
+                <pt idx="28">
+                  <v>-69371.3242469955</v>
+                </pt>
+                <pt idx="29">
+                  <v>-67963.2088753667</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1167,6 +2331,12 @@
           <tx>
             <strRef>
               <f>'Diagrammdaten'!B3</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>€ / Monat</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -1183,11 +2353,40 @@
           <cat>
             <numRef>
               <f>'Diagrammdaten'!$A$4:$A$10</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="7"/>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Diagrammdaten'!$B$4:$B$10</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="7"/>
+                <pt idx="0">
+                  <v>937.5</v>
+                </pt>
+                <pt idx="1">
+                  <v>-18.75</v>
+                </pt>
+                <pt idx="2">
+                  <v>-1078.8</v>
+                </pt>
+                <pt idx="3">
+                  <v>-145.833333333333</v>
+                </pt>
+                <pt idx="4">
+                  <v>-20.0</v>
+                </pt>
+                <pt idx="5">
+                  <v>81.5706362408238</v>
+                </pt>
+                <pt idx="6">
+                  <v>-244.31269709251</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -1341,6 +2540,12 @@
           <tx>
             <strRef>
               <f>'Diagrammdaten'!E3</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Cashflow nach Steuern / Monat</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -1369,11 +2574,73 @@
           <cat>
             <numRef>
               <f>'Diagrammdaten'!$D$4:$D$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="9"/>
+                <pt idx="0">
+                  <v>182000.0</v>
+                </pt>
+                <pt idx="1">
+                  <v>195000.0</v>
+                </pt>
+                <pt idx="2">
+                  <v>208000.0</v>
+                </pt>
+                <pt idx="3">
+                  <v>221000.0</v>
+                </pt>
+                <pt idx="4">
+                  <v>234000.0</v>
+                </pt>
+                <pt idx="5">
+                  <v>247000.0</v>
+                </pt>
+                <pt idx="6">
+                  <v>260000.0</v>
+                </pt>
+                <pt idx="7">
+                  <v>273000.0</v>
+                </pt>
+                <pt idx="8">
+                  <v>286000.0</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Diagrammdaten'!$E$4:$E$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="9"/>
+                <pt idx="0">
+                  <v>51.3138270980857</v>
+                </pt>
+                <pt idx="1">
+                  <v>2.04273973298643</v>
+                </pt>
+                <pt idx="2">
+                  <v>-47.2283476321128</v>
+                </pt>
+                <pt idx="3">
+                  <v>-96.499434997212</v>
+                </pt>
+                <pt idx="4">
+                  <v>-145.770522362311</v>
+                </pt>
+                <pt idx="5">
+                  <v>-195.04160972741</v>
+                </pt>
+                <pt idx="6">
+                  <v>-244.31269709251</v>
+                </pt>
+                <pt idx="7">
+                  <v>-293.583784457609</v>
+                </pt>
+                <pt idx="8">
+                  <v>-342.854871822708</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1516,6 +2783,12 @@
           <tx>
             <strRef>
               <f>'Diagrammdaten'!K3</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Guthaben Verkäufer (Ende Jahr)</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -1537,11 +2810,199 @@
           <cat>
             <numRef>
               <f>'Diagrammdaten'!$H$4:$H$33</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>1.0</v>
+                </pt>
+                <pt idx="1">
+                  <v>2.0</v>
+                </pt>
+                <pt idx="2">
+                  <v>3.0</v>
+                </pt>
+                <pt idx="3">
+                  <v>4.0</v>
+                </pt>
+                <pt idx="4">
+                  <v>5.0</v>
+                </pt>
+                <pt idx="5">
+                  <v>6.0</v>
+                </pt>
+                <pt idx="6">
+                  <v>7.0</v>
+                </pt>
+                <pt idx="7">
+                  <v>8.0</v>
+                </pt>
+                <pt idx="8">
+                  <v>9.0</v>
+                </pt>
+                <pt idx="9">
+                  <v>10.0</v>
+                </pt>
+                <pt idx="10">
+                  <v>11.0</v>
+                </pt>
+                <pt idx="11">
+                  <v>12.0</v>
+                </pt>
+                <pt idx="12">
+                  <v>13.0</v>
+                </pt>
+                <pt idx="13">
+                  <v>14.0</v>
+                </pt>
+                <pt idx="14">
+                  <v>15.0</v>
+                </pt>
+                <pt idx="15">
+                  <v>16.0</v>
+                </pt>
+                <pt idx="16">
+                  <v>17.0</v>
+                </pt>
+                <pt idx="17">
+                  <v>18.0</v>
+                </pt>
+                <pt idx="18">
+                  <v>19.0</v>
+                </pt>
+                <pt idx="19">
+                  <v>20.0</v>
+                </pt>
+                <pt idx="20">
+                  <v>21.0</v>
+                </pt>
+                <pt idx="21">
+                  <v>22.0</v>
+                </pt>
+                <pt idx="22">
+                  <v>23.0</v>
+                </pt>
+                <pt idx="23">
+                  <v>24.0</v>
+                </pt>
+                <pt idx="24">
+                  <v>25.0</v>
+                </pt>
+                <pt idx="25">
+                  <v>26.0</v>
+                </pt>
+                <pt idx="26">
+                  <v>27.0</v>
+                </pt>
+                <pt idx="27">
+                  <v>28.0</v>
+                </pt>
+                <pt idx="28">
+                  <v>29.0</v>
+                </pt>
+                <pt idx="29">
+                  <v>30.0</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Diagrammdaten'!$K$4:$K$33</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>255250.0</v>
+                </pt>
+                <pt idx="1">
+                  <v>250381.25</v>
+                </pt>
+                <pt idx="2">
+                  <v>245390.78125</v>
+                </pt>
+                <pt idx="3">
+                  <v>240275.55078125</v>
+                </pt>
+                <pt idx="4">
+                  <v>235032.439550781</v>
+                </pt>
+                <pt idx="5">
+                  <v>229658.250539551</v>
+                </pt>
+                <pt idx="6">
+                  <v>224149.70680304</v>
+                </pt>
+                <pt idx="7">
+                  <v>218503.449473116</v>
+                </pt>
+                <pt idx="8">
+                  <v>212716.035709944</v>
+                </pt>
+                <pt idx="9">
+                  <v>206783.936602692</v>
+                </pt>
+                <pt idx="10">
+                  <v>200703.53501776</v>
+                </pt>
+                <pt idx="11">
+                  <v>194471.123393204</v>
+                </pt>
+                <pt idx="12">
+                  <v>188082.901478034</v>
+                </pt>
+                <pt idx="13">
+                  <v>181534.974014985</v>
+                </pt>
+                <pt idx="14">
+                  <v>174823.348365359</v>
+                </pt>
+                <pt idx="15">
+                  <v>167943.932074493</v>
+                </pt>
+                <pt idx="16">
+                  <v>160892.530376356</v>
+                </pt>
+                <pt idx="17">
+                  <v>153664.843635764</v>
+                </pt>
+                <pt idx="18">
+                  <v>146256.464726659</v>
+                </pt>
+                <pt idx="19">
+                  <v>138662.876344825</v>
+                </pt>
+                <pt idx="20">
+                  <v>130879.448253446</v>
+                </pt>
+                <pt idx="21">
+                  <v>122901.434459782</v>
+                </pt>
+                <pt idx="22">
+                  <v>114723.970321277</v>
+                </pt>
+                <pt idx="23">
+                  <v>106342.069579308</v>
+                </pt>
+                <pt idx="24">
+                  <v>97750.6213187911</v>
+                </pt>
+                <pt idx="25">
+                  <v>88944.386851761</v>
+                </pt>
+                <pt idx="26">
+                  <v>79917.9965230551</v>
+                </pt>
+                <pt idx="27">
+                  <v>70665.9464361314</v>
+                </pt>
+                <pt idx="28">
+                  <v>61182.5950970347</v>
+                </pt>
+                <pt idx="29">
+                  <v>51462.1599744607</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1683,14 +3144,19 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
+  <twoCellAnchor editAs="twoCell">
     <from>
       <col>1</col>
       <colOff>0</colOff>
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="2736000"/>
+    <to>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1704,15 +3170,20 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
     <from>
       <col>10</col>
-      <colOff>0</colOff>
+      <colOff>180000</colOff>
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="2736000"/>
+    <to>
+      <col>19</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1726,15 +3197,20 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
     <from>
       <col>1</col>
       <colOff>0</colOff>
       <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="2736000"/>
+    <to>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1748,15 +3224,20 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
     <from>
       <col>10</col>
-      <colOff>0</colOff>
+      <colOff>180000</colOff>
       <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="2736000"/>
+    <to>
+      <col>19</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1770,15 +3251,20 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
     <from>
       <col>1</col>
       <colOff>0</colOff>
       <row>39</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="2736000"/>
+    <to>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -1792,15 +3278,20 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
     <from>
       <col>10</col>
-      <colOff>0</colOff>
+      <colOff>180000</colOff>
       <row>39</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="2736000"/>
+    <to>
+      <col>19</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -1814,15 +3305,20 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
     <from>
       <col>1</col>
       <colOff>0</colOff>
       <row>55</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="2736000"/>
+    <to>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>70</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -1836,7 +3332,7 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
+  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -2214,37 +3710,37 @@
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="5">
         <f>Rechner!$H$19</f>
-        <v/>
+        <v>-244.31269709251</v>
       </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="6">
         <f>Rechner!$H$21</f>
-        <v/>
+        <v>23.1111111111111</v>
       </c>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="7">
         <f>Rechner!$H$22</f>
-        <v/>
+        <v>0.0432692307692308</v>
       </c>
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="5">
         <f>Rechner!$H$32</f>
-        <v/>
+        <v>195538.969565093</v>
       </c>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="5">
         <f>Prognose!P14+Prognose!N14-Rechner!$C$17</f>
-        <v/>
+        <v>49893.3253908025</v>
       </c>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
       <c r="Q5" s="8">
         <f>Rechner!$H$39</f>
-        <v/>
+        <v>34.9182779848937</v>
       </c>
       <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
@@ -2257,9 +3753,9 @@
       </c>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="9">
+      <c r="E6" s="9" t="str">
         <f>Rechner!I21</f>
-        <v/>
+        <v>teuer</v>
       </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
@@ -2284,9 +3780,9 @@
       </c>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="9">
+      <c r="Q6" s="9" t="str">
         <f>"Lebenserwartung ca. "&amp;TEXT(Rechner!$H$38,"0")&amp;" J."</f>
-        <v/>
+        <v>Lebenserwartung ca. 13 J.</v>
       </c>
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
@@ -2467,7 +3963,7 @@
       </c>
       <c r="H6" s="16">
         <f>$C$7*$C$8</f>
-        <v/>
+        <v>937.5</v>
       </c>
     </row>
     <row r="7">
@@ -2496,7 +3992,7 @@
       </c>
       <c r="H7" s="16">
         <f>$H$6+$C$11</f>
-        <v/>
+        <v>937.5</v>
       </c>
     </row>
     <row r="8">
@@ -2525,7 +4021,7 @@
       </c>
       <c r="H8" s="16">
         <f>$C$6*($C$13+$C$14+$C$15)</f>
-        <v/>
+        <v>18200</v>
       </c>
     </row>
     <row r="9">
@@ -2554,7 +4050,7 @@
       </c>
       <c r="H9" s="16">
         <f>$C$6+$H$8+$C$9</f>
-        <v/>
+        <v>278200</v>
       </c>
     </row>
     <row r="10">
@@ -2583,7 +4079,7 @@
       </c>
       <c r="H10" s="16">
         <f>MAX(0,$H$9-$C$17)</f>
-        <v/>
+        <v>223200</v>
       </c>
     </row>
     <row r="11">
@@ -2629,7 +4125,7 @@
       </c>
       <c r="H12" s="16">
         <f>$H$7</f>
-        <v/>
+        <v>937.5</v>
       </c>
     </row>
     <row r="13">
@@ -2658,7 +4154,7 @@
       </c>
       <c r="H13" s="16">
         <f>-$H$7*$C$25</f>
-        <v/>
+        <v>-18.75</v>
       </c>
     </row>
     <row r="14">
@@ -2687,7 +4183,7 @@
       </c>
       <c r="H14" s="16">
         <f>-$H$10*($C$18+$C$19)/12</f>
-        <v/>
+        <v>-1078.8</v>
       </c>
     </row>
     <row r="15">
@@ -2716,7 +4212,7 @@
       </c>
       <c r="H15" s="16">
         <f>-($C$7+$C$10)*$C$23/12</f>
-        <v/>
+        <v>-145.833333333333</v>
       </c>
     </row>
     <row r="16">
@@ -2735,7 +4231,7 @@
       </c>
       <c r="H16" s="16">
         <f>-$C$24</f>
-        <v/>
+        <v>-20</v>
       </c>
     </row>
     <row r="17">
@@ -2764,7 +4260,7 @@
       </c>
       <c r="H17" s="20">
         <f>SUM($H$12:$H$16)</f>
-        <v/>
+        <v>-325.883333333333</v>
       </c>
     </row>
     <row r="18">
@@ -2793,7 +4289,7 @@
       </c>
       <c r="H18" s="16">
         <f>-$H$30/12</f>
-        <v/>
+        <v>81.5706362408238</v>
       </c>
     </row>
     <row r="19">
@@ -2822,11 +4318,11 @@
       </c>
       <c r="H19" s="23">
         <f>$H$17+$H$18</f>
-        <v/>
-      </c>
-      <c r="I19" s="22">
+        <v>-244.31269709251</v>
+      </c>
+      <c r="I19" s="22" t="str">
         <f>IF($H$19&gt;=0,"Trägt sich selbst",IF($H$19&gt;=-150,"Leichter Zuschuss nötig","Deutlicher Zuschuss nötig"))</f>
-        <v/>
+        <v>Deutlicher Zuschuss nötig</v>
       </c>
     </row>
     <row r="20">
@@ -2882,11 +4378,11 @@
       </c>
       <c r="H21" s="24">
         <f>IFERROR($C$6/($H$7*12),0)</f>
-        <v/>
-      </c>
-      <c r="I21" s="10">
+        <v>23.1111111111111</v>
+      </c>
+      <c r="I21" s="10" t="str">
         <f>IF($H$21&lt;=18,"günstig",IF($H$21&lt;=22,"mittel","teuer"))</f>
-        <v/>
+        <v>teuer</v>
       </c>
     </row>
     <row r="22">
@@ -2905,7 +4401,7 @@
       </c>
       <c r="H22" s="25">
         <f>IFERROR($H$7*12/$C$6,0)</f>
-        <v/>
+        <v>0.0432692307692308</v>
       </c>
     </row>
     <row r="23">
@@ -2934,7 +4430,7 @@
       </c>
       <c r="H23" s="25">
         <f>IFERROR(($H$12+$H$13+$H$15+$H$16)*12/$H$9,0)</f>
-        <v/>
+        <v>0.0324766355140187</v>
       </c>
     </row>
     <row r="24">
@@ -2963,7 +4459,7 @@
       </c>
       <c r="H24" s="26">
         <f>IFERROR(($H$19*12+$H$27)/$C$17,0)</f>
-        <v/>
+        <v>0.0292876760955806</v>
       </c>
     </row>
     <row r="25">
@@ -3015,7 +4511,7 @@
       </c>
       <c r="H26" s="27">
         <f>-Prognose!$G$5</f>
-        <v/>
+        <v>8403.02544963295</v>
       </c>
     </row>
     <row r="27">
@@ -3044,7 +4540,7 @@
       </c>
       <c r="H27" s="27">
         <f>-Prognose!$H$5</f>
-        <v/>
+        <v>4542.57455036705</v>
       </c>
     </row>
     <row r="28">
@@ -3073,7 +4569,7 @@
       </c>
       <c r="H28" s="16">
         <f>(($C$6+$H$8)*$C$26+$C$9)*$C$27</f>
-        <v/>
+        <v>3894.8</v>
       </c>
     </row>
     <row r="29">
@@ -3092,7 +4588,7 @@
       </c>
       <c r="H29" s="16">
         <f>($H$12+$H$13+$H$15+$H$16)*12-$H$26-$H$28</f>
-        <v/>
+        <v>-3262.82544963295</v>
       </c>
     </row>
     <row r="30">
@@ -3121,7 +4617,7 @@
       </c>
       <c r="H30" s="16">
         <f>$H$29*$C$28</f>
-        <v/>
+        <v>-978.847634889885</v>
       </c>
     </row>
     <row r="31">
@@ -3177,7 +4673,7 @@
       </c>
       <c r="H32" s="28">
         <f>IF($H$10&lt;=0,"–",MAX(0,$C$6+$H$19/((1+$C$13+$C$14+$C$15)/12*(($C$18+$C$19)-$C$28*($H$26/$H$10+$C$26*$C$27)))))</f>
-        <v/>
+        <v>195538.969565093</v>
       </c>
       <c r="I32" s="29" t="n"/>
     </row>
@@ -3197,7 +4693,7 @@
       </c>
       <c r="H33" s="16">
         <f>IF(ISNUMBER($H$32),MAX(0,$C$6-$H$32),0)</f>
-        <v/>
+        <v>64461.0304349071</v>
       </c>
     </row>
     <row r="34">
@@ -3226,11 +4722,11 @@
       </c>
       <c r="H34" s="26">
         <f>IFERROR($H$33/$C$6,0)</f>
-        <v/>
-      </c>
-      <c r="I34" s="10">
+        <v>0.247927040134258</v>
+      </c>
+      <c r="I34" s="10" t="str">
         <f>IF($H$10&lt;=0,"kein Darlehen – Formel nicht nötig",IF($H$33=0,"Preis passt","so viel Abschlag bräuchtest du"))</f>
-        <v/>
+        <v>so viel Abschlag bräuchtest du</v>
       </c>
     </row>
     <row r="35">
@@ -3268,7 +4764,7 @@
       </c>
       <c r="H36" s="16">
         <f>$C$6</f>
-        <v/>
+        <v>260000</v>
       </c>
     </row>
     <row r="37">
@@ -3279,7 +4775,7 @@
       </c>
       <c r="H37" s="16">
         <f>$H$6*12</f>
-        <v/>
+        <v>11250</v>
       </c>
     </row>
     <row r="38">
@@ -3290,7 +4786,7 @@
       </c>
       <c r="H38" s="24">
         <f>INDEX(Lebenserwartung!$B$4:$B$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1))+(INDEX(Lebenserwartung!$B$4:$B$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)+1)-INDEX(Lebenserwartung!$B$4:$B$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)))*(MIN(MAX($C$34,60),95)-INDEX(Lebenserwartung!$A$4:$A$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)))/(INDEX(Lebenserwartung!$A$4:$A$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)+1)-INDEX(Lebenserwartung!$A$4:$A$11,MATCH(MIN(MAX($C$34,60),94.99),Lebenserwartung!$A$4:$A$11,1)))</f>
-        <v/>
+        <v>13.2</v>
       </c>
     </row>
     <row r="39">
@@ -3301,7 +4797,7 @@
       </c>
       <c r="H39" s="24">
         <f>IF($H$37&lt;=0,"unbegrenzt",IF($C$35=0,$C$6/$H$37,IF($H$37&lt;=$C$6*$C$35,"unbegrenzt",NPER($C$35,-$H$37,$C$6))))</f>
-        <v/>
+        <v>34.9182779848937</v>
       </c>
     </row>
     <row r="40">
@@ -3312,7 +4808,7 @@
       </c>
       <c r="H40" s="16">
         <f>MAX(0,IF($C$35=0,$C$6-$H$37*$H$38,FV($C$35,$H$38,$H$37,-$C$6)))</f>
-        <v/>
+        <v>186786.218776152</v>
       </c>
     </row>
     <row r="41">
@@ -3321,9 +4817,9 @@
           <t>Bewertung</t>
         </is>
       </c>
-      <c r="H41" s="30">
+      <c r="H41" s="30" t="str">
         <f>IF($H$39="unbegrenzt","Geld reicht sicher",IF($H$39&gt;$H$38,"Geld reicht sicher","Achtung: Geld reicht voraussichtlich nicht"))</f>
-        <v/>
+        <v>Geld reicht sicher</v>
       </c>
     </row>
     <row r="43">
@@ -3341,9 +4837,9 @@
           <t>Prognose Jahr 1 = Monatswert × 12</t>
         </is>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="31" t="str">
         <f>IF(ABS(Prognose!$M$5-$H$19*12)&lt;1,"OK","Abweichung prüfen")</f>
-        <v/>
+        <v>OK</v>
       </c>
     </row>
     <row r="45">
@@ -3352,9 +4848,9 @@
           <t>Restschuld nie negativ</t>
         </is>
       </c>
-      <c r="H45" s="31">
+      <c r="H45" s="31" t="str">
         <f>IF(MIN(Prognose!$I$5:$I$34)&gt;=-0.01,"OK","Abweichung prüfen")</f>
-        <v/>
+        <v>OK</v>
       </c>
     </row>
     <row r="46">
@@ -3363,9 +4859,9 @@
           <t>Tilgung Jahr 1 + Zinsen = 12 Raten</t>
         </is>
       </c>
-      <c r="H46" s="31">
+      <c r="H46" s="31" t="str">
         <f>IF($H$10=0,"OK",IF(ABS($H$26+$H$27+$H$14*12)&lt;1,"OK","Abweichung prüfen"))</f>
-        <v/>
+        <v>OK</v>
       </c>
     </row>
     <row r="49">
@@ -3701,63 +5197,63 @@
       </c>
       <c r="B5" s="34">
         <f>IF(A5&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.038</v>
       </c>
       <c r="C5" s="35">
         <f>Rechner!$H$10</f>
-        <v/>
+        <v>223200</v>
       </c>
       <c r="D5" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A5-1)</f>
-        <v/>
+        <v>11250</v>
       </c>
       <c r="E5" s="35">
         <f>-D5*Rechner!$C$25</f>
-        <v/>
+        <v>-225</v>
       </c>
       <c r="F5" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A5-1)</f>
-        <v/>
+        <v>-1990</v>
       </c>
       <c r="G5" s="36">
         <f>IF(C5&lt;=0,0,IF(I5&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C5-I5)),IF(B5=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B5/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C5)-C5))))</f>
-        <v/>
+        <v>-8403.02544963295</v>
       </c>
       <c r="H5" s="36">
         <f>-(C5-I5)</f>
-        <v/>
+        <v>-4542.57455036705</v>
       </c>
       <c r="I5" s="36">
         <f>IF(C5&lt;=0,0,IF(B5=0,MAX(0,C5-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C5*(1+B5/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B5/12)^12-1)/(B5/12)))))</f>
-        <v/>
+        <v>218657.425449633</v>
       </c>
       <c r="J5" s="36">
         <f>D5+E5+F5+G5+H5</f>
-        <v/>
+        <v>-3910.6</v>
       </c>
       <c r="K5" s="35">
         <f>-Rechner!$H$28*(A5&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L5" s="36">
         <f>-(D5+E5+F5+G5+K5)*Rechner!$C$28</f>
-        <v/>
+        <v>978.847634889885</v>
       </c>
       <c r="M5" s="37">
         <f>J5+L5</f>
-        <v/>
+        <v>-2931.75236511011</v>
       </c>
       <c r="N5" s="36">
         <f>M5</f>
-        <v/>
+        <v>-2931.75236511011</v>
       </c>
       <c r="O5" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A5</f>
-        <v/>
+        <v>263900</v>
       </c>
       <c r="P5" s="37">
         <f>O5-I5</f>
-        <v/>
+        <v>45242.5745503671</v>
       </c>
     </row>
     <row r="6">
@@ -3766,63 +5262,63 @@
       </c>
       <c r="B6" s="34">
         <f>IF(A6&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.038</v>
       </c>
       <c r="C6" s="36">
         <f>I5</f>
-        <v/>
+        <v>218657.425449633</v>
       </c>
       <c r="D6" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A6-1)</f>
-        <v/>
+        <v>11418.75</v>
       </c>
       <c r="E6" s="35">
         <f>-D6*Rechner!$C$25</f>
-        <v/>
+        <v>-228.375</v>
       </c>
       <c r="F6" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A6-1)</f>
-        <v/>
+        <v>-2029.8</v>
       </c>
       <c r="G6" s="36">
         <f>IF(C6&lt;=0,0,IF(I6&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C6-I6)),IF(B6=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B6/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C6)-C6))))</f>
-        <v/>
+        <v>-8227.36922769425</v>
       </c>
       <c r="H6" s="36">
         <f>-(C6-I6)</f>
-        <v/>
+        <v>-4718.23077230575</v>
       </c>
       <c r="I6" s="36">
         <f>IF(C6&lt;=0,0,IF(B6=0,MAX(0,C6-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C6*(1+B6/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B6/12)^12-1)/(B6/12)))))</f>
-        <v/>
+        <v>213939.194677327</v>
       </c>
       <c r="J6" s="36">
         <f>D6+E6+F6+G6+H6</f>
-        <v/>
+        <v>-3785.025</v>
       </c>
       <c r="K6" s="35">
         <f>-Rechner!$H$28*(A6&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L6" s="36">
         <f>-(D6+E6+F6+G6+K6)*Rechner!$C$28</f>
-        <v/>
+        <v>888.478268308276</v>
       </c>
       <c r="M6" s="37">
         <f>J6+L6</f>
-        <v/>
+        <v>-2896.54673169172</v>
       </c>
       <c r="N6" s="36">
         <f>N5+M6</f>
-        <v/>
+        <v>-5828.29909680184</v>
       </c>
       <c r="O6" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A6</f>
-        <v/>
+        <v>267858.5</v>
       </c>
       <c r="P6" s="37">
         <f>O6-I6</f>
-        <v/>
+        <v>53919.3053226727</v>
       </c>
     </row>
     <row r="7">
@@ -3831,63 +5327,63 @@
       </c>
       <c r="B7" s="34">
         <f>IF(A7&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.038</v>
       </c>
       <c r="C7" s="36">
         <f>I6</f>
-        <v/>
+        <v>213939.194677327</v>
       </c>
       <c r="D7" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A7-1)</f>
-        <v/>
+        <v>11590.03125</v>
       </c>
       <c r="E7" s="35">
         <f>-D7*Rechner!$C$25</f>
-        <v/>
+        <v>-231.800625</v>
       </c>
       <c r="F7" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A7-1)</f>
-        <v/>
+        <v>-2070.396</v>
       </c>
       <c r="G7" s="36">
         <f>IF(C7&lt;=0,0,IF(I7&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C7-I7)),IF(B7=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B7/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C7)-C7))))</f>
-        <v/>
+        <v>-8044.92057825354</v>
       </c>
       <c r="H7" s="36">
         <f>-(C7-I7)</f>
-        <v/>
+        <v>-4900.67942174646</v>
       </c>
       <c r="I7" s="36">
         <f>IF(C7&lt;=0,0,IF(B7=0,MAX(0,C7-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C7*(1+B7/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B7/12)^12-1)/(B7/12)))))</f>
-        <v/>
+        <v>209038.515255581</v>
       </c>
       <c r="J7" s="36">
         <f>D7+E7+F7+G7+H7</f>
-        <v/>
+        <v>-3657.765375</v>
       </c>
       <c r="K7" s="35">
         <f>-Rechner!$H$28*(A7&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L7" s="36">
         <f>-(D7+E7+F7+G7+K7)*Rechner!$C$28</f>
-        <v/>
+        <v>795.565785976062</v>
       </c>
       <c r="M7" s="37">
         <f>J7+L7</f>
-        <v/>
+        <v>-2862.19958902394</v>
       </c>
       <c r="N7" s="36">
         <f>N6+M7</f>
-        <v/>
+        <v>-8690.49868582578</v>
       </c>
       <c r="O7" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A7</f>
-        <v/>
+        <v>271876.3775</v>
       </c>
       <c r="P7" s="37">
         <f>O7-I7</f>
-        <v/>
+        <v>62837.8622444191</v>
       </c>
     </row>
     <row r="8">
@@ -3896,63 +5392,63 @@
       </c>
       <c r="B8" s="34">
         <f>IF(A8&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.038</v>
       </c>
       <c r="C8" s="36">
         <f>I7</f>
-        <v/>
+        <v>209038.515255581</v>
       </c>
       <c r="D8" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A8-1)</f>
-        <v/>
+        <v>11763.88171875</v>
       </c>
       <c r="E8" s="35">
         <f>-D8*Rechner!$C$25</f>
-        <v/>
+        <v>-235.277634375</v>
       </c>
       <c r="F8" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A8-1)</f>
-        <v/>
+        <v>-2111.80392</v>
       </c>
       <c r="G8" s="36">
         <f>IF(C8&lt;=0,0,IF(I8&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C8-I8)),IF(B8=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B8/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C8)-C8))))</f>
-        <v/>
+        <v>-7855.41684581897</v>
       </c>
       <c r="H8" s="36">
         <f>-(C8-I8)</f>
-        <v/>
+        <v>-5090.18315418102</v>
       </c>
       <c r="I8" s="36">
         <f>IF(C8&lt;=0,0,IF(B8=0,MAX(0,C8-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C8*(1+B8/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B8/12)^12-1)/(B8/12)))))</f>
-        <v/>
+        <v>203948.3321014</v>
       </c>
       <c r="J8" s="36">
         <f>D8+E8+F8+G8+H8</f>
-        <v/>
+        <v>-3528.799835625</v>
       </c>
       <c r="K8" s="35">
         <f>-Rechner!$H$28*(A8&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L8" s="36">
         <f>-(D8+E8+F8+G8+K8)*Rechner!$C$28</f>
-        <v/>
+        <v>700.025004433194</v>
       </c>
       <c r="M8" s="37">
         <f>J8+L8</f>
-        <v/>
+        <v>-2828.77483119181</v>
       </c>
       <c r="N8" s="36">
         <f>N7+M8</f>
-        <v/>
+        <v>-11519.2735170176</v>
       </c>
       <c r="O8" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A8</f>
-        <v/>
+        <v>275954.5231625</v>
       </c>
       <c r="P8" s="37">
         <f>O8-I8</f>
-        <v/>
+        <v>72006.1910611002</v>
       </c>
     </row>
     <row r="9">
@@ -3961,63 +5457,63 @@
       </c>
       <c r="B9" s="34">
         <f>IF(A9&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.038</v>
       </c>
       <c r="C9" s="36">
         <f>I8</f>
-        <v/>
+        <v>203948.3321014</v>
       </c>
       <c r="D9" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A9-1)</f>
-        <v/>
+        <v>11940.3399445312</v>
       </c>
       <c r="E9" s="35">
         <f>-D9*Rechner!$C$25</f>
-        <v/>
+        <v>-238.806798890625</v>
       </c>
       <c r="F9" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A9-1)</f>
-        <v/>
+        <v>-2154.0399984</v>
       </c>
       <c r="G9" s="36">
         <f>IF(C9&lt;=0,0,IF(I9&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C9-I9)),IF(B9=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B9/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C9)-C9))))</f>
-        <v/>
+        <v>-7658.58521830782</v>
       </c>
       <c r="H9" s="36">
         <f>-(C9-I9)</f>
-        <v/>
+        <v>-5287.01478169218</v>
       </c>
       <c r="I9" s="36">
         <f>IF(C9&lt;=0,0,IF(B9=0,MAX(0,C9-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C9*(1+B9/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B9/12)^12-1)/(B9/12)))))</f>
-        <v/>
+        <v>198661.317319708</v>
       </c>
       <c r="J9" s="36">
         <f>D9+E9+F9+G9+H9</f>
-        <v/>
+        <v>-3398.10685275938</v>
       </c>
       <c r="K9" s="35">
         <f>-Rechner!$H$28*(A9&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L9" s="36">
         <f>-(D9+E9+F9+G9+K9)*Rechner!$C$28</f>
-        <v/>
+        <v>601.767621320158</v>
       </c>
       <c r="M9" s="37">
         <f>J9+L9</f>
-        <v/>
+        <v>-2796.33923143922</v>
       </c>
       <c r="N9" s="36">
         <f>N8+M9</f>
-        <v/>
+        <v>-14315.6127484568</v>
       </c>
       <c r="O9" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A9</f>
-        <v/>
+        <v>280093.841009937</v>
       </c>
       <c r="P9" s="37">
         <f>O9-I9</f>
-        <v/>
+        <v>81432.5236902298</v>
       </c>
     </row>
     <row r="10">
@@ -4026,63 +5522,63 @@
       </c>
       <c r="B10" s="34">
         <f>IF(A10&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.038</v>
       </c>
       <c r="C10" s="36">
         <f>I9</f>
-        <v/>
+        <v>198661.317319708</v>
       </c>
       <c r="D10" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A10-1)</f>
-        <v/>
+        <v>12119.4450436992</v>
       </c>
       <c r="E10" s="35">
         <f>-D10*Rechner!$C$25</f>
-        <v/>
+        <v>-242.388900873984</v>
       </c>
       <c r="F10" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A10-1)</f>
-        <v/>
+        <v>-2197.120798368</v>
       </c>
       <c r="G10" s="36">
         <f>IF(C10&lt;=0,0,IF(I10&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C10-I10)),IF(B10=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B10/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C10)-C10))))</f>
-        <v/>
+        <v>-7454.1423343025</v>
       </c>
       <c r="H10" s="36">
         <f>-(C10-I10)</f>
-        <v/>
+        <v>-5491.4576656975</v>
       </c>
       <c r="I10" s="36">
         <f>IF(C10&lt;=0,0,IF(B10=0,MAX(0,C10-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C10*(1+B10/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B10/12)^12-1)/(B10/12)))))</f>
-        <v/>
+        <v>193169.85965401</v>
       </c>
       <c r="J10" s="36">
         <f>D10+E10+F10+G10+H10</f>
-        <v/>
+        <v>-3265.66465554277</v>
       </c>
       <c r="K10" s="35">
         <f>-Rechner!$H$28*(A10&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L10" s="36">
         <f>-(D10+E10+F10+G10+K10)*Rechner!$C$28</f>
-        <v/>
+        <v>500.702096953582</v>
       </c>
       <c r="M10" s="37">
         <f>J10+L10</f>
-        <v/>
+        <v>-2764.96255858919</v>
       </c>
       <c r="N10" s="36">
         <f>N9+M10</f>
-        <v/>
+        <v>-17080.575307046</v>
       </c>
       <c r="O10" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A10</f>
-        <v/>
+        <v>284295.248625086</v>
       </c>
       <c r="P10" s="37">
         <f>O10-I10</f>
-        <v/>
+        <v>91125.3889710764</v>
       </c>
     </row>
     <row r="11">
@@ -4091,63 +5587,63 @@
       </c>
       <c r="B11" s="34">
         <f>IF(A11&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.038</v>
       </c>
       <c r="C11" s="36">
         <f>I10</f>
-        <v/>
+        <v>193169.85965401</v>
       </c>
       <c r="D11" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A11-1)</f>
-        <v/>
+        <v>12301.2367193547</v>
       </c>
       <c r="E11" s="35">
         <f>-D11*Rechner!$C$25</f>
-        <v/>
+        <v>-246.024734387094</v>
       </c>
       <c r="F11" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A11-1)</f>
-        <v/>
+        <v>-2241.06321433536</v>
       </c>
       <c r="G11" s="36">
         <f>IF(C11&lt;=0,0,IF(I11&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C11-I11)),IF(B11=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B11/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C11)-C11))))</f>
-        <v/>
+        <v>-7241.79387511985</v>
       </c>
       <c r="H11" s="36">
         <f>-(C11-I11)</f>
-        <v/>
+        <v>-5703.80612488015</v>
       </c>
       <c r="I11" s="36">
         <f>IF(C11&lt;=0,0,IF(B11=0,MAX(0,C11-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C11*(1+B11/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B11/12)^12-1)/(B11/12)))))</f>
-        <v/>
+        <v>187466.05352913</v>
       </c>
       <c r="J11" s="36">
         <f>D11+E11+F11+G11+H11</f>
-        <v/>
+        <v>-3131.45122936775</v>
       </c>
       <c r="K11" s="35">
         <f>-Rechner!$H$28*(A11&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L11" s="36">
         <f>-(D11+E11+F11+G11+K11)*Rechner!$C$28</f>
-        <v/>
+        <v>396.73353134628</v>
       </c>
       <c r="M11" s="37">
         <f>J11+L11</f>
-        <v/>
+        <v>-2734.71769802147</v>
       </c>
       <c r="N11" s="36">
         <f>N10+M11</f>
-        <v/>
+        <v>-19815.2930050675</v>
       </c>
       <c r="O11" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A11</f>
-        <v/>
+        <v>288559.677354463</v>
       </c>
       <c r="P11" s="37">
         <f>O11-I11</f>
-        <v/>
+        <v>101093.623825333</v>
       </c>
     </row>
     <row r="12">
@@ -4156,63 +5652,63 @@
       </c>
       <c r="B12" s="34">
         <f>IF(A12&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.038</v>
       </c>
       <c r="C12" s="36">
         <f>I11</f>
-        <v/>
+        <v>187466.05352913</v>
       </c>
       <c r="D12" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A12-1)</f>
-        <v/>
+        <v>12485.755270145</v>
       </c>
       <c r="E12" s="35">
         <f>-D12*Rechner!$C$25</f>
-        <v/>
+        <v>-249.7151054029</v>
       </c>
       <c r="F12" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A12-1)</f>
-        <v/>
+        <v>-2285.88447862207</v>
       </c>
       <c r="G12" s="36">
         <f>IF(C12&lt;=0,0,IF(I12&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C12-I12)),IF(B12=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B12/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C12)-C12))))</f>
-        <v/>
+        <v>-7021.23414110595</v>
       </c>
       <c r="H12" s="36">
         <f>-(C12-I12)</f>
-        <v/>
+        <v>-5924.36585889405</v>
       </c>
       <c r="I12" s="36">
         <f>IF(C12&lt;=0,0,IF(B12=0,MAX(0,C12-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C12*(1+B12/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B12/12)^12-1)/(B12/12)))))</f>
-        <v/>
+        <v>181541.687670236</v>
       </c>
       <c r="J12" s="36">
         <f>D12+E12+F12+G12+H12</f>
-        <v/>
+        <v>-2995.44431387995</v>
       </c>
       <c r="K12" s="35">
         <f>-Rechner!$H$28*(A12&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L12" s="36">
         <f>-(D12+E12+F12+G12+K12)*Rechner!$C$28</f>
-        <v/>
+        <v>289.76353649577</v>
       </c>
       <c r="M12" s="37">
         <f>J12+L12</f>
-        <v/>
+        <v>-2705.68077738418</v>
       </c>
       <c r="N12" s="36">
         <f>N11+M12</f>
-        <v/>
+        <v>-22520.9737824516</v>
       </c>
       <c r="O12" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A12</f>
-        <v/>
+        <v>292888.07251478</v>
       </c>
       <c r="P12" s="37">
         <f>O12-I12</f>
-        <v/>
+        <v>111346.384844544</v>
       </c>
     </row>
     <row r="13">
@@ -4221,63 +5717,63 @@
       </c>
       <c r="B13" s="34">
         <f>IF(A13&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.038</v>
       </c>
       <c r="C13" s="36">
         <f>I12</f>
-        <v/>
+        <v>181541.687670236</v>
       </c>
       <c r="D13" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A13-1)</f>
-        <v/>
+        <v>12673.0415991972</v>
       </c>
       <c r="E13" s="35">
         <f>-D13*Rechner!$C$25</f>
-        <v/>
+        <v>-253.460831983944</v>
       </c>
       <c r="F13" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A13-1)</f>
-        <v/>
+        <v>-2331.60216819451</v>
       </c>
       <c r="G13" s="36">
         <f>IF(C13&lt;=0,0,IF(I13&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C13-I13)),IF(B13=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B13/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C13)-C13))))</f>
-        <v/>
+        <v>-6792.14561154687</v>
       </c>
       <c r="H13" s="36">
         <f>-(C13-I13)</f>
-        <v/>
+        <v>-6153.45438845313</v>
       </c>
       <c r="I13" s="36">
         <f>IF(C13&lt;=0,0,IF(B13=0,MAX(0,C13-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C13*(1+B13/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B13/12)^12-1)/(B13/12)))))</f>
-        <v/>
+        <v>175388.233281783</v>
       </c>
       <c r="J13" s="36">
         <f>D13+E13+F13+G13+H13</f>
-        <v/>
+        <v>-2857.62140098126</v>
       </c>
       <c r="K13" s="35">
         <f>-Rechner!$H$28*(A13&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L13" s="36">
         <f>-(D13+E13+F13+G13+K13)*Rechner!$C$28</f>
-        <v/>
+        <v>179.690103758438</v>
       </c>
       <c r="M13" s="37">
         <f>J13+L13</f>
-        <v/>
+        <v>-2677.93129722282</v>
       </c>
       <c r="N13" s="36">
         <f>N12+M13</f>
-        <v/>
+        <v>-25198.9050796745</v>
       </c>
       <c r="O13" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A13</f>
-        <v/>
+        <v>297281.393602501</v>
       </c>
       <c r="P13" s="37">
         <f>O13-I13</f>
-        <v/>
+        <v>121893.160320719</v>
       </c>
     </row>
     <row r="14">
@@ -4286,63 +5782,63 @@
       </c>
       <c r="B14" s="34">
         <f>IF(A14&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.038</v>
       </c>
       <c r="C14" s="36">
         <f>I13</f>
-        <v/>
+        <v>175388.233281783</v>
       </c>
       <c r="D14" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A14-1)</f>
-        <v/>
+        <v>12863.1372231852</v>
       </c>
       <c r="E14" s="35">
         <f>-D14*Rechner!$C$25</f>
-        <v/>
+        <v>-257.262744463703</v>
       </c>
       <c r="F14" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A14-1)</f>
-        <v/>
+        <v>-2378.2342115584</v>
       </c>
       <c r="G14" s="36">
         <f>IF(C14&lt;=0,0,IF(I14&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C14-I14)),IF(B14=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B14/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C14)-C14))))</f>
-        <v/>
+        <v>-6554.19848756174</v>
       </c>
       <c r="H14" s="36">
         <f>-(C14-I14)</f>
-        <v/>
+        <v>-6391.40151243826</v>
       </c>
       <c r="I14" s="36">
         <f>IF(C14&lt;=0,0,IF(B14=0,MAX(0,C14-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C14*(1+B14/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B14/12)^12-1)/(B14/12)))))</f>
-        <v/>
+        <v>168996.831769344</v>
       </c>
       <c r="J14" s="36">
         <f>D14+E14+F14+G14+H14</f>
-        <v/>
+        <v>-2717.95973283695</v>
       </c>
       <c r="K14" s="35">
         <f>-Rechner!$H$28*(A14&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L14" s="36">
         <f>-(D14+E14+F14+G14+K14)*Rechner!$C$28</f>
-        <v/>
+        <v>66.4074661196078</v>
       </c>
       <c r="M14" s="37">
         <f>J14+L14</f>
-        <v/>
+        <v>-2651.55226671734</v>
       </c>
       <c r="N14" s="36">
         <f>N13+M14</f>
-        <v/>
+        <v>-27850.4573463918</v>
       </c>
       <c r="O14" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A14</f>
-        <v/>
+        <v>301740.614506539</v>
       </c>
       <c r="P14" s="37">
         <f>O14-I14</f>
-        <v/>
+        <v>132743.782737194</v>
       </c>
     </row>
     <row r="15">
@@ -4351,63 +5847,63 @@
       </c>
       <c r="B15" s="34">
         <f>IF(A15&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C15" s="36">
         <f>I14</f>
-        <v/>
+        <v>168996.831769344</v>
       </c>
       <c r="D15" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A15-1)</f>
-        <v/>
+        <v>13056.0842815329</v>
       </c>
       <c r="E15" s="35">
         <f>-D15*Rechner!$C$25</f>
-        <v/>
+        <v>-261.121685630659</v>
       </c>
       <c r="F15" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A15-1)</f>
-        <v/>
+        <v>-2425.79889578957</v>
       </c>
       <c r="G15" s="36">
         <f>IF(C15&lt;=0,0,IF(I15&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C15-I15)),IF(B15=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B15/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C15)-C15))))</f>
-        <v/>
+        <v>-7493.31601622083</v>
       </c>
       <c r="H15" s="36">
         <f>-(C15-I15)</f>
-        <v/>
+        <v>-5452.28398377917</v>
       </c>
       <c r="I15" s="36">
         <f>IF(C15&lt;=0,0,IF(B15=0,MAX(0,C15-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C15*(1+B15/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B15/12)^12-1)/(B15/12)))))</f>
-        <v/>
+        <v>163544.547785565</v>
       </c>
       <c r="J15" s="36">
         <f>D15+E15+F15+G15+H15</f>
-        <v/>
+        <v>-2576.4362998873</v>
       </c>
       <c r="K15" s="35">
         <f>-Rechner!$H$28*(A15&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L15" s="36">
         <f>-(D15+E15+F15+G15+K15)*Rechner!$C$28</f>
-        <v/>
+        <v>305.685694832438</v>
       </c>
       <c r="M15" s="37">
         <f>J15+L15</f>
-        <v/>
+        <v>-2270.75060505486</v>
       </c>
       <c r="N15" s="36">
         <f>N14+M15</f>
-        <v/>
+        <v>-30121.2079514467</v>
       </c>
       <c r="O15" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A15</f>
-        <v/>
+        <v>306266.723724137</v>
       </c>
       <c r="P15" s="37">
         <f>O15-I15</f>
-        <v/>
+        <v>142722.175938571</v>
       </c>
     </row>
     <row r="16">
@@ -4416,63 +5912,63 @@
       </c>
       <c r="B16" s="34">
         <f>IF(A16&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C16" s="36">
         <f>I15</f>
-        <v/>
+        <v>163544.547785565</v>
       </c>
       <c r="D16" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A16-1)</f>
-        <v/>
+        <v>13251.9255457559</v>
       </c>
       <c r="E16" s="35">
         <f>-D16*Rechner!$C$25</f>
-        <v/>
+        <v>-265.038510915118</v>
       </c>
       <c r="F16" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A16-1)</f>
-        <v/>
+        <v>-2474.31487370536</v>
       </c>
       <c r="G16" s="36">
         <f>IF(C16&lt;=0,0,IF(I16&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C16-I16)),IF(B16=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B16/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C16)-C16))))</f>
-        <v/>
+        <v>-7242.83904393442</v>
       </c>
       <c r="H16" s="36">
         <f>-(C16-I16)</f>
-        <v/>
+        <v>-5702.76095606558</v>
       </c>
       <c r="I16" s="36">
         <f>IF(C16&lt;=0,0,IF(B16=0,MAX(0,C16-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C16*(1+B16/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B16/12)^12-1)/(B16/12)))))</f>
-        <v/>
+        <v>157841.7868295</v>
       </c>
       <c r="J16" s="36">
         <f>D16+E16+F16+G16+H16</f>
-        <v/>
+        <v>-2433.02783886455</v>
       </c>
       <c r="K16" s="35">
         <f>-Rechner!$H$28*(A16&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L16" s="36">
         <f>-(D16+E16+F16+G16+K16)*Rechner!$C$28</f>
-        <v/>
+        <v>187.520064839691</v>
       </c>
       <c r="M16" s="37">
         <f>J16+L16</f>
-        <v/>
+        <v>-2245.50777402486</v>
       </c>
       <c r="N16" s="36">
         <f>N15+M16</f>
-        <v/>
+        <v>-32366.7157254715</v>
       </c>
       <c r="O16" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A16</f>
-        <v/>
+        <v>310860.724579999</v>
       </c>
       <c r="P16" s="37">
         <f>O16-I16</f>
-        <v/>
+        <v>153018.937750499</v>
       </c>
     </row>
     <row r="17">
@@ -4481,63 +5977,63 @@
       </c>
       <c r="B17" s="34">
         <f>IF(A17&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C17" s="36">
         <f>I16</f>
-        <v/>
+        <v>157841.7868295</v>
       </c>
       <c r="D17" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A17-1)</f>
-        <v/>
+        <v>13450.7044289423</v>
       </c>
       <c r="E17" s="35">
         <f>-D17*Rechner!$C$25</f>
-        <v/>
+        <v>-269.014088578845</v>
       </c>
       <c r="F17" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A17-1)</f>
-        <v/>
+        <v>-2523.80117117947</v>
       </c>
       <c r="G17" s="36">
         <f>IF(C17&lt;=0,0,IF(I17&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C17-I17)),IF(B17=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B17/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C17)-C17))))</f>
-        <v/>
+        <v>-6980.85520336445</v>
       </c>
       <c r="H17" s="36">
         <f>-(C17-I17)</f>
-        <v/>
+        <v>-5964.74479663555</v>
       </c>
       <c r="I17" s="36">
         <f>IF(C17&lt;=0,0,IF(B17=0,MAX(0,C17-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C17*(1+B17/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B17/12)^12-1)/(B17/12)))))</f>
-        <v/>
+        <v>151877.042032864</v>
       </c>
       <c r="J17" s="36">
         <f>D17+E17+F17+G17+H17</f>
-        <v/>
+        <v>-2287.71083081605</v>
       </c>
       <c r="K17" s="35">
         <f>-Rechner!$H$28*(A17&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L17" s="36">
         <f>-(D17+E17+F17+G17+K17)*Rechner!$C$28</f>
-        <v/>
+        <v>65.3298102541498</v>
       </c>
       <c r="M17" s="37">
         <f>J17+L17</f>
-        <v/>
+        <v>-2222.3810205619</v>
       </c>
       <c r="N17" s="36">
         <f>N16+M17</f>
-        <v/>
+        <v>-34589.0967460334</v>
       </c>
       <c r="O17" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A17</f>
-        <v/>
+        <v>315523.635448699</v>
       </c>
       <c r="P17" s="37">
         <f>O17-I17</f>
-        <v/>
+        <v>163646.593415835</v>
       </c>
     </row>
     <row r="18">
@@ -4546,63 +6042,63 @@
       </c>
       <c r="B18" s="34">
         <f>IF(A18&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C18" s="36">
         <f>I17</f>
-        <v/>
+        <v>151877.042032864</v>
       </c>
       <c r="D18" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A18-1)</f>
-        <v/>
+        <v>13652.4649953764</v>
       </c>
       <c r="E18" s="35">
         <f>-D18*Rechner!$C$25</f>
-        <v/>
+        <v>-273.049299907528</v>
       </c>
       <c r="F18" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A18-1)</f>
-        <v/>
+        <v>-2574.27719460306</v>
       </c>
       <c r="G18" s="36">
         <f>IF(C18&lt;=0,0,IF(I18&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C18-I18)),IF(B18=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B18/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C18)-C18))))</f>
-        <v/>
+        <v>-6706.83587099524</v>
       </c>
       <c r="H18" s="36">
         <f>-(C18-I18)</f>
-        <v/>
+        <v>-6238.76412900476</v>
       </c>
       <c r="I18" s="36">
         <f>IF(C18&lt;=0,0,IF(B18=0,MAX(0,C18-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C18*(1+B18/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B18/12)^12-1)/(B18/12)))))</f>
-        <v/>
+        <v>145638.277903859</v>
       </c>
       <c r="J18" s="36">
         <f>D18+E18+F18+G18+H18</f>
-        <v/>
+        <v>-2140.46149913419</v>
       </c>
       <c r="K18" s="35">
         <f>-Rechner!$H$28*(A18&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L18" s="36">
         <f>-(D18+E18+F18+G18+K18)*Rechner!$C$28</f>
-        <v/>
+        <v>-61.0507889611704</v>
       </c>
       <c r="M18" s="37">
         <f>J18+L18</f>
-        <v/>
+        <v>-2201.51228809536</v>
       </c>
       <c r="N18" s="36">
         <f>N17+M18</f>
-        <v/>
+        <v>-36790.6090341288</v>
       </c>
       <c r="O18" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A18</f>
-        <v/>
+        <v>320256.489980429</v>
       </c>
       <c r="P18" s="37">
         <f>O18-I18</f>
-        <v/>
+        <v>174618.21207657</v>
       </c>
     </row>
     <row r="19">
@@ -4611,63 +6107,63 @@
       </c>
       <c r="B19" s="34">
         <f>IF(A19&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C19" s="36">
         <f>I18</f>
-        <v/>
+        <v>145638.277903859</v>
       </c>
       <c r="D19" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A19-1)</f>
-        <v/>
+        <v>13857.251970307</v>
       </c>
       <c r="E19" s="35">
         <f>-D19*Rechner!$C$25</f>
-        <v/>
+        <v>-277.145039406141</v>
       </c>
       <c r="F19" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A19-1)</f>
-        <v/>
+        <v>-2625.76273849512</v>
       </c>
       <c r="G19" s="36">
         <f>IF(C19&lt;=0,0,IF(I19&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C19-I19)),IF(B19=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B19/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C19)-C19))))</f>
-        <v/>
+        <v>-6420.22813843926</v>
       </c>
       <c r="H19" s="36">
         <f>-(C19-I19)</f>
-        <v/>
+        <v>-6525.37186156074</v>
       </c>
       <c r="I19" s="36">
         <f>IF(C19&lt;=0,0,IF(B19=0,MAX(0,C19-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C19*(1+B19/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B19/12)^12-1)/(B19/12)))))</f>
-        <v/>
+        <v>139112.906042299</v>
       </c>
       <c r="J19" s="36">
         <f>D19+E19+F19+G19+H19</f>
-        <v/>
+        <v>-1991.25580759422</v>
       </c>
       <c r="K19" s="35">
         <f>-Rechner!$H$28*(A19&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L19" s="36">
         <f>-(D19+E19+F19+G19+K19)*Rechner!$C$28</f>
-        <v/>
+        <v>-191.794816189954</v>
       </c>
       <c r="M19" s="37">
         <f>J19+L19</f>
-        <v/>
+        <v>-2183.05062378418</v>
       </c>
       <c r="N19" s="36">
         <f>N18+M19</f>
-        <v/>
+        <v>-38973.659657913</v>
       </c>
       <c r="O19" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A19</f>
-        <v/>
+        <v>325060.337330136</v>
       </c>
       <c r="P19" s="37">
         <f>O19-I19</f>
-        <v/>
+        <v>185947.431287837</v>
       </c>
     </row>
     <row r="20">
@@ -4676,63 +6172,63 @@
       </c>
       <c r="B20" s="34">
         <f>IF(A20&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C20" s="36">
         <f>I19</f>
-        <v/>
+        <v>139112.906042299</v>
       </c>
       <c r="D20" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A20-1)</f>
-        <v/>
+        <v>14065.1107498616</v>
       </c>
       <c r="E20" s="35">
         <f>-D20*Rechner!$C$25</f>
-        <v/>
+        <v>-281.302214997233</v>
       </c>
       <c r="F20" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A20-1)</f>
-        <v/>
+        <v>-2678.27799326502</v>
       </c>
       <c r="G20" s="36">
         <f>IF(C20&lt;=0,0,IF(I20&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C20-I20)),IF(B20=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B20/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C20)-C20))))</f>
-        <v/>
+        <v>-6120.45369679436</v>
       </c>
       <c r="H20" s="36">
         <f>-(C20-I20)</f>
-        <v/>
+        <v>-6825.14630320563</v>
       </c>
       <c r="I20" s="36">
         <f>IF(C20&lt;=0,0,IF(B20=0,MAX(0,C20-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C20*(1+B20/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B20/12)^12-1)/(B20/12)))))</f>
-        <v/>
+        <v>132287.759739093</v>
       </c>
       <c r="J20" s="36">
         <f>D20+E20+F20+G20+H20</f>
-        <v/>
+        <v>-1840.06945840061</v>
       </c>
       <c r="K20" s="35">
         <f>-Rechner!$H$28*(A20&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L20" s="36">
         <f>-(D20+E20+F20+G20+K20)*Rechner!$C$28</f>
-        <v/>
+        <v>-327.083053441507</v>
       </c>
       <c r="M20" s="37">
         <f>J20+L20</f>
-        <v/>
+        <v>-2167.15251184212</v>
       </c>
       <c r="N20" s="36">
         <f>N19+M20</f>
-        <v/>
+        <v>-41140.8121697551</v>
       </c>
       <c r="O20" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A20</f>
-        <v/>
+        <v>329936.242390088</v>
       </c>
       <c r="P20" s="37">
         <f>O20-I20</f>
-        <v/>
+        <v>197648.482650995</v>
       </c>
     </row>
     <row r="21">
@@ -4741,63 +6237,63 @@
       </c>
       <c r="B21" s="34">
         <f>IF(A21&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C21" s="36">
         <f>I20</f>
-        <v/>
+        <v>132287.759739093</v>
       </c>
       <c r="D21" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A21-1)</f>
-        <v/>
+        <v>14276.0874111096</v>
       </c>
       <c r="E21" s="35">
         <f>-D21*Rechner!$C$25</f>
-        <v/>
+        <v>-285.521748222191</v>
       </c>
       <c r="F21" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A21-1)</f>
-        <v/>
+        <v>-2731.84355313032</v>
       </c>
       <c r="G21" s="36">
         <f>IF(C21&lt;=0,0,IF(I21&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C21-I21)),IF(B21=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B21/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C21)-C21))))</f>
-        <v/>
+        <v>-5806.90766974868</v>
       </c>
       <c r="H21" s="36">
         <f>-(C21-I21)</f>
-        <v/>
+        <v>-7138.69233025132</v>
       </c>
       <c r="I21" s="36">
         <f>IF(C21&lt;=0,0,IF(B21=0,MAX(0,C21-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C21*(1+B21/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B21/12)^12-1)/(B21/12)))))</f>
-        <v/>
+        <v>125149.067408842</v>
       </c>
       <c r="J21" s="36">
         <f>D21+E21+F21+G21+H21</f>
-        <v/>
+        <v>-1686.87789024295</v>
       </c>
       <c r="K21" s="35">
         <f>-Rechner!$H$28*(A21&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L21" s="36">
         <f>-(D21+E21+F21+G21+K21)*Rechner!$C$28</f>
-        <v/>
+        <v>-467.104332002511</v>
       </c>
       <c r="M21" s="37">
         <f>J21+L21</f>
-        <v/>
+        <v>-2153.98222224546</v>
       </c>
       <c r="N21" s="36">
         <f>N20+M21</f>
-        <v/>
+        <v>-43294.7943920006</v>
       </c>
       <c r="O21" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A21</f>
-        <v/>
+        <v>334885.286025939</v>
       </c>
       <c r="P21" s="37">
         <f>O21-I21</f>
-        <v/>
+        <v>209736.218617097</v>
       </c>
     </row>
     <row r="22">
@@ -4806,63 +6302,63 @@
       </c>
       <c r="B22" s="34">
         <f>IF(A22&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C22" s="36">
         <f>I21</f>
-        <v/>
+        <v>125149.067408842</v>
       </c>
       <c r="D22" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A22-1)</f>
-        <v/>
+        <v>14490.2287222762</v>
       </c>
       <c r="E22" s="35">
         <f>-D22*Rechner!$C$25</f>
-        <v/>
+        <v>-289.804574445524</v>
       </c>
       <c r="F22" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A22-1)</f>
-        <v/>
+        <v>-2786.48042419293</v>
       </c>
       <c r="G22" s="36">
         <f>IF(C22&lt;=0,0,IF(I22&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C22-I22)),IF(B22=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B22/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C22)-C22))))</f>
-        <v/>
+        <v>-5478.95739307833</v>
       </c>
       <c r="H22" s="36">
         <f>-(C22-I22)</f>
-        <v/>
+        <v>-7466.64260692167</v>
       </c>
       <c r="I22" s="36">
         <f>IF(C22&lt;=0,0,IF(B22=0,MAX(0,C22-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C22*(1+B22/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B22/12)^12-1)/(B22/12)))))</f>
-        <v/>
+        <v>117682.42480192</v>
       </c>
       <c r="J22" s="36">
         <f>D22+E22+F22+G22+H22</f>
-        <v/>
+        <v>-1531.65627636225</v>
       </c>
       <c r="K22" s="35">
         <f>-Rechner!$H$28*(A22&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L22" s="36">
         <f>-(D22+E22+F22+G22+K22)*Rechner!$C$28</f>
-        <v/>
+        <v>-612.055899167827</v>
       </c>
       <c r="M22" s="37">
         <f>J22+L22</f>
-        <v/>
+        <v>-2143.71217553007</v>
       </c>
       <c r="N22" s="36">
         <f>N21+M22</f>
-        <v/>
+        <v>-45438.5065675306</v>
       </c>
       <c r="O22" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A22</f>
-        <v/>
+        <v>339908.565316328</v>
       </c>
       <c r="P22" s="37">
         <f>O22-I22</f>
-        <v/>
+        <v>222226.140514408</v>
       </c>
     </row>
     <row r="23">
@@ -4871,63 +6367,63 @@
       </c>
       <c r="B23" s="34">
         <f>IF(A23&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C23" s="36">
         <f>I22</f>
-        <v/>
+        <v>117682.42480192</v>
       </c>
       <c r="D23" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A23-1)</f>
-        <v/>
+        <v>14707.5821531103</v>
       </c>
       <c r="E23" s="35">
         <f>-D23*Rechner!$C$25</f>
-        <v/>
+        <v>-294.151643062207</v>
       </c>
       <c r="F23" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A23-1)</f>
-        <v/>
+        <v>-2842.21003267678</v>
       </c>
       <c r="G23" s="36">
         <f>IF(C23&lt;=0,0,IF(I23&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C23-I23)),IF(B23=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B23/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C23)-C23))))</f>
-        <v/>
+        <v>-5135.94113807573</v>
       </c>
       <c r="H23" s="36">
         <f>-(C23-I23)</f>
-        <v/>
+        <v>-7809.65886192427</v>
       </c>
       <c r="I23" s="36">
         <f>IF(C23&lt;=0,0,IF(B23=0,MAX(0,C23-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C23*(1+B23/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B23/12)^12-1)/(B23/12)))))</f>
-        <v/>
+        <v>109872.765939996</v>
       </c>
       <c r="J23" s="36">
         <f>D23+E23+F23+G23+H23</f>
-        <v/>
+        <v>-1374.37952262865</v>
       </c>
       <c r="K23" s="35">
         <f>-Rechner!$H$28*(A23&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L23" s="36">
         <f>-(D23+E23+F23+G23+K23)*Rechner!$C$28</f>
-        <v/>
+        <v>-762.143801788687</v>
       </c>
       <c r="M23" s="37">
         <f>J23+L23</f>
-        <v/>
+        <v>-2136.52332441733</v>
       </c>
       <c r="N23" s="36">
         <f>N22+M23</f>
-        <v/>
+        <v>-47575.029891948</v>
       </c>
       <c r="O23" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A23</f>
-        <v/>
+        <v>345007.193796073</v>
       </c>
       <c r="P23" s="37">
         <f>O23-I23</f>
-        <v/>
+        <v>235134.427856077</v>
       </c>
     </row>
     <row r="24">
@@ -4936,63 +6432,63 @@
       </c>
       <c r="B24" s="34">
         <f>IF(A24&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C24" s="36">
         <f>I23</f>
-        <v/>
+        <v>109872.765939996</v>
       </c>
       <c r="D24" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A24-1)</f>
-        <v/>
+        <v>14928.195885407</v>
       </c>
       <c r="E24" s="35">
         <f>-D24*Rechner!$C$25</f>
-        <v/>
+        <v>-298.56391770814</v>
       </c>
       <c r="F24" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A24-1)</f>
-        <v/>
+        <v>-2899.05423333032</v>
       </c>
       <c r="G24" s="36">
         <f>IF(C24&lt;=0,0,IF(I24&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C24-I24)),IF(B24=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B24/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C24)-C24))))</f>
-        <v/>
+        <v>-4777.16677633224</v>
       </c>
       <c r="H24" s="36">
         <f>-(C24-I24)</f>
-        <v/>
+        <v>-8168.43322366776</v>
       </c>
       <c r="I24" s="36">
         <f>IF(C24&lt;=0,0,IF(B24=0,MAX(0,C24-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C24*(1+B24/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B24/12)^12-1)/(B24/12)))))</f>
-        <v/>
+        <v>101704.332716328</v>
       </c>
       <c r="J24" s="36">
         <f>D24+E24+F24+G24+H24</f>
-        <v/>
+        <v>-1215.02226563146</v>
       </c>
       <c r="K24" s="35">
         <f>-Rechner!$H$28*(A24&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L24" s="36">
         <f>-(D24+E24+F24+G24+K24)*Rechner!$C$28</f>
-        <v/>
+        <v>-917.583287410889</v>
       </c>
       <c r="M24" s="37">
         <f>J24+L24</f>
-        <v/>
+        <v>-2132.60555304235</v>
       </c>
       <c r="N24" s="36">
         <f>N23+M24</f>
-        <v/>
+        <v>-49707.6354449903</v>
       </c>
       <c r="O24" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A24</f>
-        <v/>
+        <v>350182.301703014</v>
       </c>
       <c r="P24" s="37">
         <f>O24-I24</f>
-        <v/>
+        <v>248477.968986686</v>
       </c>
     </row>
     <row r="25">
@@ -5001,63 +6497,63 @@
       </c>
       <c r="B25" s="34">
         <f>IF(A25&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C25" s="36">
         <f>I24</f>
-        <v/>
+        <v>101704.332716328</v>
       </c>
       <c r="D25" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A25-1)</f>
-        <v/>
+        <v>15152.1188236881</v>
       </c>
       <c r="E25" s="35">
         <f>-D25*Rechner!$C$25</f>
-        <v/>
+        <v>-303.042376473762</v>
       </c>
       <c r="F25" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A25-1)</f>
-        <v/>
+        <v>-2957.03531799693</v>
       </c>
       <c r="G25" s="36">
         <f>IF(C25&lt;=0,0,IF(I25&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C25-I25)),IF(B25=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B25/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C25)-C25))))</f>
-        <v/>
+        <v>-4401.9103831812</v>
       </c>
       <c r="H25" s="36">
         <f>-(C25-I25)</f>
-        <v/>
+        <v>-8543.6896168188</v>
       </c>
       <c r="I25" s="36">
         <f>IF(C25&lt;=0,0,IF(B25=0,MAX(0,C25-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C25*(1+B25/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B25/12)^12-1)/(B25/12)))))</f>
-        <v/>
+        <v>93160.6430995092</v>
       </c>
       <c r="J25" s="36">
         <f>D25+E25+F25+G25+H25</f>
-        <v/>
+        <v>-1053.55887078258</v>
       </c>
       <c r="K25" s="35">
         <f>-Rechner!$H$28*(A25&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L25" s="36">
         <f>-(D25+E25+F25+G25+K25)*Rechner!$C$28</f>
-        <v/>
+        <v>-1078.59922381086</v>
       </c>
       <c r="M25" s="37">
         <f>J25+L25</f>
-        <v/>
+        <v>-2132.15809459345</v>
       </c>
       <c r="N25" s="36">
         <f>N24+M25</f>
-        <v/>
+        <v>-51839.7935395838</v>
       </c>
       <c r="O25" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A25</f>
-        <v/>
+        <v>355435.036228559</v>
       </c>
       <c r="P25" s="37">
         <f>O25-I25</f>
-        <v/>
+        <v>262274.39312905</v>
       </c>
     </row>
     <row r="26">
@@ -5066,63 +6562,63 @@
       </c>
       <c r="B26" s="34">
         <f>IF(A26&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C26" s="36">
         <f>I25</f>
-        <v/>
+        <v>93160.6430995092</v>
       </c>
       <c r="D26" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A26-1)</f>
-        <v/>
+        <v>15379.4006060434</v>
       </c>
       <c r="E26" s="35">
         <f>-D26*Rechner!$C$25</f>
-        <v/>
+        <v>-307.588012120868</v>
       </c>
       <c r="F26" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A26-1)</f>
-        <v/>
+        <v>-3016.17602435686</v>
       </c>
       <c r="G26" s="36">
         <f>IF(C26&lt;=0,0,IF(I26&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C26-I26)),IF(B26=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B26/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C26)-C26))))</f>
-        <v/>
+        <v>-4009.41477698345</v>
       </c>
       <c r="H26" s="36">
         <f>-(C26-I26)</f>
-        <v/>
+        <v>-8936.18522301655</v>
       </c>
       <c r="I26" s="36">
         <f>IF(C26&lt;=0,0,IF(B26=0,MAX(0,C26-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C26*(1+B26/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B26/12)^12-1)/(B26/12)))))</f>
-        <v/>
+        <v>84224.4578764927</v>
       </c>
       <c r="J26" s="36">
         <f>D26+E26+F26+G26+H26</f>
-        <v/>
+        <v>-889.963430434309</v>
       </c>
       <c r="K26" s="35">
         <f>-Rechner!$H$28*(A26&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L26" s="36">
         <f>-(D26+E26+F26+G26+K26)*Rechner!$C$28</f>
-        <v/>
+        <v>-1245.42653777467</v>
       </c>
       <c r="M26" s="37">
         <f>J26+L26</f>
-        <v/>
+        <v>-2135.38996820898</v>
       </c>
       <c r="N26" s="36">
         <f>N25+M26</f>
-        <v/>
+        <v>-53975.1835077927</v>
       </c>
       <c r="O26" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A26</f>
-        <v/>
+        <v>360766.561771987</v>
       </c>
       <c r="P26" s="37">
         <f>O26-I26</f>
-        <v/>
+        <v>276542.103895495</v>
       </c>
     </row>
     <row r="27">
@@ -5131,63 +6627,63 @@
       </c>
       <c r="B27" s="34">
         <f>IF(A27&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C27" s="36">
         <f>I26</f>
-        <v/>
+        <v>84224.4578764927</v>
       </c>
       <c r="D27" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A27-1)</f>
-        <v/>
+        <v>15610.0916151341</v>
       </c>
       <c r="E27" s="35">
         <f>-D27*Rechner!$C$25</f>
-        <v/>
+        <v>-312.201832302681</v>
       </c>
       <c r="F27" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A27-1)</f>
-        <v/>
+        <v>-3076.499544844</v>
       </c>
       <c r="G27" s="36">
         <f>IF(C27&lt;=0,0,IF(I27&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C27-I27)),IF(B27=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B27/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C27)-C27))))</f>
-        <v/>
+        <v>-3598.88799130776</v>
       </c>
       <c r="H27" s="36">
         <f>-(C27-I27)</f>
-        <v/>
+        <v>-9346.71200869224</v>
       </c>
       <c r="I27" s="36">
         <f>IF(C27&lt;=0,0,IF(B27=0,MAX(0,C27-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C27*(1+B27/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B27/12)^12-1)/(B27/12)))))</f>
-        <v/>
+        <v>74877.7458678004</v>
       </c>
       <c r="J27" s="36">
         <f>D27+E27+F27+G27+H27</f>
-        <v/>
+        <v>-724.209762012612</v>
       </c>
       <c r="K27" s="35">
         <f>-Rechner!$H$28*(A27&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L27" s="36">
         <f>-(D27+E27+F27+G27+K27)*Rechner!$C$28</f>
-        <v/>
+        <v>-1418.31067400389</v>
       </c>
       <c r="M27" s="37">
         <f>J27+L27</f>
-        <v/>
+        <v>-2142.5204360165</v>
       </c>
       <c r="N27" s="36">
         <f>N26+M27</f>
-        <v/>
+        <v>-56117.7039438092</v>
       </c>
       <c r="O27" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A27</f>
-        <v/>
+        <v>366178.060198567</v>
       </c>
       <c r="P27" s="37">
         <f>O27-I27</f>
-        <v/>
+        <v>291300.314330767</v>
       </c>
     </row>
     <row r="28">
@@ -5196,63 +6692,63 @@
       </c>
       <c r="B28" s="34">
         <f>IF(A28&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C28" s="36">
         <f>I27</f>
-        <v/>
+        <v>74877.7458678004</v>
       </c>
       <c r="D28" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A28-1)</f>
-        <v/>
+        <v>15844.2429893611</v>
       </c>
       <c r="E28" s="35">
         <f>-D28*Rechner!$C$25</f>
-        <v/>
+        <v>-316.884859787222</v>
       </c>
       <c r="F28" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A28-1)</f>
-        <v/>
+        <v>-3138.02953574088</v>
       </c>
       <c r="G28" s="36">
         <f>IF(C28&lt;=0,0,IF(I28&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C28-I28)),IF(B28=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B28/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C28)-C28))))</f>
-        <v/>
+        <v>-3169.50167692366</v>
       </c>
       <c r="H28" s="36">
         <f>-(C28-I28)</f>
-        <v/>
+        <v>-9776.09832307634</v>
       </c>
       <c r="I28" s="36">
         <f>IF(C28&lt;=0,0,IF(B28=0,MAX(0,C28-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C28*(1+B28/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B28/12)^12-1)/(B28/12)))))</f>
-        <v/>
+        <v>65101.6475447241</v>
       </c>
       <c r="J28" s="36">
         <f>D28+E28+F28+G28+H28</f>
-        <v/>
+        <v>-556.271406167023</v>
       </c>
       <c r="K28" s="35">
         <f>-Rechner!$H$28*(A28&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L28" s="36">
         <f>-(D28+E28+F28+G28+K28)*Rechner!$C$28</f>
-        <v/>
+        <v>-1597.50807507279</v>
       </c>
       <c r="M28" s="37">
         <f>J28+L28</f>
-        <v/>
+        <v>-2153.77948123982</v>
       </c>
       <c r="N28" s="36">
         <f>N27+M28</f>
-        <v/>
+        <v>-58271.4834250491</v>
       </c>
       <c r="O28" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A28</f>
-        <v/>
+        <v>371670.731101546</v>
       </c>
       <c r="P28" s="37">
         <f>O28-I28</f>
-        <v/>
+        <v>306569.083556822</v>
       </c>
     </row>
     <row r="29">
@@ -5261,63 +6757,63 @@
       </c>
       <c r="B29" s="34">
         <f>IF(A29&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C29" s="36">
         <f>I28</f>
-        <v/>
+        <v>65101.6475447241</v>
       </c>
       <c r="D29" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A29-1)</f>
-        <v/>
+        <v>16081.9066342015</v>
       </c>
       <c r="E29" s="35">
         <f>-D29*Rechner!$C$25</f>
-        <v/>
+        <v>-321.63813268403</v>
       </c>
       <c r="F29" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A29-1)</f>
-        <v/>
+        <v>-3200.7901264557</v>
       </c>
       <c r="G29" s="36">
         <f>IF(C29&lt;=0,0,IF(I29&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C29-I29)),IF(B29=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B29/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C29)-C29))))</f>
-        <v/>
+        <v>-2720.38943038193</v>
       </c>
       <c r="H29" s="36">
         <f>-(C29-I29)</f>
-        <v/>
+        <v>-10225.2105696181</v>
       </c>
       <c r="I29" s="36">
         <f>IF(C29&lt;=0,0,IF(B29=0,MAX(0,C29-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C29*(1+B29/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B29/12)^12-1)/(B29/12)))))</f>
-        <v/>
+        <v>54876.436975106</v>
       </c>
       <c r="J29" s="36">
         <f>D29+E29+F29+G29+H29</f>
-        <v/>
+        <v>-386.121624938232</v>
       </c>
       <c r="K29" s="35">
         <f>-Rechner!$H$28*(A29&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L29" s="36">
         <f>-(D29+E29+F29+G29+K29)*Rechner!$C$28</f>
-        <v/>
+        <v>-1783.28668340395</v>
       </c>
       <c r="M29" s="37">
         <f>J29+L29</f>
-        <v/>
+        <v>-2169.40830834218</v>
       </c>
       <c r="N29" s="36">
         <f>N28+M29</f>
-        <v/>
+        <v>-60440.8917333912</v>
       </c>
       <c r="O29" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A29</f>
-        <v/>
+        <v>377245.792068069</v>
       </c>
       <c r="P29" s="37">
         <f>O29-I29</f>
-        <v/>
+        <v>322369.355092963</v>
       </c>
     </row>
     <row r="30">
@@ -5326,63 +6822,63 @@
       </c>
       <c r="B30" s="34">
         <f>IF(A30&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C30" s="36">
         <f>I29</f>
-        <v/>
+        <v>54876.436975106</v>
       </c>
       <c r="D30" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A30-1)</f>
-        <v/>
+        <v>16323.1352337145</v>
       </c>
       <c r="E30" s="35">
         <f>-D30*Rechner!$C$25</f>
-        <v/>
+        <v>-326.46270467429</v>
       </c>
       <c r="F30" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A30-1)</f>
-        <v/>
+        <v>-3264.80592898481</v>
       </c>
       <c r="G30" s="36">
         <f>IF(C30&lt;=0,0,IF(I30&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C30-I30)),IF(B30=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B30/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C30)-C30))))</f>
-        <v/>
+        <v>-2250.6450458105</v>
       </c>
       <c r="H30" s="36">
         <f>-(C30-I30)</f>
-        <v/>
+        <v>-10694.9549541895</v>
       </c>
       <c r="I30" s="36">
         <f>IF(C30&lt;=0,0,IF(B30=0,MAX(0,C30-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C30*(1+B30/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B30/12)^12-1)/(B30/12)))))</f>
-        <v/>
+        <v>44181.4820209165</v>
       </c>
       <c r="J30" s="36">
         <f>D30+E30+F30+G30+H30</f>
-        <v/>
+        <v>-213.733399944587</v>
       </c>
       <c r="K30" s="35">
         <f>-Rechner!$H$28*(A30&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L30" s="36">
         <f>-(D30+E30+F30+G30+K30)*Rechner!$C$28</f>
-        <v/>
+        <v>-1975.92646627347</v>
       </c>
       <c r="M30" s="37">
         <f>J30+L30</f>
-        <v/>
+        <v>-2189.65986621806</v>
       </c>
       <c r="N30" s="36">
         <f>N29+M30</f>
-        <v/>
+        <v>-62630.5515996093</v>
       </c>
       <c r="O30" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A30</f>
-        <v/>
+        <v>382904.47894909</v>
       </c>
       <c r="P30" s="37">
         <f>O30-I30</f>
-        <v/>
+        <v>338722.996928173</v>
       </c>
     </row>
     <row r="31">
@@ -5391,63 +6887,63 @@
       </c>
       <c r="B31" s="34">
         <f>IF(A31&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C31" s="36">
         <f>I30</f>
-        <v/>
+        <v>44181.4820209165</v>
       </c>
       <c r="D31" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A31-1)</f>
-        <v/>
+        <v>16567.9822622202</v>
       </c>
       <c r="E31" s="35">
         <f>-D31*Rechner!$C$25</f>
-        <v/>
+        <v>-331.359645244405</v>
       </c>
       <c r="F31" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A31-1)</f>
-        <v/>
+        <v>-3330.10204756451</v>
       </c>
       <c r="G31" s="36">
         <f>IF(C31&lt;=0,0,IF(I31&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C31-I31)),IF(B31=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B31/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C31)-C31))))</f>
-        <v/>
+        <v>-1759.32068639805</v>
       </c>
       <c r="H31" s="36">
         <f>-(C31-I31)</f>
-        <v/>
+        <v>-11186.279313602</v>
       </c>
       <c r="I31" s="36">
         <f>IF(C31&lt;=0,0,IF(B31=0,MAX(0,C31-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C31*(1+B31/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B31/12)^12-1)/(B31/12)))))</f>
-        <v/>
+        <v>32995.2027073146</v>
       </c>
       <c r="J31" s="36">
         <f>D31+E31+F31+G31+H31</f>
-        <v/>
+        <v>-39.0794305886811</v>
       </c>
       <c r="K31" s="35">
         <f>-Rechner!$H$28*(A31&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L31" s="36">
         <f>-(D31+E31+F31+G31+K31)*Rechner!$C$28</f>
-        <v/>
+        <v>-2175.71996490398</v>
       </c>
       <c r="M31" s="37">
         <f>J31+L31</f>
-        <v/>
+        <v>-2214.79939549266</v>
       </c>
       <c r="N31" s="36">
         <f>N30+M31</f>
-        <v/>
+        <v>-64845.350995102</v>
       </c>
       <c r="O31" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A31</f>
-        <v/>
+        <v>388648.046133326</v>
       </c>
       <c r="P31" s="37">
         <f>O31-I31</f>
-        <v/>
+        <v>355652.843426012</v>
       </c>
     </row>
     <row r="32">
@@ -5456,63 +6952,63 @@
       </c>
       <c r="B32" s="34">
         <f>IF(A32&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C32" s="36">
         <f>I31</f>
-        <v/>
+        <v>32995.2027073146</v>
       </c>
       <c r="D32" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A32-1)</f>
-        <v/>
+        <v>16816.5019961535</v>
       </c>
       <c r="E32" s="35">
         <f>-D32*Rechner!$C$25</f>
-        <v/>
+        <v>-336.330039923071</v>
       </c>
       <c r="F32" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A32-1)</f>
-        <v/>
+        <v>-3396.7040885158</v>
       </c>
       <c r="G32" s="36">
         <f>IF(C32&lt;=0,0,IF(I32&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C32-I32)),IF(B32=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B32/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C32)-C32))))</f>
-        <v/>
+        <v>-1245.424971876</v>
       </c>
       <c r="H32" s="36">
         <f>-(C32-I32)</f>
-        <v/>
+        <v>-11700.175028124</v>
       </c>
       <c r="I32" s="36">
         <f>IF(C32&lt;=0,0,IF(B32=0,MAX(0,C32-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C32*(1+B32/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B32/12)^12-1)/(B32/12)))))</f>
-        <v/>
+        <v>21295.0276791906</v>
       </c>
       <c r="J32" s="36">
         <f>D32+E32+F32+G32+H32</f>
-        <v/>
+        <v>137.867867714662</v>
       </c>
       <c r="K32" s="35">
         <f>-Rechner!$H$28*(A32&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L32" s="36">
         <f>-(D32+E32+F32+G32+K32)*Rechner!$C$28</f>
-        <v/>
+        <v>-2382.9728687516</v>
       </c>
       <c r="M32" s="37">
         <f>J32+L32</f>
-        <v/>
+        <v>-2245.10500103694</v>
       </c>
       <c r="N32" s="36">
         <f>N31+M32</f>
-        <v/>
+        <v>-67090.4559961389</v>
       </c>
       <c r="O32" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A32</f>
-        <v/>
+        <v>394477.766825326</v>
       </c>
       <c r="P32" s="37">
         <f>O32-I32</f>
-        <v/>
+        <v>373182.739146135</v>
       </c>
     </row>
     <row r="33">
@@ -5521,63 +7017,63 @@
       </c>
       <c r="B33" s="34">
         <f>IF(A33&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C33" s="36">
         <f>I32</f>
-        <v/>
+        <v>21295.0276791906</v>
       </c>
       <c r="D33" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A33-1)</f>
-        <v/>
+        <v>17068.7495260958</v>
       </c>
       <c r="E33" s="35">
         <f>-D33*Rechner!$C$25</f>
-        <v/>
+        <v>-341.374990521917</v>
       </c>
       <c r="F33" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A33-1)</f>
-        <v/>
+        <v>-3464.63817028612</v>
       </c>
       <c r="G33" s="36">
         <f>IF(C33&lt;=0,0,IF(I33&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C33-I33)),IF(B33=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B33/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C33)-C33))))</f>
-        <v/>
+        <v>-707.920978139713</v>
       </c>
       <c r="H33" s="36">
         <f>-(C33-I33)</f>
-        <v/>
+        <v>-12237.6790218603</v>
       </c>
       <c r="I33" s="36">
         <f>IF(C33&lt;=0,0,IF(B33=0,MAX(0,C33-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C33*(1+B33/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B33/12)^12-1)/(B33/12)))))</f>
-        <v/>
+        <v>9057.34865733028</v>
       </c>
       <c r="J33" s="36">
         <f>D33+E33+F33+G33+H33</f>
-        <v/>
+        <v>317.136365287804</v>
       </c>
       <c r="K33" s="35">
         <f>-Rechner!$H$28*(A33&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L33" s="36">
         <f>-(D33+E33+F33+G33+K33)*Rechner!$C$28</f>
-        <v/>
+        <v>-2598.00461614443</v>
       </c>
       <c r="M33" s="37">
         <f>J33+L33</f>
-        <v/>
+        <v>-2280.86825085662</v>
       </c>
       <c r="N33" s="36">
         <f>N32+M33</f>
-        <v/>
+        <v>-69371.3242469955</v>
       </c>
       <c r="O33" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A33</f>
-        <v/>
+        <v>400394.933327706</v>
       </c>
       <c r="P33" s="37">
         <f>O33-I33</f>
-        <v/>
+        <v>391337.584670376</v>
       </c>
     </row>
     <row r="34">
@@ -5586,63 +7082,63 @@
       </c>
       <c r="B34" s="34">
         <f>IF(A34&lt;=Rechner!$C$20,Rechner!$C$18,Rechner!$C$21)</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="C34" s="36">
         <f>I33</f>
-        <v/>
+        <v>9057.34865733028</v>
       </c>
       <c r="D34" s="35">
         <f>Rechner!$H$7*12*(1+Rechner!$C$30)^(A34-1)</f>
-        <v/>
+        <v>17324.7807689873</v>
       </c>
       <c r="E34" s="35">
         <f>-D34*Rechner!$C$25</f>
-        <v/>
+        <v>-346.495615379745</v>
       </c>
       <c r="F34" s="35">
         <f>(Rechner!$H$15+Rechner!$H$16)*12*(1+Rechner!$C$31)^(A34-1)</f>
-        <v/>
+        <v>-3533.93093369184</v>
       </c>
       <c r="G34" s="36">
         <f>IF(C34&lt;=0,0,IF(I34&gt;0,-(12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)-(C34-I34)),IF(B34=0,0,-((Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*NPER(B34/12,-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12),C34)-C34))))</f>
-        <v/>
+        <v>-162.891321402753</v>
       </c>
       <c r="H34" s="36">
         <f>-(C34-I34)</f>
-        <v/>
+        <v>-9057.34865733028</v>
       </c>
       <c r="I34" s="36">
         <f>IF(C34&lt;=0,0,IF(B34=0,MAX(0,C34-12*(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)),MAX(0,(C34*(1+B34/12)^12-(Rechner!$H$10*(Rechner!$C$18+Rechner!$C$19)/12)*((1+B34/12)^12-1)/(B34/12)))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J34" s="36">
         <f>D34+E34+F34+G34+H34</f>
-        <v/>
+        <v>4224.11424118266</v>
       </c>
       <c r="K34" s="35">
         <f>-Rechner!$H$28*(A34&lt;=1/Rechner!$C$27)</f>
-        <v/>
+        <v>-3894.8</v>
       </c>
       <c r="L34" s="36">
         <f>-(D34+E34+F34+G34+K34)*Rechner!$C$28</f>
-        <v/>
+        <v>-2815.99886955388</v>
       </c>
       <c r="M34" s="37">
         <f>J34+L34</f>
-        <v/>
+        <v>1408.11537162878</v>
       </c>
       <c r="N34" s="36">
         <f>N33+M34</f>
-        <v/>
+        <v>-67963.2088753667</v>
       </c>
       <c r="O34" s="35">
         <f>Rechner!$C$6*(1+Rechner!$C$32)^A34</f>
-        <v/>
+        <v>406400.857327621</v>
       </c>
       <c r="P34" s="37">
         <f>O34-I34</f>
-        <v/>
+        <v>406400.857327621</v>
       </c>
     </row>
     <row r="36">
@@ -5859,15 +7355,15 @@
       </c>
       <c r="B4" s="35">
         <f>Rechner!$H$12</f>
-        <v/>
+        <v>937.5</v>
       </c>
       <c r="D4" s="41">
         <f>Rechner!$C$6*(1+F4)</f>
-        <v/>
+        <v>182000</v>
       </c>
       <c r="E4" s="41">
         <f>Rechner!$H$19-$E$14*(D4-Rechner!$C$6)</f>
-        <v/>
+        <v>51.3138270980857</v>
       </c>
       <c r="F4" s="42" t="n">
         <v>-0.3</v>
@@ -5877,15 +7373,15 @@
       </c>
       <c r="I4" s="41">
         <f>-Prognose!G5</f>
-        <v/>
+        <v>8403.02544963295</v>
       </c>
       <c r="J4" s="41">
         <f>-Prognose!H5</f>
-        <v/>
+        <v>4542.57455036705</v>
       </c>
       <c r="K4" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H4,FV(Rechner!$C$35,H4,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>255250</v>
       </c>
     </row>
     <row r="5">
@@ -5896,15 +7392,15 @@
       </c>
       <c r="B5" s="35">
         <f>Rechner!$H$13</f>
-        <v/>
+        <v>-18.75</v>
       </c>
       <c r="D5" s="41">
         <f>Rechner!$C$6*(1+F5)</f>
-        <v/>
+        <v>195000</v>
       </c>
       <c r="E5" s="41">
         <f>Rechner!$H$19-$E$14*(D5-Rechner!$C$6)</f>
-        <v/>
+        <v>2.04273973298643</v>
       </c>
       <c r="F5" s="42" t="n">
         <v>-0.25</v>
@@ -5914,15 +7410,15 @@
       </c>
       <c r="I5" s="41">
         <f>-Prognose!G6</f>
-        <v/>
+        <v>8227.36922769425</v>
       </c>
       <c r="J5" s="41">
         <f>-Prognose!H6</f>
-        <v/>
+        <v>4718.23077230575</v>
       </c>
       <c r="K5" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H5,FV(Rechner!$C$35,H5,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>250381.25</v>
       </c>
     </row>
     <row r="6">
@@ -5933,15 +7429,15 @@
       </c>
       <c r="B6" s="35">
         <f>Rechner!$H$14</f>
-        <v/>
+        <v>-1078.8</v>
       </c>
       <c r="D6" s="41">
         <f>Rechner!$C$6*(1+F6)</f>
-        <v/>
+        <v>208000</v>
       </c>
       <c r="E6" s="41">
         <f>Rechner!$H$19-$E$14*(D6-Rechner!$C$6)</f>
-        <v/>
+        <v>-47.2283476321128</v>
       </c>
       <c r="F6" s="42" t="n">
         <v>-0.2</v>
@@ -5951,15 +7447,15 @@
       </c>
       <c r="I6" s="41">
         <f>-Prognose!G7</f>
-        <v/>
+        <v>8044.92057825354</v>
       </c>
       <c r="J6" s="41">
         <f>-Prognose!H7</f>
-        <v/>
+        <v>4900.67942174646</v>
       </c>
       <c r="K6" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H6,FV(Rechner!$C$35,H6,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>245390.78125</v>
       </c>
     </row>
     <row r="7">
@@ -5970,15 +7466,15 @@
       </c>
       <c r="B7" s="35">
         <f>Rechner!$H$15</f>
-        <v/>
+        <v>-145.833333333333</v>
       </c>
       <c r="D7" s="41">
         <f>Rechner!$C$6*(1+F7)</f>
-        <v/>
+        <v>221000</v>
       </c>
       <c r="E7" s="41">
         <f>Rechner!$H$19-$E$14*(D7-Rechner!$C$6)</f>
-        <v/>
+        <v>-96.499434997212</v>
       </c>
       <c r="F7" s="42" t="n">
         <v>-0.15</v>
@@ -5988,15 +7484,15 @@
       </c>
       <c r="I7" s="41">
         <f>-Prognose!G8</f>
-        <v/>
+        <v>7855.41684581897</v>
       </c>
       <c r="J7" s="41">
         <f>-Prognose!H8</f>
-        <v/>
+        <v>5090.18315418102</v>
       </c>
       <c r="K7" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H7,FV(Rechner!$C$35,H7,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>240275.55078125</v>
       </c>
     </row>
     <row r="8">
@@ -6007,15 +7503,15 @@
       </c>
       <c r="B8" s="35">
         <f>Rechner!$H$16</f>
-        <v/>
+        <v>-20</v>
       </c>
       <c r="D8" s="41">
         <f>Rechner!$C$6*(1+F8)</f>
-        <v/>
+        <v>234000</v>
       </c>
       <c r="E8" s="41">
         <f>Rechner!$H$19-$E$14*(D8-Rechner!$C$6)</f>
-        <v/>
+        <v>-145.770522362311</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>-0.1</v>
@@ -6025,15 +7521,15 @@
       </c>
       <c r="I8" s="41">
         <f>-Prognose!G9</f>
-        <v/>
+        <v>7658.58521830782</v>
       </c>
       <c r="J8" s="41">
         <f>-Prognose!H9</f>
-        <v/>
+        <v>5287.01478169218</v>
       </c>
       <c r="K8" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H8,FV(Rechner!$C$35,H8,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>235032.439550781</v>
       </c>
     </row>
     <row r="9">
@@ -6044,15 +7540,15 @@
       </c>
       <c r="B9" s="35">
         <f>Rechner!$H$18</f>
-        <v/>
+        <v>81.5706362408238</v>
       </c>
       <c r="D9" s="41">
         <f>Rechner!$C$6*(1+F9)</f>
-        <v/>
+        <v>247000</v>
       </c>
       <c r="E9" s="41">
         <f>Rechner!$H$19-$E$14*(D9-Rechner!$C$6)</f>
-        <v/>
+        <v>-195.04160972741</v>
       </c>
       <c r="F9" s="42" t="n">
         <v>-0.05</v>
@@ -6062,15 +7558,15 @@
       </c>
       <c r="I9" s="41">
         <f>-Prognose!G10</f>
-        <v/>
+        <v>7454.1423343025</v>
       </c>
       <c r="J9" s="41">
         <f>-Prognose!H10</f>
-        <v/>
+        <v>5491.4576656975</v>
       </c>
       <c r="K9" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H9,FV(Rechner!$C$35,H9,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>229658.250539551</v>
       </c>
     </row>
     <row r="10">
@@ -6081,15 +7577,15 @@
       </c>
       <c r="B10" s="35">
         <f>Rechner!$H$19</f>
-        <v/>
+        <v>-244.31269709251</v>
       </c>
       <c r="D10" s="41">
         <f>Rechner!$C$6*(1+F10)</f>
-        <v/>
+        <v>260000</v>
       </c>
       <c r="E10" s="41">
         <f>Rechner!$H$19-$E$14*(D10-Rechner!$C$6)</f>
-        <v/>
+        <v>-244.31269709251</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>0</v>
@@ -6099,25 +7595,25 @@
       </c>
       <c r="I10" s="41">
         <f>-Prognose!G11</f>
-        <v/>
+        <v>7241.79387511985</v>
       </c>
       <c r="J10" s="41">
         <f>-Prognose!H11</f>
-        <v/>
+        <v>5703.80612488015</v>
       </c>
       <c r="K10" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H10,FV(Rechner!$C$35,H10,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>224149.70680304</v>
       </c>
     </row>
     <row r="11">
       <c r="D11" s="41">
         <f>Rechner!$C$6*(1+F11)</f>
-        <v/>
+        <v>273000</v>
       </c>
       <c r="E11" s="41">
         <f>Rechner!$H$19-$E$14*(D11-Rechner!$C$6)</f>
-        <v/>
+        <v>-293.583784457609</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>0.05</v>
@@ -6127,25 +7623,25 @@
       </c>
       <c r="I11" s="41">
         <f>-Prognose!G12</f>
-        <v/>
+        <v>7021.23414110595</v>
       </c>
       <c r="J11" s="41">
         <f>-Prognose!H12</f>
-        <v/>
+        <v>5924.36585889405</v>
       </c>
       <c r="K11" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H11,FV(Rechner!$C$35,H11,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>218503.449473116</v>
       </c>
     </row>
     <row r="12">
       <c r="D12" s="41">
         <f>Rechner!$C$6*(1+F12)</f>
-        <v/>
+        <v>286000</v>
       </c>
       <c r="E12" s="41">
         <f>Rechner!$H$19-$E$14*(D12-Rechner!$C$6)</f>
-        <v/>
+        <v>-342.854871822708</v>
       </c>
       <c r="F12" s="42" t="n">
         <v>0.1</v>
@@ -6155,15 +7651,15 @@
       </c>
       <c r="I12" s="41">
         <f>-Prognose!G13</f>
-        <v/>
+        <v>6792.14561154687</v>
       </c>
       <c r="J12" s="41">
         <f>-Prognose!H13</f>
-        <v/>
+        <v>6153.45438845313</v>
       </c>
       <c r="K12" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H12,FV(Rechner!$C$35,H12,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>212716.035709944</v>
       </c>
     </row>
     <row r="13">
@@ -6172,15 +7668,15 @@
       </c>
       <c r="I13" s="41">
         <f>-Prognose!G14</f>
-        <v/>
+        <v>6554.19848756174</v>
       </c>
       <c r="J13" s="41">
         <f>-Prognose!H14</f>
-        <v/>
+        <v>6391.40151243826</v>
       </c>
       <c r="K13" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H13,FV(Rechner!$C$35,H13,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>206783.936602692</v>
       </c>
     </row>
     <row r="14">
@@ -6191,22 +7687,22 @@
       </c>
       <c r="E14" s="43">
         <f>IF(Rechner!$H$10&lt;=0,0,(1+Rechner!$C$13+Rechner!$C$14+Rechner!$C$15)/12*((Rechner!$C$18+Rechner!$C$19)-Rechner!$C$28*(Rechner!$H$26/Rechner!$H$10+Rechner!$C$26*Rechner!$C$27)))</f>
-        <v/>
+        <v>0.00379008364346917</v>
       </c>
       <c r="H14" t="n">
         <v>11</v>
       </c>
       <c r="I14" s="41">
         <f>-Prognose!G15</f>
-        <v/>
+        <v>7493.31601622083</v>
       </c>
       <c r="J14" s="41">
         <f>-Prognose!H15</f>
-        <v/>
+        <v>5452.28398377917</v>
       </c>
       <c r="K14" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H14,FV(Rechner!$C$35,H14,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>200703.53501776</v>
       </c>
     </row>
     <row r="15">
@@ -6220,15 +7716,15 @@
       </c>
       <c r="I15" s="41">
         <f>-Prognose!G16</f>
-        <v/>
+        <v>7242.83904393442</v>
       </c>
       <c r="J15" s="41">
         <f>-Prognose!H16</f>
-        <v/>
+        <v>5702.76095606558</v>
       </c>
       <c r="K15" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H15,FV(Rechner!$C$35,H15,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>194471.123393204</v>
       </c>
     </row>
     <row r="16">
@@ -6237,15 +7733,15 @@
       </c>
       <c r="I16" s="41">
         <f>-Prognose!G17</f>
-        <v/>
+        <v>6980.85520336445</v>
       </c>
       <c r="J16" s="41">
         <f>-Prognose!H17</f>
-        <v/>
+        <v>5964.74479663555</v>
       </c>
       <c r="K16" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H16,FV(Rechner!$C$35,H16,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>188082.901478034</v>
       </c>
     </row>
     <row r="17">
@@ -6254,15 +7750,15 @@
       </c>
       <c r="I17" s="41">
         <f>-Prognose!G18</f>
-        <v/>
+        <v>6706.83587099524</v>
       </c>
       <c r="J17" s="41">
         <f>-Prognose!H18</f>
-        <v/>
+        <v>6238.76412900476</v>
       </c>
       <c r="K17" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H17,FV(Rechner!$C$35,H17,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>181534.974014985</v>
       </c>
     </row>
     <row r="18">
@@ -6271,15 +7767,15 @@
       </c>
       <c r="I18" s="41">
         <f>-Prognose!G19</f>
-        <v/>
+        <v>6420.22813843926</v>
       </c>
       <c r="J18" s="41">
         <f>-Prognose!H19</f>
-        <v/>
+        <v>6525.37186156074</v>
       </c>
       <c r="K18" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H18,FV(Rechner!$C$35,H18,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>174823.348365359</v>
       </c>
     </row>
     <row r="19">
@@ -6288,15 +7784,15 @@
       </c>
       <c r="I19" s="41">
         <f>-Prognose!G20</f>
-        <v/>
+        <v>6120.45369679436</v>
       </c>
       <c r="J19" s="41">
         <f>-Prognose!H20</f>
-        <v/>
+        <v>6825.14630320563</v>
       </c>
       <c r="K19" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H19,FV(Rechner!$C$35,H19,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>167943.932074493</v>
       </c>
     </row>
     <row r="20">
@@ -6305,15 +7801,15 @@
       </c>
       <c r="I20" s="41">
         <f>-Prognose!G21</f>
-        <v/>
+        <v>5806.90766974868</v>
       </c>
       <c r="J20" s="41">
         <f>-Prognose!H21</f>
-        <v/>
+        <v>7138.69233025132</v>
       </c>
       <c r="K20" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H20,FV(Rechner!$C$35,H20,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>160892.530376356</v>
       </c>
     </row>
     <row r="21">
@@ -6322,15 +7818,15 @@
       </c>
       <c r="I21" s="41">
         <f>-Prognose!G22</f>
-        <v/>
+        <v>5478.95739307833</v>
       </c>
       <c r="J21" s="41">
         <f>-Prognose!H22</f>
-        <v/>
+        <v>7466.64260692167</v>
       </c>
       <c r="K21" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H21,FV(Rechner!$C$35,H21,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>153664.843635764</v>
       </c>
     </row>
     <row r="22">
@@ -6339,15 +7835,15 @@
       </c>
       <c r="I22" s="41">
         <f>-Prognose!G23</f>
-        <v/>
+        <v>5135.94113807573</v>
       </c>
       <c r="J22" s="41">
         <f>-Prognose!H23</f>
-        <v/>
+        <v>7809.65886192427</v>
       </c>
       <c r="K22" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H22,FV(Rechner!$C$35,H22,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>146256.464726659</v>
       </c>
     </row>
     <row r="23">
@@ -6356,15 +7852,15 @@
       </c>
       <c r="I23" s="41">
         <f>-Prognose!G24</f>
-        <v/>
+        <v>4777.16677633224</v>
       </c>
       <c r="J23" s="41">
         <f>-Prognose!H24</f>
-        <v/>
+        <v>8168.43322366776</v>
       </c>
       <c r="K23" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H23,FV(Rechner!$C$35,H23,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>138662.876344825</v>
       </c>
     </row>
     <row r="24">
@@ -6373,15 +7869,15 @@
       </c>
       <c r="I24" s="41">
         <f>-Prognose!G25</f>
-        <v/>
+        <v>4401.9103831812</v>
       </c>
       <c r="J24" s="41">
         <f>-Prognose!H25</f>
-        <v/>
+        <v>8543.6896168188</v>
       </c>
       <c r="K24" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H24,FV(Rechner!$C$35,H24,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>130879.448253446</v>
       </c>
     </row>
     <row r="25">
@@ -6390,15 +7886,15 @@
       </c>
       <c r="I25" s="41">
         <f>-Prognose!G26</f>
-        <v/>
+        <v>4009.41477698345</v>
       </c>
       <c r="J25" s="41">
         <f>-Prognose!H26</f>
-        <v/>
+        <v>8936.18522301655</v>
       </c>
       <c r="K25" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H25,FV(Rechner!$C$35,H25,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>122901.434459782</v>
       </c>
     </row>
     <row r="26">
@@ -6407,15 +7903,15 @@
       </c>
       <c r="I26" s="41">
         <f>-Prognose!G27</f>
-        <v/>
+        <v>3598.88799130776</v>
       </c>
       <c r="J26" s="41">
         <f>-Prognose!H27</f>
-        <v/>
+        <v>9346.71200869224</v>
       </c>
       <c r="K26" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H26,FV(Rechner!$C$35,H26,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>114723.970321277</v>
       </c>
     </row>
     <row r="27">
@@ -6424,15 +7920,15 @@
       </c>
       <c r="I27" s="41">
         <f>-Prognose!G28</f>
-        <v/>
+        <v>3169.50167692366</v>
       </c>
       <c r="J27" s="41">
         <f>-Prognose!H28</f>
-        <v/>
+        <v>9776.09832307634</v>
       </c>
       <c r="K27" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H27,FV(Rechner!$C$35,H27,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>106342.069579308</v>
       </c>
     </row>
     <row r="28">
@@ -6441,15 +7937,15 @@
       </c>
       <c r="I28" s="41">
         <f>-Prognose!G29</f>
-        <v/>
+        <v>2720.38943038193</v>
       </c>
       <c r="J28" s="41">
         <f>-Prognose!H29</f>
-        <v/>
+        <v>10225.2105696181</v>
       </c>
       <c r="K28" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H28,FV(Rechner!$C$35,H28,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>97750.6213187911</v>
       </c>
     </row>
     <row r="29">
@@ -6458,15 +7954,15 @@
       </c>
       <c r="I29" s="41">
         <f>-Prognose!G30</f>
-        <v/>
+        <v>2250.6450458105</v>
       </c>
       <c r="J29" s="41">
         <f>-Prognose!H30</f>
-        <v/>
+        <v>10694.9549541895</v>
       </c>
       <c r="K29" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H29,FV(Rechner!$C$35,H29,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>88944.386851761</v>
       </c>
     </row>
     <row r="30">
@@ -6475,15 +7971,15 @@
       </c>
       <c r="I30" s="41">
         <f>-Prognose!G31</f>
-        <v/>
+        <v>1759.32068639805</v>
       </c>
       <c r="J30" s="41">
         <f>-Prognose!H31</f>
-        <v/>
+        <v>11186.279313602</v>
       </c>
       <c r="K30" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H30,FV(Rechner!$C$35,H30,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>79917.9965230551</v>
       </c>
     </row>
     <row r="31">
@@ -6492,15 +7988,15 @@
       </c>
       <c r="I31" s="41">
         <f>-Prognose!G32</f>
-        <v/>
+        <v>1245.424971876</v>
       </c>
       <c r="J31" s="41">
         <f>-Prognose!H32</f>
-        <v/>
+        <v>11700.175028124</v>
       </c>
       <c r="K31" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H31,FV(Rechner!$C$35,H31,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>70665.9464361314</v>
       </c>
     </row>
     <row r="32">
@@ -6509,15 +8005,15 @@
       </c>
       <c r="I32" s="41">
         <f>-Prognose!G33</f>
-        <v/>
+        <v>707.920978139713</v>
       </c>
       <c r="J32" s="41">
         <f>-Prognose!H33</f>
-        <v/>
+        <v>12237.6790218603</v>
       </c>
       <c r="K32" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H32,FV(Rechner!$C$35,H32,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>61182.5950970347</v>
       </c>
     </row>
     <row r="33">
@@ -6526,15 +8022,15 @@
       </c>
       <c r="I33" s="41">
         <f>-Prognose!G34</f>
-        <v/>
+        <v>162.891321402753</v>
       </c>
       <c r="J33" s="41">
         <f>-Prognose!H34</f>
-        <v/>
+        <v>9057.34865733028</v>
       </c>
       <c r="K33" s="41">
         <f>MAX(0,IF(Rechner!$C$35=0,Rechner!$C$6-Rechner!$H$37*H33,FV(Rechner!$C$35,H33,Rechner!$H$37,-Rechner!$C$6)))</f>
-        <v/>
+        <v>51462.1599744607</v>
       </c>
     </row>
   </sheetData>
